--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,24 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>Santa Fe</t>
+  </si>
+  <si>
+    <t>Deportivo Cali</t>
+  </si>
+  <si>
+    <t>2026-09-21 01:29:42</t>
   </si>
 </sst>
 </file>
@@ -585,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -830,6 +848,248 @@
         <v>79</v>
       </c>
     </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2">
+        <v>2.16</v>
+      </c>
+      <c r="G2">
+        <v>2.44</v>
+      </c>
+      <c r="H2">
+        <v>3.65</v>
+      </c>
+      <c r="I2">
+        <v>4.3</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3.45</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.11</v>
+      </c>
+      <c r="N2">
+        <v>2.46</v>
+      </c>
+      <c r="O2">
+        <v>1.47</v>
+      </c>
+      <c r="P2">
+        <v>1.57</v>
+      </c>
+      <c r="Q2">
+        <v>2.4</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>4.3</v>
+      </c>
+      <c r="T2">
+        <v>1.86</v>
+      </c>
+      <c r="U2">
+        <v>1.71</v>
+      </c>
+      <c r="V2">
+        <v>1.3</v>
+      </c>
+      <c r="W2">
+        <v>1.7</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>13.5</v>
+      </c>
+      <c r="Z2">
+        <v>32</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>9</v>
+      </c>
+      <c r="AC2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD2">
+        <v>20</v>
+      </c>
+      <c r="AE2">
+        <v>80</v>
+      </c>
+      <c r="AF2">
+        <v>16</v>
+      </c>
+      <c r="AG2">
+        <v>14.5</v>
+      </c>
+      <c r="AH2">
+        <v>26</v>
+      </c>
+      <c r="AI2">
+        <v>100</v>
+      </c>
+      <c r="AJ2">
+        <v>38</v>
+      </c>
+      <c r="AK2">
+        <v>36</v>
+      </c>
+      <c r="AL2">
+        <v>75</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>36</v>
+      </c>
+      <c r="AO2">
+        <v>100</v>
+      </c>
+      <c r="AP2">
+        <v>3.1</v>
+      </c>
+      <c r="AQ2">
+        <v>9</v>
+      </c>
+      <c r="AR2">
+        <v>19</v>
+      </c>
+      <c r="AS2">
+        <v>3.1</v>
+      </c>
+      <c r="AT2">
+        <v>5.7</v>
+      </c>
+      <c r="AU2">
+        <v>6</v>
+      </c>
+      <c r="AV2">
+        <v>13.5</v>
+      </c>
+      <c r="AW2">
+        <v>2.98</v>
+      </c>
+      <c r="AX2">
+        <v>9.6</v>
+      </c>
+      <c r="AY2">
+        <v>9.4</v>
+      </c>
+      <c r="AZ2">
+        <v>16</v>
+      </c>
+      <c r="BA2">
+        <v>3</v>
+      </c>
+      <c r="BB2">
+        <v>24</v>
+      </c>
+      <c r="BC2">
+        <v>22</v>
+      </c>
+      <c r="BD2">
+        <v>2.96</v>
+      </c>
+      <c r="BE2">
+        <v>3.1</v>
+      </c>
+      <c r="BF2">
+        <v>19</v>
+      </c>
+      <c r="BG2">
+        <v>3</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -271,7 +271,7 @@
     <t>Deportivo Cali</t>
   </si>
   <si>
-    <t>2026-09-21 01:29:42</t>
+    <t>2026-09-21 03:39:58</t>
   </si>
 </sst>
 </file>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -271,7 +271,7 @@
     <t>Deportivo Cali</t>
   </si>
   <si>
-    <t>2026-09-21 03:39:58</t>
+    <t>2026-09-21 05:50:28</t>
   </si>
 </sst>
 </file>
@@ -895,10 +895,10 @@
         <v>1.47</v>
       </c>
       <c r="P2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q2">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R2">
         <v>1.18</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -271,7 +271,7 @@
     <t>Deportivo Cali</t>
   </si>
   <si>
-    <t>2026-09-21 05:50:28</t>
+    <t>2026-09-21 08:00:59</t>
   </si>
 </sst>
 </file>
@@ -895,7 +895,7 @@
         <v>1.47</v>
       </c>
       <c r="P2">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q2">
         <v>2.42</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -271,7 +271,7 @@
     <t>Deportivo Cali</t>
   </si>
   <si>
-    <t>2026-09-21 08:00:59</t>
+    <t>2026-09-21 10:12:17</t>
   </si>
 </sst>
 </file>
@@ -868,34 +868,34 @@
         <v>2.16</v>
       </c>
       <c r="G2">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="H2">
         <v>3.65</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P2">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q2">
         <v>2.42</v>
@@ -907,19 +907,19 @@
         <v>4.3</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="U2">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V2">
         <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2">
         <v>13.5</v>
@@ -928,10 +928,10 @@
         <v>32</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB2">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>8.800000000000001</v>
@@ -973,7 +973,7 @@
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AQ2">
         <v>9</v>
@@ -982,7 +982,7 @@
         <v>19</v>
       </c>
       <c r="AS2">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="AT2">
         <v>5.7</v>
@@ -994,7 +994,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="AX2">
         <v>9.6</v>
@@ -1006,25 +1006,25 @@
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="BB2">
-        <v>24</v>
+        <v>3.65</v>
       </c>
       <c r="BC2">
         <v>22</v>
       </c>
       <c r="BD2">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="BE2">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="BF2">
         <v>19</v>
       </c>
       <c r="BG2">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="BH2">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -271,7 +271,7 @@
     <t>Deportivo Cali</t>
   </si>
   <si>
-    <t>2026-09-21 10:12:17</t>
+    <t>2026-09-21 12:23:53</t>
   </si>
 </sst>
 </file>
@@ -865,16 +865,16 @@
         <v>84</v>
       </c>
       <c r="F2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="I2">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
         <v>3.15</v>
@@ -886,70 +886,70 @@
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N2">
         <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P2">
         <v>1.6</v>
       </c>
       <c r="Q2">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="T2">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X2">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB2">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE2">
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>100</v>
@@ -964,67 +964,67 @@
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AO2">
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2">
+        <v>8.4</v>
+      </c>
+      <c r="AS2">
+        <v>9.6</v>
+      </c>
+      <c r="AT2">
+        <v>6.8</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
+        <v>15</v>
+      </c>
+      <c r="AW2">
+        <v>10</v>
+      </c>
+      <c r="AX2">
+        <v>10.5</v>
+      </c>
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
         <v>19</v>
       </c>
-      <c r="AS2">
-        <v>3.85</v>
-      </c>
-      <c r="AT2">
-        <v>5.7</v>
-      </c>
-      <c r="AU2">
-        <v>6</v>
-      </c>
-      <c r="AV2">
-        <v>13.5</v>
-      </c>
-      <c r="AW2">
-        <v>3.85</v>
-      </c>
-      <c r="AX2">
-        <v>9.6</v>
-      </c>
-      <c r="AY2">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2">
-        <v>16</v>
-      </c>
       <c r="BA2">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="BB2">
-        <v>3.65</v>
+        <v>21</v>
       </c>
       <c r="BC2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD2">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="BE2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG2">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1033,7 +1033,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
@@ -1045,13 +1045,13 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
@@ -1063,13 +1063,13 @@
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW2">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -271,7 +271,7 @@
     <t>Deportivo Cali</t>
   </si>
   <si>
-    <t>2026-09-21 12:23:53</t>
+    <t>2026-09-21 14:35:42</t>
   </si>
 </sst>
 </file>
@@ -868,10 +868,10 @@
         <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I2">
         <v>4.2</v>
@@ -898,7 +898,7 @@
         <v>1.6</v>
       </c>
       <c r="Q2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R2">
         <v>1.22</v>
@@ -907,7 +907,7 @@
         <v>4.9</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
         <v>1.82</v>
@@ -919,7 +919,7 @@
         <v>1.76</v>
       </c>
       <c r="X2">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
         <v>11.5</v>
@@ -943,7 +943,7 @@
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -973,16 +973,16 @@
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2">
         <v>9.800000000000001</v>
       </c>
       <c r="AR2">
+        <v>7.2</v>
+      </c>
+      <c r="AS2">
         <v>8.4</v>
-      </c>
-      <c r="AS2">
-        <v>9.6</v>
       </c>
       <c r="AT2">
         <v>6.8</v>
@@ -994,7 +994,7 @@
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1006,7 +1006,7 @@
         <v>19</v>
       </c>
       <c r="BA2">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BB2">
         <v>21</v>
@@ -1015,76 +1015,76 @@
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2">
         <v>18.5</v>
       </c>
       <c r="BG2">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BN2">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BO2">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BP2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT2">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BV2">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="s">
         <v>85</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -271,7 +271,7 @@
     <t>Deportivo Cali</t>
   </si>
   <si>
-    <t>2026-09-21 14:35:42</t>
+    <t>2026-09-21 16:47:36</t>
   </si>
 </sst>
 </file>
@@ -865,7 +865,7 @@
         <v>84</v>
       </c>
       <c r="F2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
         <v>2.32</v>
@@ -874,7 +874,7 @@
         <v>3.9</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
         <v>3.15</v>
@@ -892,7 +892,7 @@
         <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P2">
         <v>1.6</v>
@@ -910,16 +910,16 @@
         <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
         <v>1.76</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2">
         <v>11.5</v>
@@ -928,7 +928,7 @@
         <v>38</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB2">
         <v>7.8</v>
@@ -943,7 +943,7 @@
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -973,16 +973,16 @@
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2">
         <v>9.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT2">
         <v>6.8</v>
@@ -1018,7 +1018,7 @@
         <v>8.6</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF2">
         <v>18.5</v>
@@ -1036,34 +1036,34 @@
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BN2">
         <v>5</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ2">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BT2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
         <v>6</v>
@@ -1072,19 +1072,19 @@
         <v>44</v>
       </c>
       <c r="BW2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BZ2">
         <v>48</v>
       </c>
       <c r="CA2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="s">
         <v>85</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
   <si>
     <t>League</t>
   </si>
@@ -259,19 +259,31 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Peruvian Primera Division</t>
+  </si>
+  <si>
     <t>2026-09-23</t>
   </si>
   <si>
     <t>01:00:00</t>
   </si>
   <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
     <t>Santa Fe</t>
   </si>
   <si>
+    <t>Asociacion Deportiva Tarma</t>
+  </si>
+  <si>
     <t>Deportivo Cali</t>
   </si>
   <si>
-    <t>2026-09-21 16:47:36</t>
+    <t>Cienciano</t>
+  </si>
+  <si>
+    <t>2026-09-21 19:13:49</t>
   </si>
 </sst>
 </file>
@@ -603,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -853,22 +865,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
         <v>3.9</v>
@@ -892,10 +904,10 @@
         <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q2">
         <v>2.44</v>
@@ -910,7 +922,7 @@
         <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V2">
         <v>1.32</v>
@@ -934,10 +946,10 @@
         <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
         <v>80</v>
@@ -964,7 +976,7 @@
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN2">
         <v>28</v>
@@ -988,7 +1000,7 @@
         <v>6.8</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>15</v>
@@ -1006,7 +1018,7 @@
         <v>19</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
         <v>21</v>
@@ -1024,7 +1036,7 @@
         <v>18.5</v>
       </c>
       <c r="BG2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
         <v>3.15</v>
@@ -1048,7 +1060,7 @@
         <v>5</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BP2">
         <v>22</v>
@@ -1087,7 +1099,249 @@
         <v>6.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>85</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3">
+        <v>3.25</v>
+      </c>
+      <c r="G3">
+        <v>3.6</v>
+      </c>
+      <c r="H3">
+        <v>2.22</v>
+      </c>
+      <c r="I3">
+        <v>2.36</v>
+      </c>
+      <c r="J3">
+        <v>3.7</v>
+      </c>
+      <c r="K3">
+        <v>4.2</v>
+      </c>
+      <c r="L3">
+        <v>1.3</v>
+      </c>
+      <c r="M3">
+        <v>1.04</v>
+      </c>
+      <c r="N3">
+        <v>4.1</v>
+      </c>
+      <c r="O3">
+        <v>1.26</v>
+      </c>
+      <c r="P3">
+        <v>2.08</v>
+      </c>
+      <c r="Q3">
+        <v>1.78</v>
+      </c>
+      <c r="R3">
+        <v>1.41</v>
+      </c>
+      <c r="S3">
+        <v>2.98</v>
+      </c>
+      <c r="T3">
+        <v>1.56</v>
+      </c>
+      <c r="U3">
+        <v>2.26</v>
+      </c>
+      <c r="V3">
+        <v>1.73</v>
+      </c>
+      <c r="W3">
+        <v>1.39</v>
+      </c>
+      <c r="X3">
+        <v>22</v>
+      </c>
+      <c r="Y3">
+        <v>13.5</v>
+      </c>
+      <c r="Z3">
+        <v>16</v>
+      </c>
+      <c r="AA3">
+        <v>36</v>
+      </c>
+      <c r="AB3">
+        <v>18</v>
+      </c>
+      <c r="AC3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>13.5</v>
+      </c>
+      <c r="AE3">
+        <v>28</v>
+      </c>
+      <c r="AF3">
+        <v>30</v>
+      </c>
+      <c r="AG3">
+        <v>17.5</v>
+      </c>
+      <c r="AH3">
+        <v>17.5</v>
+      </c>
+      <c r="AI3">
+        <v>34</v>
+      </c>
+      <c r="AJ3">
+        <v>70</v>
+      </c>
+      <c r="AK3">
+        <v>38</v>
+      </c>
+      <c r="AL3">
+        <v>55</v>
+      </c>
+      <c r="AM3">
+        <v>95</v>
+      </c>
+      <c r="AN3">
+        <v>36</v>
+      </c>
+      <c r="AO3">
+        <v>16</v>
+      </c>
+      <c r="AP3">
+        <v>13</v>
+      </c>
+      <c r="AQ3">
+        <v>8.4</v>
+      </c>
+      <c r="AR3">
+        <v>11.5</v>
+      </c>
+      <c r="AS3">
+        <v>21</v>
+      </c>
+      <c r="AT3">
+        <v>11</v>
+      </c>
+      <c r="AU3">
+        <v>7.6</v>
+      </c>
+      <c r="AV3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW3">
+        <v>16.5</v>
+      </c>
+      <c r="AX3">
+        <v>17.5</v>
+      </c>
+      <c r="AY3">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3">
+        <v>12</v>
+      </c>
+      <c r="BA3">
+        <v>1.03</v>
+      </c>
+      <c r="BB3">
+        <v>1.01</v>
+      </c>
+      <c r="BC3">
+        <v>1.03</v>
+      </c>
+      <c r="BD3">
+        <v>1.01</v>
+      </c>
+      <c r="BE3">
+        <v>1.01</v>
+      </c>
+      <c r="BF3">
+        <v>20</v>
+      </c>
+      <c r="BG3">
+        <v>11</v>
+      </c>
+      <c r="BH3">
+        <v>4.4</v>
+      </c>
+      <c r="BI3">
+        <v>2.96</v>
+      </c>
+      <c r="BJ3">
+        <v>9.4</v>
+      </c>
+      <c r="BK3">
+        <v>5.6</v>
+      </c>
+      <c r="BL3">
+        <v>120</v>
+      </c>
+      <c r="BM3">
+        <v>6.8</v>
+      </c>
+      <c r="BN3">
+        <v>7</v>
+      </c>
+      <c r="BO3">
+        <v>5.7</v>
+      </c>
+      <c r="BP3">
+        <v>26</v>
+      </c>
+      <c r="BQ3">
+        <v>5.7</v>
+      </c>
+      <c r="BR3">
+        <v>36</v>
+      </c>
+      <c r="BS3">
+        <v>6</v>
+      </c>
+      <c r="BT3">
+        <v>5.5</v>
+      </c>
+      <c r="BU3">
+        <v>4.6</v>
+      </c>
+      <c r="BV3">
+        <v>17</v>
+      </c>
+      <c r="BW3">
+        <v>5.1</v>
+      </c>
+      <c r="BX3">
+        <v>34</v>
+      </c>
+      <c r="BY3">
+        <v>6</v>
+      </c>
+      <c r="BZ3">
+        <v>23</v>
+      </c>
+      <c r="CA3">
+        <v>5.5</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -283,7 +283,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-21 19:13:49</t>
+    <t>2026-09-21 21:23:30</t>
   </si>
 </sst>
 </file>
@@ -889,7 +889,7 @@
         <v>4.1</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
         <v>3.35</v>
@@ -901,28 +901,28 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O2">
         <v>1.49</v>
       </c>
       <c r="P2">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q2">
         <v>2.44</v>
       </c>
       <c r="R2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T2">
         <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V2">
         <v>1.32</v>
@@ -985,13 +985,13 @@
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2">
         <v>9.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS2">
         <v>8.6</v>
@@ -1006,7 +1006,7 @@
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1027,7 +1027,7 @@
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE2">
         <v>9</v>
@@ -1060,7 +1060,7 @@
         <v>5</v>
       </c>
       <c r="BO2">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
         <v>22</v>
@@ -1119,7 +1119,7 @@
         <v>88</v>
       </c>
       <c r="F3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G3">
         <v>3.6</v>
@@ -1128,19 +1128,19 @@
         <v>2.22</v>
       </c>
       <c r="I3">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="J3">
         <v>3.7</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
         <v>4.1</v>
@@ -1164,13 +1164,13 @@
         <v>1.56</v>
       </c>
       <c r="U3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X3">
         <v>22</v>
@@ -1194,7 +1194,7 @@
         <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF3">
         <v>30</v>
@@ -1296,49 +1296,49 @@
         <v>120</v>
       </c>
       <c r="BM3">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BN3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BO3">
         <v>5.7</v>
       </c>
       <c r="BP3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BQ3">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="BR3">
         <v>36</v>
       </c>
       <c r="BS3">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BT3">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
         <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BW3">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BX3">
         <v>34</v>
       </c>
       <c r="BY3">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ3">
         <v>23</v>
       </c>
       <c r="CA3">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="CB3" t="s">
         <v>89</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -283,7 +283,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-21 21:23:30</t>
+    <t>2026-09-21 23:38:27</t>
   </si>
 </sst>
 </file>
@@ -880,22 +880,22 @@
         <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H2">
         <v>3.9</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
         <v>3.35</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M2">
         <v>1.11</v>
@@ -904,16 +904,16 @@
         <v>2.84</v>
       </c>
       <c r="O2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P2">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q2">
         <v>2.44</v>
       </c>
       <c r="R2">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
         <v>5</v>
@@ -922,13 +922,13 @@
         <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V2">
         <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X2">
         <v>11</v>
@@ -946,7 +946,7 @@
         <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD2">
         <v>17.5</v>
@@ -955,10 +955,10 @@
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -967,10 +967,10 @@
         <v>100</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL2">
         <v>75</v>
@@ -979,7 +979,7 @@
         <v>190</v>
       </c>
       <c r="AN2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO2">
         <v>100</v>
@@ -994,7 +994,7 @@
         <v>8</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2">
         <v>6.8</v>
@@ -1006,7 +1006,7 @@
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1018,7 +1018,7 @@
         <v>19</v>
       </c>
       <c r="BA2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB2">
         <v>21</v>
@@ -1027,10 +1027,10 @@
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2">
         <v>18.5</v>
@@ -1048,13 +1048,13 @@
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN2">
         <v>5</v>
@@ -1063,7 +1063,7 @@
         <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
         <v>5.5</v>
@@ -1119,22 +1119,22 @@
         <v>88</v>
       </c>
       <c r="F3">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="G3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="H3">
         <v>2.22</v>
       </c>
       <c r="I3">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="J3">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>1.35</v>
@@ -1146,31 +1146,31 @@
         <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q3">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
         <v>2.98</v>
       </c>
       <c r="T3">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W3">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X3">
         <v>22</v>
@@ -1185,7 +1185,7 @@
         <v>36</v>
       </c>
       <c r="AB3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC3">
         <v>9.199999999999999</v>
@@ -1197,10 +1197,10 @@
         <v>27</v>
       </c>
       <c r="AF3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH3">
         <v>17.5</v>
@@ -1212,7 +1212,7 @@
         <v>70</v>
       </c>
       <c r="AK3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL3">
         <v>55</v>
@@ -1221,52 +1221,52 @@
         <v>95</v>
       </c>
       <c r="AN3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO3">
         <v>16</v>
       </c>
       <c r="AP3">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
         <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
         <v>1.01</v>
@@ -1275,10 +1275,10 @@
         <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
         <v>4.4</v>
@@ -1287,16 +1287,16 @@
         <v>2.96</v>
       </c>
       <c r="BJ3">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
         <v>120</v>
       </c>
       <c r="BM3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BN3">
         <v>8</v>
@@ -1308,22 +1308,22 @@
         <v>30</v>
       </c>
       <c r="BQ3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR3">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU3">
         <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BW3">
         <v>4.1</v>
@@ -1332,13 +1332,13 @@
         <v>34</v>
       </c>
       <c r="BY3">
+        <v>4.6</v>
+      </c>
+      <c r="BZ3">
+        <v>27</v>
+      </c>
+      <c r="CA3">
         <v>4.5</v>
-      </c>
-      <c r="BZ3">
-        <v>23</v>
-      </c>
-      <c r="CA3">
-        <v>4.2</v>
       </c>
       <c r="CB3" t="s">
         <v>89</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -283,7 +283,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-21 23:38:27</t>
+    <t>2026-09-22 01:49:03</t>
   </si>
 </sst>
 </file>
@@ -880,7 +880,7 @@
         <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H2">
         <v>3.9</v>
@@ -889,124 +889,124 @@
         <v>4.2</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="O2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P2">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q2">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S2">
         <v>5</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB2">
         <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>100</v>
       </c>
       <c r="AJ2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AK2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AO2">
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AS2">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
         <v>6.8</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1015,88 +1015,88 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BB2">
+        <v>6.2</v>
+      </c>
+      <c r="BC2">
+        <v>6.2</v>
+      </c>
+      <c r="BD2">
+        <v>40</v>
+      </c>
+      <c r="BE2">
+        <v>7.2</v>
+      </c>
+      <c r="BF2">
         <v>21</v>
       </c>
-      <c r="BC2">
-        <v>21</v>
-      </c>
-      <c r="BD2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF2">
-        <v>18.5</v>
-      </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BH2">
         <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BN2">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BP2">
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2">
         <v>6</v>
       </c>
       <c r="BV2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW2">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX2">
         <v>65</v>
       </c>
       <c r="BY2">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ2">
         <v>48</v>
       </c>
       <c r="CA2">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1119,22 +1119,22 @@
         <v>88</v>
       </c>
       <c r="F3">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H3">
         <v>2.22</v>
       </c>
       <c r="I3">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
         <v>1.35</v>
@@ -1161,16 +1161,16 @@
         <v>2.98</v>
       </c>
       <c r="T3">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V3">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W3">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X3">
         <v>22</v>
@@ -1221,64 +1221,64 @@
         <v>95</v>
       </c>
       <c r="AN3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO3">
         <v>16</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH3">
         <v>4.4</v>
@@ -1314,7 +1314,7 @@
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT3">
         <v>5.5</v>
@@ -1323,10 +1323,10 @@
         <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BW3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BX3">
         <v>34</v>
@@ -1335,10 +1335,10 @@
         <v>4.6</v>
       </c>
       <c r="BZ3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="CA3">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="CB3" t="s">
         <v>89</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -283,7 +283,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-22 01:49:03</t>
+    <t>2026-09-22 03:59:47</t>
   </si>
 </sst>
 </file>
@@ -892,7 +892,7 @@
         <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L2">
         <v>1.53</v>
@@ -901,16 +901,16 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P2">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q2">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R2">
         <v>1.23</v>
@@ -931,7 +931,7 @@
         <v>1.8</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y2">
         <v>13</v>
@@ -955,10 +955,10 @@
         <v>85</v>
       </c>
       <c r="AF2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>27</v>
@@ -985,7 +985,7 @@
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
         <v>10</v>
@@ -994,7 +994,7 @@
         <v>22</v>
       </c>
       <c r="AS2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT2">
         <v>6.8</v>
@@ -1018,85 +1018,85 @@
         <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD2">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2">
         <v>21</v>
       </c>
       <c r="BG2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH2">
         <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BO2">
         <v>3.85</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BQ2">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BR2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BS2">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BT2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
         <v>6</v>
       </c>
       <c r="BV2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BX2">
         <v>65</v>
       </c>
       <c r="BY2">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="CA2">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1119,7 +1119,7 @@
         <v>88</v>
       </c>
       <c r="F3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G3">
         <v>3.6</v>
@@ -1128,13 +1128,13 @@
         <v>2.22</v>
       </c>
       <c r="I3">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J3">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3">
         <v>1.35</v>
@@ -1146,13 +1146,13 @@
         <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3">
         <v>2.1</v>
       </c>
       <c r="Q3">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R3">
         <v>1.4</v>
@@ -1161,10 +1161,10 @@
         <v>2.98</v>
       </c>
       <c r="T3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
         <v>1.74</v>
@@ -1185,7 +1185,7 @@
         <v>36</v>
       </c>
       <c r="AB3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC3">
         <v>9.199999999999999</v>
@@ -1197,10 +1197,10 @@
         <v>27</v>
       </c>
       <c r="AF3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH3">
         <v>17.5</v>
@@ -1212,7 +1212,7 @@
         <v>70</v>
       </c>
       <c r="AK3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL3">
         <v>55</v>
@@ -1236,13 +1236,13 @@
         <v>11</v>
       </c>
       <c r="AS3">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AT3">
         <v>11</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
         <v>9.4</v>
@@ -1251,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="AX3">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
@@ -1260,22 +1260,22 @@
         <v>12</v>
       </c>
       <c r="BA3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE3">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG3">
         <v>11</v>
@@ -1296,7 +1296,7 @@
         <v>120</v>
       </c>
       <c r="BM3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BN3">
         <v>8</v>
@@ -1308,10 +1308,10 @@
         <v>30</v>
       </c>
       <c r="BQ3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BS3">
         <v>4.7</v>
@@ -1332,13 +1332,13 @@
         <v>34</v>
       </c>
       <c r="BY3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ3">
         <v>23</v>
       </c>
       <c r="CA3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="s">
         <v>89</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -283,7 +283,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-22 03:59:47</t>
+    <t>2026-09-22 06:10:38</t>
   </si>
 </sst>
 </file>
@@ -880,10 +880,10 @@
         <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I2">
         <v>4.2</v>
@@ -892,49 +892,49 @@
         <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
         <v>2.98</v>
       </c>
       <c r="O2">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R2">
         <v>1.23</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="V2">
         <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z2">
         <v>32</v>
@@ -961,7 +961,7 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI2">
         <v>100</v>
@@ -970,22 +970,22 @@
         <v>42</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AL2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AO2">
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AQ2">
         <v>10</v>
@@ -1012,10 +1012,10 @@
         <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA2">
         <v>7.8</v>
@@ -1027,13 +1027,13 @@
         <v>6.6</v>
       </c>
       <c r="BD2">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BE2">
         <v>8.199999999999999</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BG2">
         <v>7.8</v>
@@ -1042,10 +1042,10 @@
         <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
         <v>8.6</v>
@@ -1054,7 +1054,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BN2">
         <v>5</v>
@@ -1063,16 +1063,16 @@
         <v>3.85</v>
       </c>
       <c r="BP2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT2">
         <v>7.4</v>
@@ -1084,19 +1084,19 @@
         <v>40</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX2">
         <v>65</v>
       </c>
       <c r="BY2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ2">
+        <v>40</v>
+      </c>
+      <c r="CA2">
         <v>7.6</v>
-      </c>
-      <c r="BZ2">
-        <v>42</v>
-      </c>
-      <c r="CA2">
-        <v>7.2</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1119,22 +1119,22 @@
         <v>88</v>
       </c>
       <c r="F3">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G3">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H3">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I3">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>1.35</v>
@@ -1143,49 +1143,49 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
         <v>1.26</v>
       </c>
       <c r="P3">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
         <v>1.77</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="W3">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X3">
         <v>22</v>
       </c>
       <c r="Y3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB3">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AC3">
         <v>9.199999999999999</v>
@@ -1194,91 +1194,91 @@
         <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG3">
+        <v>17</v>
+      </c>
+      <c r="AH3">
+        <v>17</v>
+      </c>
+      <c r="AI3">
+        <v>36</v>
+      </c>
+      <c r="AJ3">
+        <v>65</v>
+      </c>
+      <c r="AK3">
+        <v>36</v>
+      </c>
+      <c r="AL3">
+        <v>50</v>
+      </c>
+      <c r="AM3">
+        <v>90</v>
+      </c>
+      <c r="AN3">
+        <v>34</v>
+      </c>
+      <c r="AO3">
+        <v>17</v>
+      </c>
+      <c r="AP3">
+        <v>4.4</v>
+      </c>
+      <c r="AQ3">
+        <v>10</v>
+      </c>
+      <c r="AR3">
+        <v>4.2</v>
+      </c>
+      <c r="AS3">
+        <v>4.7</v>
+      </c>
+      <c r="AT3">
+        <v>10.5</v>
+      </c>
+      <c r="AU3">
+        <v>7.4</v>
+      </c>
+      <c r="AV3">
+        <v>3.95</v>
+      </c>
+      <c r="AW3">
+        <v>17</v>
+      </c>
+      <c r="AX3">
         <v>17.5</v>
-      </c>
-      <c r="AH3">
-        <v>17.5</v>
-      </c>
-      <c r="AI3">
-        <v>34</v>
-      </c>
-      <c r="AJ3">
-        <v>70</v>
-      </c>
-      <c r="AK3">
-        <v>38</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
-        <v>95</v>
-      </c>
-      <c r="AN3">
-        <v>32</v>
-      </c>
-      <c r="AO3">
-        <v>16</v>
-      </c>
-      <c r="AP3">
-        <v>13</v>
-      </c>
-      <c r="AQ3">
-        <v>9.4</v>
-      </c>
-      <c r="AR3">
-        <v>11</v>
-      </c>
-      <c r="AS3">
-        <v>21</v>
-      </c>
-      <c r="AT3">
-        <v>11</v>
-      </c>
-      <c r="AU3">
-        <v>7.6</v>
-      </c>
-      <c r="AV3">
-        <v>9.4</v>
-      </c>
-      <c r="AW3">
-        <v>16</v>
-      </c>
-      <c r="AX3">
-        <v>18</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="BA3">
+        <v>4.8</v>
+      </c>
+      <c r="BB3">
         <v>5.1</v>
       </c>
-      <c r="BB3">
-        <v>5.5</v>
-      </c>
       <c r="BC3">
+        <v>4.8</v>
+      </c>
+      <c r="BD3">
+        <v>5</v>
+      </c>
+      <c r="BE3">
         <v>5.2</v>
       </c>
-      <c r="BD3">
-        <v>5.4</v>
-      </c>
-      <c r="BE3">
-        <v>5.6</v>
-      </c>
       <c r="BF3">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BH3">
         <v>4.4</v>
@@ -1290,55 +1290,55 @@
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL3">
         <v>120</v>
       </c>
       <c r="BM3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BN3">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BO3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS3">
+        <v>4.9</v>
+      </c>
+      <c r="BT3">
+        <v>6.4</v>
+      </c>
+      <c r="BU3">
         <v>4.7</v>
       </c>
-      <c r="BT3">
-        <v>5.5</v>
-      </c>
-      <c r="BU3">
-        <v>4.6</v>
-      </c>
       <c r="BV3">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX3">
         <v>34</v>
       </c>
       <c r="BY3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BZ3">
         <v>23</v>
       </c>
       <c r="CA3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB3" t="s">
         <v>89</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -283,7 +283,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-22 06:10:38</t>
+    <t>2026-09-22 08:21:15</t>
   </si>
 </sst>
 </file>
@@ -877,22 +877,22 @@
         <v>87</v>
       </c>
       <c r="F2">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G2">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
         <v>1.51</v>
@@ -901,10 +901,10 @@
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P2">
         <v>1.66</v>
@@ -919,37 +919,37 @@
         <v>4.9</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="X2">
         <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE2">
         <v>85</v>
@@ -961,7 +961,7 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2">
         <v>100</v>
@@ -979,55 +979,55 @@
         <v>180</v>
       </c>
       <c r="AN2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO2">
         <v>100</v>
       </c>
       <c r="AP2">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AS2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW2">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
         <v>19</v>
       </c>
       <c r="BA2">
+        <v>8.4</v>
+      </c>
+      <c r="BB2">
+        <v>7</v>
+      </c>
+      <c r="BC2">
+        <v>7</v>
+      </c>
+      <c r="BD2">
         <v>7.8</v>
-      </c>
-      <c r="BB2">
-        <v>6.6</v>
-      </c>
-      <c r="BC2">
-        <v>6.6</v>
-      </c>
-      <c r="BD2">
-        <v>40</v>
       </c>
       <c r="BE2">
         <v>8.199999999999999</v>
@@ -1036,67 +1036,67 @@
         <v>18.5</v>
       </c>
       <c r="BG2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BN2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BR2">
+        <v>40</v>
+      </c>
+      <c r="BS2">
+        <v>7</v>
+      </c>
+      <c r="BT2">
+        <v>7.2</v>
+      </c>
+      <c r="BU2">
+        <v>4.8</v>
+      </c>
+      <c r="BV2">
         <v>38</v>
       </c>
-      <c r="BS2">
-        <v>7.6</v>
-      </c>
-      <c r="BT2">
-        <v>7.4</v>
-      </c>
-      <c r="BU2">
-        <v>6</v>
-      </c>
-      <c r="BV2">
-        <v>40</v>
-      </c>
       <c r="BW2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY2">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="CA2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1122,22 +1122,22 @@
         <v>3.15</v>
       </c>
       <c r="G3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
         <v>2.24</v>
       </c>
       <c r="I3">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="J3">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L3">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M3">
         <v>1.05</v>
@@ -1146,16 +1146,16 @@
         <v>4.2</v>
       </c>
       <c r="O3">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3">
         <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
         <v>2.96</v>
@@ -1167,13 +1167,13 @@
         <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y3">
         <v>14</v>
@@ -1200,7 +1200,7 @@
         <v>29</v>
       </c>
       <c r="AG3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH3">
         <v>17</v>
@@ -1215,10 +1215,10 @@
         <v>36</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN3">
         <v>34</v>
@@ -1227,16 +1227,16 @@
         <v>17</v>
       </c>
       <c r="AP3">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="AQ3">
         <v>10</v>
       </c>
       <c r="AR3">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT3">
         <v>10.5</v>
@@ -1245,7 +1245,7 @@
         <v>7.4</v>
       </c>
       <c r="AV3">
-        <v>3.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW3">
         <v>17</v>
@@ -1257,28 +1257,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG3">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="BH3">
         <v>4.4</v>
@@ -1290,7 +1290,7 @@
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="BL3">
         <v>120</v>
@@ -1320,7 +1320,7 @@
         <v>6.4</v>
       </c>
       <c r="BU3">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV3">
         <v>17.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="106">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,12 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Nigerian Premier League</t>
+  </si>
+  <si>
+    <t>US United Soccer League</t>
+  </si>
+  <si>
     <t>Peruvian Primera Division</t>
   </si>
   <si>
@@ -268,22 +274,64 @@
     <t>01:00:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>20:00:00</t>
   </si>
   <si>
     <t>Santa Fe</t>
   </si>
   <si>
+    <t>Enugu Rangers International</t>
+  </si>
+  <si>
+    <t>Enyimba</t>
+  </si>
+  <si>
+    <t>Shooting Stars</t>
+  </si>
+  <si>
+    <t>Inter Lagos FC</t>
+  </si>
+  <si>
+    <t>Barau FC</t>
+  </si>
+  <si>
+    <t>Birmingham Legion FC</t>
+  </si>
+  <si>
     <t>Asociacion Deportiva Tarma</t>
   </si>
   <si>
     <t>Deportivo Cali</t>
   </si>
   <si>
+    <t>Ranchers Bees FC</t>
+  </si>
+  <si>
+    <t>Sporting Lagos FC</t>
+  </si>
+  <si>
+    <t>Katsina United</t>
+  </si>
+  <si>
+    <t>Kano Pillars FC</t>
+  </si>
+  <si>
+    <t>Abia Warriors</t>
+  </si>
+  <si>
+    <t>Brooklyn FC</t>
+  </si>
+  <si>
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-22 08:21:15</t>
+    <t>2026-09-22 10:55:09</t>
   </si>
 </sst>
 </file>
@@ -615,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -865,16 +913,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F2">
         <v>2.24</v>
@@ -883,19 +931,19 @@
         <v>2.3</v>
       </c>
       <c r="H2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
         <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M2">
         <v>1.1</v>
@@ -907,10 +955,10 @@
         <v>1.47</v>
       </c>
       <c r="P2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q2">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R2">
         <v>1.23</v>
@@ -919,7 +967,7 @@
         <v>4.9</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
         <v>1.9</v>
@@ -931,49 +979,49 @@
         <v>1.76</v>
       </c>
       <c r="X2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
         <v>17</v>
       </c>
       <c r="AE2">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AF2">
         <v>13</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
         <v>23</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ2">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AK2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2">
         <v>180</v>
@@ -982,61 +1030,61 @@
         <v>28</v>
       </c>
       <c r="AO2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP2">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AS2">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="AX2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="BB2">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BC2">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="BD2">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BE2">
-        <v>8.199999999999999</v>
+        <v>110</v>
       </c>
       <c r="BF2">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="BH2">
         <v>3.25</v>
@@ -1045,61 +1093,61 @@
         <v>2.44</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BO2">
         <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY2">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BZ2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1107,241 +1155,1693 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3">
+        <v>1.15</v>
+      </c>
+      <c r="G3">
+        <v>2.38</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>1000</v>
+      </c>
+      <c r="J3">
+        <v>3.05</v>
+      </c>
+      <c r="K3">
+        <v>950</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>1.12</v>
+      </c>
+      <c r="O3">
+        <v>1.38</v>
+      </c>
+      <c r="P3">
+        <v>1.12</v>
+      </c>
+      <c r="Q3">
+        <v>1.4</v>
+      </c>
+      <c r="R3">
+        <v>1.08</v>
+      </c>
+      <c r="S3">
+        <v>2.1</v>
+      </c>
+      <c r="T3">
+        <v>1.01</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
+        <v>1.01</v>
+      </c>
+      <c r="W3">
+        <v>1.73</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3">
+        <v>1.03</v>
+      </c>
+      <c r="AR3">
+        <v>1.03</v>
+      </c>
+      <c r="AS3">
+        <v>1.03</v>
+      </c>
+      <c r="AT3">
+        <v>1.03</v>
+      </c>
+      <c r="AU3">
+        <v>1.03</v>
+      </c>
+      <c r="AV3">
+        <v>1.03</v>
+      </c>
+      <c r="AW3">
+        <v>1.03</v>
+      </c>
+      <c r="AX3">
+        <v>1.03</v>
+      </c>
+      <c r="AY3">
+        <v>1.03</v>
+      </c>
+      <c r="AZ3">
+        <v>1.03</v>
+      </c>
+      <c r="BA3">
+        <v>1.03</v>
+      </c>
+      <c r="BB3">
+        <v>1.03</v>
+      </c>
+      <c r="BC3">
+        <v>1.03</v>
+      </c>
+      <c r="BD3">
+        <v>1.03</v>
+      </c>
+      <c r="BE3">
+        <v>1.03</v>
+      </c>
+      <c r="BF3">
+        <v>1.01</v>
+      </c>
+      <c r="BG3">
+        <v>1.01</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4">
+        <v>1.1</v>
+      </c>
+      <c r="G4">
+        <v>1000</v>
+      </c>
+      <c r="H4">
+        <v>1.1</v>
+      </c>
+      <c r="I4">
+        <v>1000</v>
+      </c>
+      <c r="J4">
+        <v>1.1</v>
+      </c>
+      <c r="K4">
+        <v>870</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>1.1</v>
+      </c>
+      <c r="O4">
+        <v>1.01</v>
+      </c>
+      <c r="P4">
+        <v>1.1</v>
+      </c>
+      <c r="Q4">
+        <v>1.01</v>
+      </c>
+      <c r="R4">
+        <v>1.08</v>
+      </c>
+      <c r="S4">
+        <v>1.52</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.01</v>
+      </c>
+      <c r="W4">
+        <v>1.01</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4">
+        <v>1.01</v>
+      </c>
+      <c r="AR4">
+        <v>1.01</v>
+      </c>
+      <c r="AS4">
+        <v>1.01</v>
+      </c>
+      <c r="AT4">
+        <v>1.01</v>
+      </c>
+      <c r="AU4">
+        <v>1.01</v>
+      </c>
+      <c r="AV4">
+        <v>1.01</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>1.01</v>
+      </c>
+      <c r="AY4">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>1.01</v>
+      </c>
+      <c r="BB4">
+        <v>1.01</v>
+      </c>
+      <c r="BC4">
+        <v>1.01</v>
+      </c>
+      <c r="BD4">
+        <v>1.01</v>
+      </c>
+      <c r="BE4">
+        <v>1.01</v>
+      </c>
+      <c r="BF4">
+        <v>1.01</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>1.3</v>
+      </c>
+      <c r="G5">
+        <v>3.05</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>1000</v>
+      </c>
+      <c r="J5">
+        <v>2.98</v>
+      </c>
+      <c r="K5">
+        <v>950</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>1.12</v>
+      </c>
+      <c r="O5">
+        <v>1.43</v>
+      </c>
+      <c r="P5">
+        <v>1.12</v>
+      </c>
+      <c r="Q5">
+        <v>1.51</v>
+      </c>
+      <c r="R5">
+        <v>1.08</v>
+      </c>
+      <c r="S5">
+        <v>1.52</v>
+      </c>
+      <c r="T5">
+        <v>1.01</v>
+      </c>
+      <c r="U5">
+        <v>1.01</v>
+      </c>
+      <c r="V5">
+        <v>1.01</v>
+      </c>
+      <c r="W5">
+        <v>1.49</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5">
+        <v>1.03</v>
+      </c>
+      <c r="AR5">
+        <v>1.03</v>
+      </c>
+      <c r="AS5">
+        <v>1.03</v>
+      </c>
+      <c r="AT5">
+        <v>1.03</v>
+      </c>
+      <c r="AU5">
+        <v>1.03</v>
+      </c>
+      <c r="AV5">
+        <v>1.03</v>
+      </c>
+      <c r="AW5">
+        <v>1.03</v>
+      </c>
+      <c r="AX5">
+        <v>1.03</v>
+      </c>
+      <c r="AY5">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5">
+        <v>1.03</v>
+      </c>
+      <c r="BA5">
+        <v>1.03</v>
+      </c>
+      <c r="BB5">
+        <v>1.03</v>
+      </c>
+      <c r="BC5">
+        <v>1.03</v>
+      </c>
+      <c r="BD5">
+        <v>1.03</v>
+      </c>
+      <c r="BE5">
+        <v>1.03</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6">
+        <v>1.1</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>1.1</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1.1</v>
+      </c>
+      <c r="K6">
+        <v>870</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>1.1</v>
+      </c>
+      <c r="O6">
+        <v>1.01</v>
+      </c>
+      <c r="P6">
+        <v>1.1</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>1.08</v>
+      </c>
+      <c r="S6">
+        <v>1.46</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.01</v>
+      </c>
+      <c r="W6">
+        <v>1.01</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6">
+        <v>1.01</v>
+      </c>
+      <c r="AR6">
+        <v>1.01</v>
+      </c>
+      <c r="AS6">
+        <v>1.01</v>
+      </c>
+      <c r="AT6">
+        <v>1.01</v>
+      </c>
+      <c r="AU6">
+        <v>1.01</v>
+      </c>
+      <c r="AV6">
+        <v>1.01</v>
+      </c>
+      <c r="AW6">
+        <v>1.01</v>
+      </c>
+      <c r="AX6">
+        <v>1.01</v>
+      </c>
+      <c r="AY6">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6">
+        <v>1.01</v>
+      </c>
+      <c r="BA6">
+        <v>1.01</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7">
+        <v>1.1</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>1.1</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.1</v>
+      </c>
+      <c r="K7">
+        <v>900</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>1.1</v>
+      </c>
+      <c r="O7">
+        <v>1.01</v>
+      </c>
+      <c r="P7">
+        <v>1.1</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>1.08</v>
+      </c>
+      <c r="S7">
+        <v>1.53</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7">
+        <v>1.01</v>
+      </c>
+      <c r="AR7">
+        <v>1.01</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>1.01</v>
+      </c>
+      <c r="AU7">
+        <v>1.01</v>
+      </c>
+      <c r="AV7">
+        <v>1.01</v>
+      </c>
+      <c r="AW7">
+        <v>1.01</v>
+      </c>
+      <c r="AX7">
+        <v>1.01</v>
+      </c>
+      <c r="AY7">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7">
+        <v>1.01</v>
+      </c>
+      <c r="BA7">
+        <v>1.01</v>
+      </c>
+      <c r="BB7">
+        <v>1.01</v>
+      </c>
+      <c r="BC7">
+        <v>1.01</v>
+      </c>
+      <c r="BD7">
+        <v>1.01</v>
+      </c>
+      <c r="BE7">
+        <v>1.01</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.01</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.01</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
         <v>82</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B8" t="s">
         <v>84</v>
       </c>
-      <c r="D3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8">
+        <v>1.81</v>
+      </c>
+      <c r="G8">
+        <v>1.91</v>
+      </c>
+      <c r="H8">
+        <v>4.3</v>
+      </c>
+      <c r="I8">
+        <v>4.6</v>
+      </c>
+      <c r="J8">
+        <v>4.1</v>
+      </c>
+      <c r="K8">
+        <v>4.6</v>
+      </c>
+      <c r="L8">
+        <v>1.23</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>5.7</v>
+      </c>
+      <c r="O8">
+        <v>1.18</v>
+      </c>
+      <c r="P8">
+        <v>2.62</v>
+      </c>
+      <c r="Q8">
+        <v>1.54</v>
+      </c>
+      <c r="R8">
+        <v>1.66</v>
+      </c>
+      <c r="S8">
+        <v>2.34</v>
+      </c>
+      <c r="T8">
+        <v>1.54</v>
+      </c>
+      <c r="U8">
+        <v>2.62</v>
+      </c>
+      <c r="V8">
+        <v>1.28</v>
+      </c>
+      <c r="W8">
+        <v>2.1</v>
+      </c>
+      <c r="X8">
+        <v>32</v>
+      </c>
+      <c r="Y8">
+        <v>26</v>
+      </c>
+      <c r="Z8">
+        <v>55</v>
+      </c>
+      <c r="AA8">
+        <v>110</v>
+      </c>
+      <c r="AB8">
+        <v>16</v>
+      </c>
+      <c r="AC8">
+        <v>12</v>
+      </c>
+      <c r="AD8">
+        <v>20</v>
+      </c>
+      <c r="AE8">
+        <v>60</v>
+      </c>
+      <c r="AF8">
+        <v>16.5</v>
+      </c>
+      <c r="AG8">
+        <v>12.5</v>
+      </c>
+      <c r="AH8">
+        <v>18</v>
+      </c>
+      <c r="AI8">
+        <v>46</v>
+      </c>
+      <c r="AJ8">
+        <v>26</v>
+      </c>
+      <c r="AK8">
+        <v>19</v>
+      </c>
+      <c r="AL8">
+        <v>28</v>
+      </c>
+      <c r="AM8">
+        <v>65</v>
+      </c>
+      <c r="AN8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO8">
+        <v>40</v>
+      </c>
+      <c r="AP8">
+        <v>20</v>
+      </c>
+      <c r="AQ8">
+        <v>17</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>12</v>
+      </c>
+      <c r="AU8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV8">
+        <v>14.5</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>12.5</v>
+      </c>
+      <c r="AY8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8">
+        <v>13</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>17</v>
+      </c>
+      <c r="BC8">
+        <v>14</v>
+      </c>
+      <c r="BD8">
+        <v>18.5</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>7</v>
+      </c>
+      <c r="BG8">
+        <v>26</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
         <v>88</v>
       </c>
-      <c r="F3">
-        <v>3.15</v>
-      </c>
-      <c r="G3">
-        <v>3.45</v>
-      </c>
-      <c r="H3">
+      <c r="D9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9">
+        <v>3.1</v>
+      </c>
+      <c r="G9">
+        <v>3.4</v>
+      </c>
+      <c r="H9">
         <v>2.24</v>
       </c>
-      <c r="I3">
+      <c r="I9">
         <v>2.4</v>
       </c>
-      <c r="J3">
+      <c r="J9">
         <v>3.65</v>
       </c>
-      <c r="K3">
-        <v>3.95</v>
-      </c>
-      <c r="L3">
+      <c r="K9">
+        <v>4.1</v>
+      </c>
+      <c r="L9">
         <v>1.3</v>
       </c>
-      <c r="M3">
+      <c r="M9">
         <v>1.05</v>
       </c>
-      <c r="N3">
+      <c r="N9">
         <v>4.2</v>
       </c>
-      <c r="O3">
+      <c r="O9">
         <v>1.25</v>
       </c>
-      <c r="P3">
-        <v>2.06</v>
-      </c>
-      <c r="Q3">
-        <v>1.75</v>
-      </c>
-      <c r="R3">
-        <v>1.4</v>
-      </c>
-      <c r="S3">
+      <c r="P9">
+        <v>2.1</v>
+      </c>
+      <c r="Q9">
+        <v>1.74</v>
+      </c>
+      <c r="R9">
+        <v>1.39</v>
+      </c>
+      <c r="S9">
         <v>2.96</v>
       </c>
-      <c r="T3">
-        <v>1.55</v>
-      </c>
-      <c r="U3">
-        <v>2.06</v>
-      </c>
-      <c r="V3">
+      <c r="T9">
+        <v>1.56</v>
+      </c>
+      <c r="U9">
+        <v>2.28</v>
+      </c>
+      <c r="V9">
         <v>1.71</v>
       </c>
-      <c r="W3">
-        <v>1.4</v>
-      </c>
-      <c r="X3">
+      <c r="W9">
+        <v>1.41</v>
+      </c>
+      <c r="X9">
         <v>18.5</v>
       </c>
-      <c r="Y3">
+      <c r="Y9">
         <v>14</v>
       </c>
-      <c r="Z3">
+      <c r="Z9">
         <v>17</v>
       </c>
-      <c r="AA3">
+      <c r="AA9">
         <v>32</v>
       </c>
-      <c r="AB3">
+      <c r="AB9">
         <v>18</v>
       </c>
-      <c r="AC3">
+      <c r="AC9">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD3">
+      <c r="AD9">
         <v>13.5</v>
       </c>
-      <c r="AE3">
+      <c r="AE9">
         <v>29</v>
       </c>
-      <c r="AF3">
+      <c r="AF9">
         <v>29</v>
       </c>
-      <c r="AG3">
+      <c r="AG9">
         <v>17.5</v>
       </c>
-      <c r="AH3">
+      <c r="AH9">
         <v>17</v>
       </c>
-      <c r="AI3">
+      <c r="AI9">
         <v>36</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ9">
         <v>65</v>
       </c>
-      <c r="AK3">
+      <c r="AK9">
         <v>36</v>
       </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
+      <c r="AL9">
+        <v>50</v>
+      </c>
+      <c r="AM9">
         <v>95</v>
       </c>
-      <c r="AN3">
+      <c r="AN9">
         <v>34</v>
       </c>
-      <c r="AO3">
+      <c r="AO9">
+        <v>16.5</v>
+      </c>
+      <c r="AP9">
+        <v>12.5</v>
+      </c>
+      <c r="AQ9">
+        <v>10</v>
+      </c>
+      <c r="AR9">
+        <v>11.5</v>
+      </c>
+      <c r="AS9">
+        <v>5</v>
+      </c>
+      <c r="AT9">
+        <v>10.5</v>
+      </c>
+      <c r="AU9">
+        <v>6.4</v>
+      </c>
+      <c r="AV9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW9">
         <v>17</v>
       </c>
-      <c r="AP3">
-        <v>15</v>
-      </c>
-      <c r="AQ3">
-        <v>10</v>
-      </c>
-      <c r="AR3">
-        <v>13.5</v>
-      </c>
-      <c r="AS3">
-        <v>4.8</v>
-      </c>
-      <c r="AT3">
+      <c r="AX9">
+        <v>17.5</v>
+      </c>
+      <c r="AY9">
         <v>10.5</v>
       </c>
-      <c r="AU3">
-        <v>7.4</v>
-      </c>
-      <c r="AV3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW3">
-        <v>17</v>
-      </c>
-      <c r="AX3">
+      <c r="AZ9">
+        <v>12</v>
+      </c>
+      <c r="BA9">
+        <v>5</v>
+      </c>
+      <c r="BB9">
+        <v>5.4</v>
+      </c>
+      <c r="BC9">
+        <v>5</v>
+      </c>
+      <c r="BD9">
+        <v>5.3</v>
+      </c>
+      <c r="BE9">
+        <v>5.5</v>
+      </c>
+      <c r="BF9">
+        <v>20</v>
+      </c>
+      <c r="BG9">
+        <v>11.5</v>
+      </c>
+      <c r="BH9">
+        <v>4.4</v>
+      </c>
+      <c r="BI9">
+        <v>2.96</v>
+      </c>
+      <c r="BJ9">
+        <v>11</v>
+      </c>
+      <c r="BK9">
+        <v>3.8</v>
+      </c>
+      <c r="BL9">
+        <v>120</v>
+      </c>
+      <c r="BM9">
+        <v>5.5</v>
+      </c>
+      <c r="BN9">
+        <v>6.8</v>
+      </c>
+      <c r="BO9">
+        <v>5.6</v>
+      </c>
+      <c r="BP9">
+        <v>25</v>
+      </c>
+      <c r="BQ9">
+        <v>4.7</v>
+      </c>
+      <c r="BR9">
+        <v>34</v>
+      </c>
+      <c r="BS9">
+        <v>4.9</v>
+      </c>
+      <c r="BT9">
+        <v>6.4</v>
+      </c>
+      <c r="BU9">
+        <v>4.1</v>
+      </c>
+      <c r="BV9">
         <v>17.5</v>
       </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
-        <v>13.5</v>
-      </c>
-      <c r="BA3">
+      <c r="BW9">
+        <v>4.3</v>
+      </c>
+      <c r="BX9">
+        <v>34</v>
+      </c>
+      <c r="BY9">
         <v>4.9</v>
       </c>
-      <c r="BB3">
-        <v>5.2</v>
-      </c>
-      <c r="BC3">
-        <v>4.9</v>
-      </c>
-      <c r="BD3">
-        <v>5.2</v>
-      </c>
-      <c r="BE3">
-        <v>5.4</v>
-      </c>
-      <c r="BF3">
-        <v>4.9</v>
-      </c>
-      <c r="BG3">
-        <v>13.5</v>
-      </c>
-      <c r="BH3">
-        <v>4.4</v>
-      </c>
-      <c r="BI3">
-        <v>2.96</v>
-      </c>
-      <c r="BJ3">
-        <v>11</v>
-      </c>
-      <c r="BK3">
-        <v>3.8</v>
-      </c>
-      <c r="BL3">
-        <v>120</v>
-      </c>
-      <c r="BM3">
-        <v>5.5</v>
-      </c>
-      <c r="BN3">
-        <v>6.8</v>
-      </c>
-      <c r="BO3">
-        <v>5.6</v>
-      </c>
-      <c r="BP3">
-        <v>25</v>
-      </c>
-      <c r="BQ3">
-        <v>4.7</v>
-      </c>
-      <c r="BR3">
-        <v>34</v>
-      </c>
-      <c r="BS3">
-        <v>4.9</v>
-      </c>
-      <c r="BT3">
-        <v>6.4</v>
-      </c>
-      <c r="BU3">
-        <v>4.1</v>
-      </c>
-      <c r="BV3">
-        <v>17.5</v>
-      </c>
-      <c r="BW3">
-        <v>4.3</v>
-      </c>
-      <c r="BX3">
-        <v>34</v>
-      </c>
-      <c r="BY3">
-        <v>4.9</v>
-      </c>
-      <c r="BZ3">
+      <c r="BZ9">
         <v>23</v>
       </c>
-      <c r="CA3">
+      <c r="CA9">
         <v>4.6</v>
       </c>
-      <c r="CB3" t="s">
-        <v>89</v>
+      <c r="CB9" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -331,7 +331,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-22 10:55:09</t>
+    <t>2026-09-22 13:07:11</t>
   </si>
 </sst>
 </file>
@@ -925,22 +925,22 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G2">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H2">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
         <v>1.52</v>
@@ -955,13 +955,13 @@
         <v>1.47</v>
       </c>
       <c r="P2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
         <v>4.9</v>
@@ -973,10 +973,10 @@
         <v>1.9</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X2">
         <v>10.5</v>
@@ -988,22 +988,22 @@
         <v>27</v>
       </c>
       <c r="AA2">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AB2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
         <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE2">
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1012,7 +1012,7 @@
         <v>23</v>
       </c>
       <c r="AI2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
         <v>32</v>
@@ -1027,7 +1027,7 @@
         <v>180</v>
       </c>
       <c r="AN2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO2">
         <v>90</v>
@@ -1036,40 +1036,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR2">
         <v>23</v>
       </c>
       <c r="AS2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW2">
         <v>44</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
         <v>50</v>
       </c>
       <c r="BB2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC2">
         <v>25</v>
@@ -1081,7 +1081,7 @@
         <v>110</v>
       </c>
       <c r="BF2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG2">
         <v>55</v>
@@ -1093,58 +1093,58 @@
         <v>2.44</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BN2">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BO2">
         <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT2">
         <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY2">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2">
         <v>40</v>
       </c>
       <c r="CA2">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1170,7 +1170,7 @@
         <v>1.15</v>
       </c>
       <c r="G3">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1179,7 +1179,7 @@
         <v>1000</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
         <v>950</v>
@@ -1191,16 +1191,16 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O3">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P3">
         <v>1.12</v>
       </c>
       <c r="Q3">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="R3">
         <v>1.08</v>
@@ -1218,7 +1218,7 @@
         <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1409,22 +1409,22 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="G4">
         <v>1000</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="I4">
         <v>1000</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K4">
-        <v>870</v>
+        <v>950</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1433,7 +1433,7 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O4">
         <v>1.01</v>
@@ -1442,13 +1442,13 @@
         <v>1.1</v>
       </c>
       <c r="Q4">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R4">
         <v>1.08</v>
       </c>
       <c r="S4">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1517,52 +1517,52 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
         <v>1.01</v>
@@ -1654,16 +1654,16 @@
         <v>1.3</v>
       </c>
       <c r="G5">
+        <v>1.5</v>
+      </c>
+      <c r="H5">
         <v>3.05</v>
       </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
       <c r="I5">
         <v>1000</v>
       </c>
       <c r="J5">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1675,19 +1675,19 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="O5">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Q5">
         <v>1.51</v>
       </c>
       <c r="R5">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="S5">
         <v>1.52</v>
@@ -1702,7 +1702,7 @@
         <v>1.01</v>
       </c>
       <c r="W5">
-        <v>1.49</v>
+        <v>3</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1893,22 +1893,22 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G6">
         <v>1000</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="I6">
         <v>1000</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K6">
-        <v>870</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1920,19 +1920,19 @@
         <v>1.1</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
         <v>1.1</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R6">
         <v>1.08</v>
       </c>
       <c r="S6">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2001,52 +2001,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2135,22 +2135,22 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G7">
         <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K7">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2159,22 +2159,22 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="O7">
         <v>1.01</v>
       </c>
       <c r="P7">
-        <v>1.1</v>
+        <v>1.66</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R7">
         <v>1.08</v>
       </c>
       <c r="S7">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2243,52 +2243,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2377,10 +2377,10 @@
         <v>103</v>
       </c>
       <c r="F8">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G8">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H8">
         <v>4.3</v>
@@ -2395,10 +2395,10 @@
         <v>4.6</v>
       </c>
       <c r="L8">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8">
         <v>5.7</v>
@@ -2416,16 +2416,16 @@
         <v>1.66</v>
       </c>
       <c r="S8">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T8">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="U8">
         <v>2.62</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W8">
         <v>2.1</v>
@@ -2449,7 +2449,7 @@
         <v>12</v>
       </c>
       <c r="AD8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE8">
         <v>60</v>
@@ -2539,64 +2539,64 @@
         <v>26</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB8" t="s">
         <v>105</v>
@@ -2619,7 +2619,7 @@
         <v>104</v>
       </c>
       <c r="F9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G9">
         <v>3.4</v>
@@ -2628,13 +2628,13 @@
         <v>2.24</v>
       </c>
       <c r="I9">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J9">
         <v>3.65</v>
       </c>
       <c r="K9">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L9">
         <v>1.3</v>
@@ -2664,10 +2664,10 @@
         <v>1.56</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W9">
         <v>1.41</v>
@@ -2718,7 +2718,7 @@
         <v>50</v>
       </c>
       <c r="AM9">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN9">
         <v>34</v>
@@ -2727,37 +2727,37 @@
         <v>16.5</v>
       </c>
       <c r="AP9">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ9">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="AR9">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS9">
         <v>5</v>
       </c>
       <c r="AT9">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU9">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="AV9">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AW9">
-        <v>17</v>
+        <v>4.9</v>
       </c>
       <c r="AX9">
-        <v>17.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="AZ9">
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -2775,10 +2775,10 @@
         <v>5.5</v>
       </c>
       <c r="BF9">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BG9">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH9">
         <v>4.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -331,7 +331,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-22 13:07:11</t>
+    <t>2026-09-22 15:17:44</t>
   </si>
 </sst>
 </file>
@@ -925,16 +925,16 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H2">
         <v>3.95</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J2">
         <v>3.3</v>
@@ -946,7 +946,7 @@
         <v>1.52</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N2">
         <v>3</v>
@@ -955,7 +955,7 @@
         <v>1.47</v>
       </c>
       <c r="P2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q2">
         <v>2.44</v>
@@ -970,13 +970,13 @@
         <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
         <v>10.5</v>
@@ -988,7 +988,7 @@
         <v>27</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB2">
         <v>7.8</v>
@@ -997,13 +997,13 @@
         <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AE2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1012,13 +1012,13 @@
         <v>23</v>
       </c>
       <c r="AI2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL2">
         <v>55</v>
@@ -1030,13 +1030,13 @@
         <v>26</v>
       </c>
       <c r="AO2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP2">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR2">
         <v>23</v>
@@ -1096,13 +1096,13 @@
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BN2">
         <v>5</v>
@@ -1111,37 +1111,37 @@
         <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT2">
         <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="CA2">
         <v>6.8</v>
@@ -1170,7 +1170,7 @@
         <v>1.15</v>
       </c>
       <c r="G3">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1179,7 +1179,7 @@
         <v>1000</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>950</v>
@@ -1194,13 +1194,13 @@
         <v>1.13</v>
       </c>
       <c r="O3">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="P3">
         <v>1.12</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="R3">
         <v>1.08</v>
@@ -1218,7 +1218,7 @@
         <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1457,7 +1457,7 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4">
         <v>1.01</v>
@@ -1684,7 +1684,7 @@
         <v>1.16</v>
       </c>
       <c r="Q5">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="R5">
         <v>1.16</v>
@@ -1699,7 +1699,7 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -1941,10 +1941,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2174,7 +2174,7 @@
         <v>1.08</v>
       </c>
       <c r="S7">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2380,7 +2380,7 @@
         <v>1.79</v>
       </c>
       <c r="G8">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H8">
         <v>4.3</v>
@@ -2401,22 +2401,22 @@
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O8">
         <v>1.18</v>
       </c>
       <c r="P8">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q8">
         <v>1.54</v>
       </c>
       <c r="R8">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T8">
         <v>1.47</v>
@@ -2428,7 +2428,7 @@
         <v>1.27</v>
       </c>
       <c r="W8">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X8">
         <v>32</v>
@@ -2449,7 +2449,7 @@
         <v>12</v>
       </c>
       <c r="AD8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE8">
         <v>60</v>
@@ -2458,7 +2458,7 @@
         <v>16.5</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8">
         <v>18</v>
@@ -2515,7 +2515,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA8">
         <v>1.03</v>
@@ -2619,22 +2619,22 @@
         <v>104</v>
       </c>
       <c r="F9">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G9">
         <v>3.4</v>
       </c>
       <c r="H9">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="I9">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="J9">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K9">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
         <v>1.3</v>
@@ -2652,22 +2652,22 @@
         <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S9">
         <v>2.96</v>
       </c>
       <c r="T9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W9">
         <v>1.41</v>
@@ -2700,7 +2700,7 @@
         <v>29</v>
       </c>
       <c r="AG9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH9">
         <v>17</v>
@@ -2727,58 +2727,58 @@
         <v>16.5</v>
       </c>
       <c r="AP9">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ9">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="AR9">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AS9">
         <v>5</v>
       </c>
       <c r="AT9">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU9">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV9">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AW9">
-        <v>4.9</v>
+        <v>17</v>
       </c>
       <c r="AX9">
-        <v>4.9</v>
+        <v>17</v>
       </c>
       <c r="AY9">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BA9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB9">
         <v>5.4</v>
       </c>
       <c r="BC9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD9">
         <v>5.3</v>
       </c>
       <c r="BE9">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF9">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="BG9">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BH9">
         <v>4.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -331,7 +331,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-22 15:17:44</t>
+    <t>2026-09-22 17:29:27</t>
   </si>
 </sst>
 </file>
@@ -925,22 +925,22 @@
         <v>97</v>
       </c>
       <c r="F2">
+        <v>2.14</v>
+      </c>
+      <c r="G2">
         <v>2.18</v>
       </c>
-      <c r="G2">
-        <v>2.24</v>
-      </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L2">
         <v>1.52</v>
@@ -955,10 +955,10 @@
         <v>1.47</v>
       </c>
       <c r="P2">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q2">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R2">
         <v>1.24</v>
@@ -967,58 +967,58 @@
         <v>4.9</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X2">
         <v>10.5</v>
       </c>
       <c r="Y2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z2">
         <v>27</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
         <v>23</v>
       </c>
       <c r="AI2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL2">
         <v>55</v>
@@ -1027,10 +1027,10 @@
         <v>180</v>
       </c>
       <c r="AN2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP2">
         <v>9.199999999999999</v>
@@ -1039,55 +1039,55 @@
         <v>11</v>
       </c>
       <c r="AR2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT2">
         <v>7</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV2">
         <v>15</v>
       </c>
       <c r="AW2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AX2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BE2">
         <v>110</v>
       </c>
       <c r="BF2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI2">
         <v>2.44</v>
@@ -1096,55 +1096,55 @@
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BO2">
         <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BQ2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT2">
         <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BW2">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1170,7 +1170,7 @@
         <v>1.15</v>
       </c>
       <c r="G3">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1218,7 +1218,7 @@
         <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1412,13 +1412,13 @@
         <v>1.33</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H4">
         <v>2.1</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J4">
         <v>1.12</v>
@@ -1433,13 +1433,13 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="O4">
         <v>1.01</v>
       </c>
       <c r="P4">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q4">
         <v>1.53</v>
@@ -1448,7 +1448,7 @@
         <v>1.08</v>
       </c>
       <c r="S4">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1457,10 +1457,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1660,10 +1660,10 @@
         <v>3.05</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1684,7 +1684,7 @@
         <v>1.16</v>
       </c>
       <c r="Q5">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="R5">
         <v>1.16</v>
@@ -1699,7 +1699,7 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -1896,13 +1896,13 @@
         <v>1.3</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H6">
         <v>2.6</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J6">
         <v>1.12</v>
@@ -1917,13 +1917,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="O6">
         <v>1.4</v>
       </c>
       <c r="P6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q6">
         <v>1.42</v>
@@ -1941,10 +1941,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2162,19 +2162,19 @@
         <v>1.66</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P7">
         <v>1.66</v>
       </c>
       <c r="Q7">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="R7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S7">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2183,10 +2183,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2377,22 +2377,22 @@
         <v>103</v>
       </c>
       <c r="F8">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G8">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H8">
         <v>4.3</v>
       </c>
       <c r="I8">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J8">
         <v>4.1</v>
       </c>
       <c r="K8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
         <v>1.24</v>
@@ -2401,7 +2401,7 @@
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O8">
         <v>1.18</v>
@@ -2410,22 +2410,22 @@
         <v>2.64</v>
       </c>
       <c r="Q8">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T8">
         <v>1.47</v>
       </c>
       <c r="U8">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W8">
         <v>2.12</v>
@@ -2443,7 +2443,7 @@
         <v>110</v>
       </c>
       <c r="AB8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC8">
         <v>12</v>
@@ -2473,7 +2473,7 @@
         <v>19</v>
       </c>
       <c r="AL8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM8">
         <v>65</v>
@@ -2542,7 +2542,7 @@
         <v>5.2</v>
       </c>
       <c r="BI8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ8">
         <v>10</v>
@@ -2554,7 +2554,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BN8">
         <v>5.7</v>
@@ -2569,10 +2569,10 @@
         <v>9</v>
       </c>
       <c r="BR8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BT8">
         <v>9.199999999999999</v>
@@ -2584,19 +2584,19 @@
         <v>34</v>
       </c>
       <c r="BW8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BX8">
         <v>38</v>
       </c>
       <c r="BY8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BZ8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CA8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="s">
         <v>105</v>
@@ -2619,61 +2619,61 @@
         <v>104</v>
       </c>
       <c r="F9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G9">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H9">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I9">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J9">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K9">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L9">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
         <v>4.2</v>
       </c>
       <c r="O9">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
         <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R9">
         <v>1.4</v>
       </c>
       <c r="S9">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="T9">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="U9">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W9">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y9">
         <v>14</v>
@@ -2685,22 +2685,22 @@
         <v>32</v>
       </c>
       <c r="AB9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD9">
         <v>13.5</v>
       </c>
       <c r="AE9">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AF9">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AG9">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
         <v>17</v>
@@ -2715,13 +2715,13 @@
         <v>36</v>
       </c>
       <c r="AL9">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM9">
         <v>90</v>
       </c>
       <c r="AN9">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO9">
         <v>16.5</v>
@@ -2730,55 +2730,55 @@
         <v>12.5</v>
       </c>
       <c r="AQ9">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR9">
+        <v>13.5</v>
+      </c>
+      <c r="AS9">
+        <v>6.2</v>
+      </c>
+      <c r="AT9">
+        <v>12</v>
+      </c>
+      <c r="AU9">
+        <v>7.6</v>
+      </c>
+      <c r="AV9">
+        <v>10</v>
+      </c>
+      <c r="AW9">
+        <v>20</v>
+      </c>
+      <c r="AX9">
+        <v>19.5</v>
+      </c>
+      <c r="AY9">
         <v>11.5</v>
       </c>
-      <c r="AS9">
-        <v>5</v>
-      </c>
-      <c r="AT9">
-        <v>10.5</v>
-      </c>
-      <c r="AU9">
-        <v>6.4</v>
-      </c>
-      <c r="AV9">
-        <v>8.4</v>
-      </c>
-      <c r="AW9">
-        <v>17</v>
-      </c>
-      <c r="AX9">
-        <v>17</v>
-      </c>
-      <c r="AY9">
-        <v>10</v>
-      </c>
       <c r="AZ9">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA9">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BB9">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC9">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BD9">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="BE9">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF9">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BG9">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH9">
         <v>4.4</v>
@@ -2790,7 +2790,7 @@
         <v>11</v>
       </c>
       <c r="BK9">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL9">
         <v>120</v>
@@ -2820,7 +2820,7 @@
         <v>6.4</v>
       </c>
       <c r="BU9">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV9">
         <v>17.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -331,7 +331,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-22 17:29:27</t>
+    <t>2026-09-22 19:40:27</t>
   </si>
 </sst>
 </file>
@@ -925,124 +925,124 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="G2">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="H2">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J2">
+        <v>3.35</v>
+      </c>
+      <c r="K2">
+        <v>3.45</v>
+      </c>
+      <c r="L2">
+        <v>1.5</v>
+      </c>
+      <c r="M2">
+        <v>1.1</v>
+      </c>
+      <c r="N2">
         <v>3.25</v>
       </c>
-      <c r="K2">
-        <v>3.35</v>
-      </c>
-      <c r="L2">
-        <v>1.52</v>
-      </c>
-      <c r="M2">
-        <v>1.11</v>
-      </c>
-      <c r="N2">
-        <v>3</v>
-      </c>
       <c r="O2">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="P2">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="U2">
         <v>1.91</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="X2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB2">
         <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AE2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2">
         <v>24</v>
       </c>
       <c r="AS2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AT2">
         <v>7</v>
@@ -1051,16 +1051,16 @@
         <v>7</v>
       </c>
       <c r="AV2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW2">
         <v>50</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
         <v>20</v>
@@ -1069,82 +1069,82 @@
         <v>60</v>
       </c>
       <c r="BB2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BG2">
         <v>60</v>
       </c>
       <c r="BH2">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="BI2">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BM2">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
         <v>4.8</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BR2">
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BV2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1170,7 +1170,7 @@
         <v>1.15</v>
       </c>
       <c r="G3">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1188,7 +1188,7 @@
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3">
         <v>1.13</v>
@@ -1218,7 +1218,7 @@
         <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1275,52 +1275,52 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
         <v>1.01</v>
@@ -1409,22 +1409,22 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="G4">
-        <v>110</v>
+        <v>2.44</v>
       </c>
       <c r="H4">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="J4">
-        <v>1.12</v>
+        <v>2.72</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1442,13 +1442,13 @@
         <v>1.12</v>
       </c>
       <c r="Q4">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R4">
         <v>1.08</v>
       </c>
       <c r="S4">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1457,13 +1457,13 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y4">
         <v>1000</v>
@@ -1475,10 +1475,10 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4">
         <v>1000</v>
@@ -1487,10 +1487,10 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH4">
         <v>1000</v>
@@ -1499,73 +1499,73 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG4">
         <v>1.01</v>
@@ -1651,22 +1651,22 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="G5">
         <v>1.5</v>
       </c>
       <c r="H5">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="J5">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1675,10 +1675,10 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.16</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
         <v>1.16</v>
@@ -1687,10 +1687,10 @@
         <v>1.37</v>
       </c>
       <c r="R5">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1699,7 +1699,7 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -1717,10 +1717,10 @@
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD5">
         <v>1000</v>
@@ -1729,10 +1729,10 @@
         <v>1000</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH5">
         <v>1000</v>
@@ -1741,76 +1741,76 @@
         <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5">
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1893,22 +1893,22 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="G6">
-        <v>110</v>
+        <v>2.3</v>
       </c>
       <c r="H6">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="I6">
         <v>110</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>2.84</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1920,7 +1920,7 @@
         <v>1.13</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
         <v>1.12</v>
@@ -1941,10 +1941,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -1959,10 +1959,10 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD6">
         <v>1000</v>
@@ -1971,10 +1971,10 @@
         <v>1000</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH6">
         <v>1000</v>
@@ -1983,76 +1983,76 @@
         <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6">
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2135,22 +2135,22 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>2.8</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2162,19 +2162,19 @@
         <v>1.66</v>
       </c>
       <c r="O7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
         <v>1.66</v>
       </c>
       <c r="Q7">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="R7">
         <v>1.09</v>
       </c>
       <c r="S7">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2183,10 +2183,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.76</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2201,10 +2201,10 @@
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD7">
         <v>1000</v>
@@ -2213,10 +2213,10 @@
         <v>1000</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH7">
         <v>1000</v>
@@ -2225,76 +2225,76 @@
         <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM7">
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO7">
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2380,19 +2380,19 @@
         <v>1.81</v>
       </c>
       <c r="G8">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I8">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J8">
         <v>4.1</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
         <v>1.24</v>
@@ -2401,7 +2401,7 @@
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O8">
         <v>1.18</v>
@@ -2410,22 +2410,22 @@
         <v>2.64</v>
       </c>
       <c r="Q8">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S8">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T8">
         <v>1.47</v>
       </c>
       <c r="U8">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V8">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W8">
         <v>2.12</v>
@@ -2437,10 +2437,10 @@
         <v>26</v>
       </c>
       <c r="Z8">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AA8">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB8">
         <v>15.5</v>
@@ -2449,10 +2449,10 @@
         <v>12</v>
       </c>
       <c r="AD8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE8">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF8">
         <v>16.5</v>
@@ -2461,10 +2461,10 @@
         <v>12</v>
       </c>
       <c r="AH8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ8">
         <v>26</v>
@@ -2473,10 +2473,10 @@
         <v>19</v>
       </c>
       <c r="AL8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM8">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN8">
         <v>9.199999999999999</v>
@@ -2491,10 +2491,10 @@
         <v>17</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT8">
         <v>12</v>
@@ -2503,10 +2503,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX8">
         <v>12.5</v>
@@ -2515,10 +2515,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB8">
         <v>17</v>
@@ -2530,13 +2530,13 @@
         <v>18.5</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF8">
         <v>7</v>
       </c>
       <c r="BG8">
-        <v>26</v>
+        <v>5.6</v>
       </c>
       <c r="BH8">
         <v>5.2</v>
@@ -2554,7 +2554,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BN8">
         <v>5.7</v>
@@ -2572,7 +2572,7 @@
         <v>24</v>
       </c>
       <c r="BS8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BT8">
         <v>9.199999999999999</v>
@@ -2584,7 +2584,7 @@
         <v>34</v>
       </c>
       <c r="BW8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BX8">
         <v>38</v>
@@ -2625,16 +2625,16 @@
         <v>3.3</v>
       </c>
       <c r="H9">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I9">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J9">
         <v>3.6</v>
       </c>
       <c r="K9">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L9">
         <v>1.35</v>
@@ -2646,7 +2646,7 @@
         <v>4.2</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P9">
         <v>2.1</v>
@@ -2655,7 +2655,7 @@
         <v>1.76</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S9">
         <v>3.05</v>
@@ -2664,13 +2664,13 @@
         <v>1.7</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
         <v>1.69</v>
       </c>
       <c r="W9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X9">
         <v>18</v>
@@ -2685,7 +2685,7 @@
         <v>32</v>
       </c>
       <c r="AB9">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -2697,7 +2697,7 @@
         <v>25</v>
       </c>
       <c r="AF9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG9">
         <v>14.5</v>
@@ -2721,7 +2721,7 @@
         <v>90</v>
       </c>
       <c r="AN9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO9">
         <v>16.5</v>
@@ -2736,7 +2736,7 @@
         <v>13.5</v>
       </c>
       <c r="AS9">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT9">
         <v>12</v>
@@ -2760,22 +2760,22 @@
         <v>13.5</v>
       </c>
       <c r="BA9">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB9">
+        <v>7.4</v>
+      </c>
+      <c r="BC9">
         <v>6.8</v>
-      </c>
-      <c r="BC9">
-        <v>6.2</v>
       </c>
       <c r="BD9">
         <v>32</v>
       </c>
       <c r="BE9">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF9">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG9">
         <v>13.5</v>
@@ -2796,7 +2796,7 @@
         <v>120</v>
       </c>
       <c r="BM9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BN9">
         <v>6.8</v>
@@ -2805,19 +2805,19 @@
         <v>5.6</v>
       </c>
       <c r="BP9">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BQ9">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BR9">
         <v>34</v>
       </c>
       <c r="BS9">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BT9">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BU9">
         <v>4.7</v>
@@ -2826,19 +2826,19 @@
         <v>17.5</v>
       </c>
       <c r="BW9">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BX9">
         <v>34</v>
       </c>
       <c r="BY9">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BZ9">
         <v>23</v>
       </c>
       <c r="CA9">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="s">
         <v>105</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -331,7 +331,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-22 19:40:27</t>
+    <t>2026-09-22 21:51:31</t>
   </si>
 </sst>
 </file>
@@ -925,16 +925,16 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="G2">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I2">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J2">
         <v>3.35</v>
@@ -943,16 +943,16 @@
         <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M2">
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P2">
         <v>1.71</v>
@@ -964,49 +964,49 @@
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U2">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
         <v>22</v>
@@ -1015,34 +1015,34 @@
         <v>95</v>
       </c>
       <c r="AJ2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL2">
         <v>50</v>
       </c>
       <c r="AM2">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO2">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AP2">
         <v>10</v>
       </c>
       <c r="AQ2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AS2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AT2">
         <v>7</v>
@@ -1051,10 +1051,10 @@
         <v>7</v>
       </c>
       <c r="AV2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX2">
         <v>10</v>
@@ -1063,88 +1063,88 @@
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA2">
         <v>60</v>
       </c>
       <c r="BB2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BE2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="BF2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BH2">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI2">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL2">
-        <v>970</v>
+        <v>200</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>140</v>
       </c>
       <c r="BN2">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BQ2">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BR2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BV2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1218,7 +1218,7 @@
         <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1409,13 +1409,13 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G4">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I4">
         <v>34</v>
@@ -1436,7 +1436,7 @@
         <v>1.12</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4">
         <v>1.12</v>
@@ -1460,10 +1460,10 @@
         <v>1.11</v>
       </c>
       <c r="W4">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X4">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y4">
         <v>1000</v>
@@ -1517,58 +1517,58 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU4">
         <v>4.4</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF4">
         <v>3.85</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1759,7 +1759,7 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AQ5">
         <v>2.5</v>
@@ -1771,10 +1771,10 @@
         <v>2.5</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AV5">
         <v>2.5</v>
@@ -1783,28 +1783,28 @@
         <v>2.5</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BA5">
         <v>2.5</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BF5">
         <v>3.2</v>
@@ -1923,13 +1923,13 @@
         <v>1.02</v>
       </c>
       <c r="P6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q6">
         <v>1.42</v>
       </c>
       <c r="R6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S6">
         <v>1.43</v>
@@ -1944,7 +1944,7 @@
         <v>1.09</v>
       </c>
       <c r="W6">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2001,52 +2001,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AU6">
         <v>4.9</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF6">
         <v>3.2</v>
@@ -2168,7 +2168,7 @@
         <v>1.66</v>
       </c>
       <c r="Q7">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R7">
         <v>1.09</v>
@@ -2186,7 +2186,7 @@
         <v>1.07</v>
       </c>
       <c r="W7">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2243,52 +2243,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AU7">
         <v>4.9</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BF7">
         <v>3.55</v>
@@ -2377,16 +2377,16 @@
         <v>103</v>
       </c>
       <c r="F8">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G8">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H8">
         <v>4.2</v>
       </c>
       <c r="I8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J8">
         <v>4.1</v>
@@ -2407,7 +2407,7 @@
         <v>1.18</v>
       </c>
       <c r="P8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
         <v>1.54</v>
@@ -2422,13 +2422,13 @@
         <v>1.47</v>
       </c>
       <c r="U8">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X8">
         <v>32</v>
@@ -2437,7 +2437,7 @@
         <v>26</v>
       </c>
       <c r="Z8">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AA8">
         <v>900</v>
@@ -2449,7 +2449,7 @@
         <v>12</v>
       </c>
       <c r="AD8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE8">
         <v>130</v>
@@ -2473,7 +2473,7 @@
         <v>19</v>
       </c>
       <c r="AL8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM8">
         <v>200</v>
@@ -2521,7 +2521,7 @@
         <v>5</v>
       </c>
       <c r="BB8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BC8">
         <v>14</v>
@@ -2536,7 +2536,7 @@
         <v>7</v>
       </c>
       <c r="BG8">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BH8">
         <v>5.2</v>
@@ -2554,7 +2554,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BN8">
         <v>5.7</v>
@@ -2572,7 +2572,7 @@
         <v>24</v>
       </c>
       <c r="BS8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BT8">
         <v>9.199999999999999</v>
@@ -2619,13 +2619,13 @@
         <v>104</v>
       </c>
       <c r="F9">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G9">
         <v>3.3</v>
       </c>
       <c r="H9">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I9">
         <v>2.44</v>
@@ -2658,25 +2658,25 @@
         <v>1.42</v>
       </c>
       <c r="S9">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T9">
         <v>1.7</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y9">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z9">
         <v>17</v>
@@ -2688,28 +2688,28 @@
         <v>15</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE9">
         <v>25</v>
       </c>
       <c r="AF9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI9">
         <v>36</v>
       </c>
       <c r="AJ9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK9">
         <v>36</v>
@@ -2718,7 +2718,7 @@
         <v>44</v>
       </c>
       <c r="AM9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN9">
         <v>28</v>
@@ -2727,19 +2727,19 @@
         <v>16.5</v>
       </c>
       <c r="AP9">
+        <v>14.5</v>
+      </c>
+      <c r="AQ9">
+        <v>10</v>
+      </c>
+      <c r="AR9">
+        <v>14</v>
+      </c>
+      <c r="AS9">
+        <v>27</v>
+      </c>
+      <c r="AT9">
         <v>12.5</v>
-      </c>
-      <c r="AQ9">
-        <v>10.5</v>
-      </c>
-      <c r="AR9">
-        <v>13.5</v>
-      </c>
-      <c r="AS9">
-        <v>6.6</v>
-      </c>
-      <c r="AT9">
-        <v>12</v>
       </c>
       <c r="AU9">
         <v>7.6</v>
@@ -2748,34 +2748,34 @@
         <v>10</v>
       </c>
       <c r="AW9">
+        <v>21</v>
+      </c>
+      <c r="AX9">
         <v>20</v>
       </c>
-      <c r="AX9">
-        <v>19.5</v>
-      </c>
       <c r="AY9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA9">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BB9">
-        <v>7.4</v>
+        <v>46</v>
       </c>
       <c r="BC9">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BD9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE9">
-        <v>7.6</v>
+        <v>60</v>
       </c>
       <c r="BF9">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG9">
         <v>13.5</v>
@@ -2796,28 +2796,28 @@
         <v>120</v>
       </c>
       <c r="BM9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BN9">
         <v>6.8</v>
       </c>
       <c r="BO9">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP9">
         <v>28</v>
       </c>
       <c r="BQ9">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR9">
         <v>34</v>
       </c>
       <c r="BS9">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU9">
         <v>4.7</v>
@@ -2826,13 +2826,13 @@
         <v>17.5</v>
       </c>
       <c r="BW9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX9">
         <v>34</v>
       </c>
       <c r="BY9">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BZ9">
         <v>23</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="102">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
     <t>Nigerian Premier League</t>
   </si>
   <si>
@@ -271,9 +268,6 @@
     <t>2026-09-23</t>
   </si>
   <si>
-    <t>01:00:00</t>
-  </si>
-  <si>
     <t>15:00:00</t>
   </si>
   <si>
@@ -283,9 +277,6 @@
     <t>20:00:00</t>
   </si>
   <si>
-    <t>Santa Fe</t>
-  </si>
-  <si>
     <t>Enugu Rangers International</t>
   </si>
   <si>
@@ -307,9 +298,6 @@
     <t>Asociacion Deportiva Tarma</t>
   </si>
   <si>
-    <t>Deportivo Cali</t>
-  </si>
-  <si>
     <t>Ranchers Bees FC</t>
   </si>
   <si>
@@ -331,7 +319,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-22 21:51:31</t>
+    <t>2026-09-23 00:02:48</t>
   </si>
 </sst>
 </file>
@@ -663,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -913,285 +901,285 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
         <v>84</v>
       </c>
-      <c r="C2" t="s">
-        <v>85</v>
-      </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F2">
-        <v>1.99</v>
+        <v>1.15</v>
       </c>
       <c r="G2">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="H2">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L2">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>1.14</v>
       </c>
       <c r="O2">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.12</v>
       </c>
       <c r="Q2">
-        <v>2.36</v>
+        <v>1.36</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="S2">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="T2">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>140</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:80">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
         <v>84</v>
       </c>
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F3">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="G3">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O3">
         <v>1.02</v>
@@ -1200,13 +1188,13 @@
         <v>1.12</v>
       </c>
       <c r="Q3">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="R3">
         <v>1.08</v>
       </c>
       <c r="S3">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1215,13 +1203,13 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W3">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y3">
         <v>1000</v>
@@ -1233,10 +1221,10 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD3">
         <v>1000</v>
@@ -1245,10 +1233,10 @@
         <v>1000</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH3">
         <v>1000</v>
@@ -1257,76 +1245,76 @@
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1389,39 +1377,39 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
         <v>84</v>
       </c>
-      <c r="C4" t="s">
-        <v>86</v>
-      </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F4">
+        <v>1.36</v>
+      </c>
+      <c r="G4">
         <v>1.5</v>
       </c>
-      <c r="G4">
-        <v>2.42</v>
-      </c>
       <c r="H4">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="I4">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="J4">
-        <v>2.72</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -1433,16 +1421,16 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="O4">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="P4">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Q4">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="R4">
         <v>1.08</v>
@@ -1457,13 +1445,13 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="W4">
-        <v>1.71</v>
+        <v>3</v>
       </c>
       <c r="X4">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
         <v>1000</v>
@@ -1478,7 +1466,7 @@
         <v>500</v>
       </c>
       <c r="AC4">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD4">
         <v>1000</v>
@@ -1511,64 +1499,64 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AQ4">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="AR4">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="AS4">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="AT4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AU4">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="AV4">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="AW4">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="AX4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AY4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AZ4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BA4">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="BB4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BC4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BD4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BE4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BF4">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="BG4">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1631,42 +1619,42 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
         <v>84</v>
       </c>
-      <c r="C5" t="s">
-        <v>86</v>
-      </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F5">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="G5">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="H5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I5">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="J5">
-        <v>3.65</v>
+        <v>2.84</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1675,22 +1663,22 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>1.13</v>
       </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Q5">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="R5">
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1699,10 +1687,10 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W5">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1753,64 +1741,64 @@
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AQ5">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AR5">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AS5">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AT5">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AU5">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="AV5">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AW5">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AX5">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AY5">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AZ5">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BA5">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="BB5">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BC5">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BD5">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BE5">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BF5">
         <v>3.2</v>
       </c>
       <c r="BG5">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1873,39 +1861,39 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
         <v>84</v>
       </c>
-      <c r="C6" t="s">
-        <v>86</v>
-      </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F6">
         <v>1.44</v>
       </c>
       <c r="G6">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="H6">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="I6">
         <v>110</v>
       </c>
       <c r="J6">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -1917,22 +1905,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.13</v>
+        <v>1.66</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.13</v>
+        <v>1.66</v>
       </c>
       <c r="Q6">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="R6">
         <v>1.09</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -1941,10 +1929,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W6">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -1995,61 +1983,61 @@
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AQ6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AR6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AS6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AT6">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AU6">
         <v>4.9</v>
       </c>
       <c r="AV6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AW6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AX6">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AY6">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AZ6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BA6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BB6">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="BC6">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="BD6">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="BE6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BF6">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BG6">
         <v>1.55</v>
@@ -2115,7 +2103,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2123,241 +2111,241 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F7">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="H7">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I7">
-        <v>110</v>
+        <v>4.6</v>
       </c>
       <c r="J7">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M7">
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.66</v>
+        <v>5.8</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P7">
-        <v>1.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q7">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R7">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="S7">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AB7">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AC7">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF7">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AG7">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ7">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AK7">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AL7">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN7">
-        <v>500</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP7">
-        <v>1.08</v>
+        <v>20</v>
       </c>
       <c r="AQ7">
-        <v>1.08</v>
+        <v>17</v>
       </c>
       <c r="AR7">
-        <v>1.08</v>
+        <v>6</v>
       </c>
       <c r="AS7">
-        <v>1.08</v>
+        <v>6.2</v>
       </c>
       <c r="AT7">
-        <v>1.08</v>
+        <v>12</v>
       </c>
       <c r="AU7">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>1.08</v>
+        <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>1.08</v>
+        <v>6.2</v>
       </c>
       <c r="AX7">
-        <v>1.08</v>
+        <v>12.5</v>
       </c>
       <c r="AY7">
-        <v>1.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7">
-        <v>1.08</v>
+        <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>1.08</v>
+        <v>5.9</v>
       </c>
       <c r="BB7">
-        <v>1.08</v>
+        <v>20</v>
       </c>
       <c r="BC7">
-        <v>1.08</v>
+        <v>14.5</v>
       </c>
       <c r="BD7">
-        <v>1.08</v>
+        <v>13</v>
       </c>
       <c r="BE7">
-        <v>1.08</v>
+        <v>6</v>
       </c>
       <c r="BF7">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="BG7">
-        <v>1.55</v>
+        <v>5.9</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2365,483 +2353,241 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="G8">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="H8">
+        <v>2.38</v>
+      </c>
+      <c r="I8">
+        <v>2.44</v>
+      </c>
+      <c r="J8">
+        <v>3.65</v>
+      </c>
+      <c r="K8">
+        <v>3.8</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.06</v>
+      </c>
+      <c r="N8">
         <v>4.2</v>
       </c>
-      <c r="I8">
-        <v>4.5</v>
-      </c>
-      <c r="J8">
-        <v>4.1</v>
-      </c>
-      <c r="K8">
-        <v>4.6</v>
-      </c>
-      <c r="L8">
-        <v>1.24</v>
-      </c>
-      <c r="M8">
-        <v>1.02</v>
-      </c>
-      <c r="N8">
-        <v>5.8</v>
-      </c>
       <c r="O8">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="Q8">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="R8">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="T8">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="U8">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="W8">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="X8">
+        <v>17.5</v>
+      </c>
+      <c r="Y8">
+        <v>12.5</v>
+      </c>
+      <c r="Z8">
+        <v>17.5</v>
+      </c>
+      <c r="AA8">
+        <v>34</v>
+      </c>
+      <c r="AB8">
+        <v>15</v>
+      </c>
+      <c r="AC8">
+        <v>9</v>
+      </c>
+      <c r="AD8">
+        <v>12</v>
+      </c>
+      <c r="AE8">
+        <v>25</v>
+      </c>
+      <c r="AF8">
+        <v>28</v>
+      </c>
+      <c r="AG8">
+        <v>14.5</v>
+      </c>
+      <c r="AH8">
+        <v>19.5</v>
+      </c>
+      <c r="AI8">
+        <v>36</v>
+      </c>
+      <c r="AJ8">
+        <v>55</v>
+      </c>
+      <c r="AK8">
+        <v>34</v>
+      </c>
+      <c r="AL8">
+        <v>42</v>
+      </c>
+      <c r="AM8">
+        <v>80</v>
+      </c>
+      <c r="AN8">
+        <v>28</v>
+      </c>
+      <c r="AO8">
+        <v>17</v>
+      </c>
+      <c r="AP8">
+        <v>14.5</v>
+      </c>
+      <c r="AQ8">
+        <v>10.5</v>
+      </c>
+      <c r="AR8">
+        <v>13.5</v>
+      </c>
+      <c r="AS8">
+        <v>29</v>
+      </c>
+      <c r="AT8">
+        <v>13</v>
+      </c>
+      <c r="AU8">
+        <v>7.6</v>
+      </c>
+      <c r="AV8">
+        <v>10</v>
+      </c>
+      <c r="AW8">
+        <v>20</v>
+      </c>
+      <c r="AX8">
+        <v>20</v>
+      </c>
+      <c r="AY8">
+        <v>12</v>
+      </c>
+      <c r="AZ8">
+        <v>14</v>
+      </c>
+      <c r="BA8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB8">
+        <v>44</v>
+      </c>
+      <c r="BC8">
+        <v>8</v>
+      </c>
+      <c r="BD8">
         <v>32</v>
       </c>
-      <c r="Y8">
-        <v>26</v>
-      </c>
-      <c r="Z8">
-        <v>48</v>
-      </c>
-      <c r="AA8">
-        <v>900</v>
-      </c>
-      <c r="AB8">
-        <v>15.5</v>
-      </c>
-      <c r="AC8">
-        <v>12</v>
-      </c>
-      <c r="AD8">
-        <v>19</v>
-      </c>
-      <c r="AE8">
-        <v>130</v>
-      </c>
-      <c r="AF8">
-        <v>16.5</v>
-      </c>
-      <c r="AG8">
-        <v>12</v>
-      </c>
-      <c r="AH8">
-        <v>17.5</v>
-      </c>
-      <c r="AI8">
-        <v>44</v>
-      </c>
-      <c r="AJ8">
-        <v>26</v>
-      </c>
-      <c r="AK8">
-        <v>19</v>
-      </c>
-      <c r="AL8">
-        <v>29</v>
-      </c>
-      <c r="AM8">
-        <v>200</v>
-      </c>
-      <c r="AN8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO8">
-        <v>40</v>
-      </c>
-      <c r="AP8">
-        <v>20</v>
-      </c>
-      <c r="AQ8">
-        <v>17</v>
-      </c>
-      <c r="AR8">
-        <v>5.1</v>
-      </c>
-      <c r="AS8">
-        <v>5.4</v>
-      </c>
-      <c r="AT8">
-        <v>12</v>
-      </c>
-      <c r="AU8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV8">
+      <c r="BE8">
+        <v>55</v>
+      </c>
+      <c r="BF8">
+        <v>7.6</v>
+      </c>
+      <c r="BG8">
         <v>14</v>
       </c>
-      <c r="AW8">
-        <v>5.2</v>
-      </c>
-      <c r="AX8">
-        <v>12.5</v>
-      </c>
-      <c r="AY8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8">
-        <v>13</v>
-      </c>
-      <c r="BA8">
-        <v>5</v>
-      </c>
-      <c r="BB8">
-        <v>20</v>
-      </c>
-      <c r="BC8">
-        <v>14</v>
-      </c>
-      <c r="BD8">
-        <v>18.5</v>
-      </c>
-      <c r="BE8">
-        <v>5.2</v>
-      </c>
-      <c r="BF8">
-        <v>7</v>
-      </c>
-      <c r="BG8">
-        <v>5</v>
-      </c>
       <c r="BH8">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>6.8</v>
+        <v>1.21</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>4</v>
+        <v>1.21</v>
       </c>
       <c r="BP8">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9</v>
+        <v>1.21</v>
       </c>
       <c r="BR8">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>6.2</v>
+        <v>1.21</v>
       </c>
       <c r="BV8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>21</v>
+        <v>1.21</v>
       </c>
       <c r="BX8">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>10.5</v>
+        <v>1.21</v>
       </c>
       <c r="CB8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:80">
-      <c r="A9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9">
-        <v>3.15</v>
-      </c>
-      <c r="G9">
-        <v>3.3</v>
-      </c>
-      <c r="H9">
-        <v>2.38</v>
-      </c>
-      <c r="I9">
-        <v>2.44</v>
-      </c>
-      <c r="J9">
-        <v>3.6</v>
-      </c>
-      <c r="K9">
-        <v>3.75</v>
-      </c>
-      <c r="L9">
-        <v>1.35</v>
-      </c>
-      <c r="M9">
-        <v>1.06</v>
-      </c>
-      <c r="N9">
-        <v>4.2</v>
-      </c>
-      <c r="O9">
-        <v>1.26</v>
-      </c>
-      <c r="P9">
-        <v>2.1</v>
-      </c>
-      <c r="Q9">
-        <v>1.76</v>
-      </c>
-      <c r="R9">
-        <v>1.42</v>
-      </c>
-      <c r="S9">
-        <v>2.98</v>
-      </c>
-      <c r="T9">
-        <v>1.7</v>
-      </c>
-      <c r="U9">
-        <v>2.28</v>
-      </c>
-      <c r="V9">
-        <v>1.68</v>
-      </c>
-      <c r="W9">
-        <v>1.43</v>
-      </c>
-      <c r="X9">
-        <v>17.5</v>
-      </c>
-      <c r="Y9">
-        <v>12.5</v>
-      </c>
-      <c r="Z9">
-        <v>17</v>
-      </c>
-      <c r="AA9">
-        <v>32</v>
-      </c>
-      <c r="AB9">
-        <v>15</v>
-      </c>
-      <c r="AC9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD9">
-        <v>11.5</v>
-      </c>
-      <c r="AE9">
-        <v>25</v>
-      </c>
-      <c r="AF9">
-        <v>25</v>
-      </c>
-      <c r="AG9">
-        <v>14</v>
-      </c>
-      <c r="AH9">
-        <v>16.5</v>
-      </c>
-      <c r="AI9">
-        <v>36</v>
-      </c>
-      <c r="AJ9">
-        <v>55</v>
-      </c>
-      <c r="AK9">
-        <v>36</v>
-      </c>
-      <c r="AL9">
-        <v>44</v>
-      </c>
-      <c r="AM9">
-        <v>85</v>
-      </c>
-      <c r="AN9">
-        <v>28</v>
-      </c>
-      <c r="AO9">
-        <v>16.5</v>
-      </c>
-      <c r="AP9">
-        <v>14.5</v>
-      </c>
-      <c r="AQ9">
-        <v>10</v>
-      </c>
-      <c r="AR9">
-        <v>14</v>
-      </c>
-      <c r="AS9">
-        <v>27</v>
-      </c>
-      <c r="AT9">
-        <v>12.5</v>
-      </c>
-      <c r="AU9">
-        <v>7.6</v>
-      </c>
-      <c r="AV9">
-        <v>10</v>
-      </c>
-      <c r="AW9">
-        <v>21</v>
-      </c>
-      <c r="AX9">
-        <v>20</v>
-      </c>
-      <c r="AY9">
-        <v>12</v>
-      </c>
-      <c r="AZ9">
-        <v>14</v>
-      </c>
-      <c r="BA9">
-        <v>29</v>
-      </c>
-      <c r="BB9">
-        <v>46</v>
-      </c>
-      <c r="BC9">
-        <v>28</v>
-      </c>
-      <c r="BD9">
-        <v>34</v>
-      </c>
-      <c r="BE9">
-        <v>60</v>
-      </c>
-      <c r="BF9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG9">
-        <v>13.5</v>
-      </c>
-      <c r="BH9">
-        <v>4.4</v>
-      </c>
-      <c r="BI9">
-        <v>2.96</v>
-      </c>
-      <c r="BJ9">
-        <v>11</v>
-      </c>
-      <c r="BK9">
-        <v>6.8</v>
-      </c>
-      <c r="BL9">
-        <v>120</v>
-      </c>
-      <c r="BM9">
-        <v>6</v>
-      </c>
-      <c r="BN9">
-        <v>6.8</v>
-      </c>
-      <c r="BO9">
-        <v>5.5</v>
-      </c>
-      <c r="BP9">
-        <v>28</v>
-      </c>
-      <c r="BQ9">
-        <v>5.2</v>
-      </c>
-      <c r="BR9">
-        <v>34</v>
-      </c>
-      <c r="BS9">
-        <v>5.3</v>
-      </c>
-      <c r="BT9">
-        <v>5.7</v>
-      </c>
-      <c r="BU9">
-        <v>4.7</v>
-      </c>
-      <c r="BV9">
-        <v>17.5</v>
-      </c>
-      <c r="BW9">
-        <v>4.6</v>
-      </c>
-      <c r="BX9">
-        <v>34</v>
-      </c>
-      <c r="BY9">
-        <v>5.3</v>
-      </c>
-      <c r="BZ9">
-        <v>23</v>
-      </c>
-      <c r="CA9">
-        <v>5</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -319,7 +319,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-23 00:02:48</t>
+    <t>2026-09-23 02:13:27</t>
   </si>
 </sst>
 </file>
@@ -916,7 +916,7 @@
         <v>1.15</v>
       </c>
       <c r="G2">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -1158,7 +1158,7 @@
         <v>1.52</v>
       </c>
       <c r="G3">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -1167,7 +1167,7 @@
         <v>34</v>
       </c>
       <c r="J3">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="K3">
         <v>7</v>
@@ -1182,19 +1182,19 @@
         <v>1.12</v>
       </c>
       <c r="O3">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
         <v>1.12</v>
       </c>
       <c r="Q3">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R3">
         <v>1.08</v>
       </c>
       <c r="S3">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1206,19 +1206,19 @@
         <v>1.11</v>
       </c>
       <c r="W3">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="X3">
         <v>970</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB3">
         <v>500</v>
@@ -1227,10 +1227,10 @@
         <v>970</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF3">
         <v>500</v>
@@ -1239,10 +1239,10 @@
         <v>500</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ3">
         <v>500</v>
@@ -1254,67 +1254,67 @@
         <v>500</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN3">
         <v>600</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AQ3">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AR3">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AS3">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AT3">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AU3">
         <v>4.4</v>
       </c>
       <c r="AV3">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AW3">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AX3">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AY3">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AZ3">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="BA3">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="BB3">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="BC3">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="BD3">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="BE3">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="BF3">
         <v>3.85</v>
       </c>
       <c r="BG3">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1418,10 +1418,10 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="O4">
         <v>1.09</v>
@@ -1466,7 +1466,7 @@
         <v>500</v>
       </c>
       <c r="AC4">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD4">
         <v>1000</v>
@@ -1505,7 +1505,7 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AQ4">
         <v>2.5</v>
@@ -1517,10 +1517,10 @@
         <v>2.5</v>
       </c>
       <c r="AT4">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AU4">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AV4">
         <v>2.5</v>
@@ -1535,7 +1535,7 @@
         <v>1.09</v>
       </c>
       <c r="AZ4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BA4">
         <v>2.5</v>
@@ -1550,7 +1550,7 @@
         <v>1.09</v>
       </c>
       <c r="BE4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BF4">
         <v>3.2</v>
@@ -1645,7 +1645,7 @@
         <v>2.3</v>
       </c>
       <c r="H5">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="I5">
         <v>14</v>
@@ -1654,7 +1654,7 @@
         <v>2.84</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1669,16 +1669,16 @@
         <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Q5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S5">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1690,31 +1690,31 @@
         <v>1.09</v>
       </c>
       <c r="W5">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB5">
         <v>500</v>
       </c>
       <c r="AC5">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF5">
         <v>500</v>
@@ -1723,10 +1723,10 @@
         <v>500</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ5">
         <v>500</v>
@@ -1738,61 +1738,61 @@
         <v>500</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5">
         <v>600</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP5">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AQ5">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR5">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AS5">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AT5">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AU5">
         <v>4.9</v>
       </c>
       <c r="AV5">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AW5">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AX5">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AY5">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AZ5">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="BA5">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BB5">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BC5">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BD5">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="BE5">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BF5">
         <v>3.2</v>
@@ -1881,22 +1881,22 @@
         <v>98</v>
       </c>
       <c r="F6">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="G6">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="H6">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="I6">
         <v>110</v>
       </c>
       <c r="J6">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1905,22 +1905,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O6">
         <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q6">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
         <v>1.09</v>
       </c>
       <c r="S6">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -1929,10 +1929,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W6">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -1950,7 +1950,7 @@
         <v>500</v>
       </c>
       <c r="AC6">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD6">
         <v>1000</v>
@@ -1983,58 +1983,58 @@
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AQ6">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AR6">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AS6">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AT6">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AU6">
         <v>4.9</v>
       </c>
       <c r="AV6">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AW6">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AX6">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AY6">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AZ6">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BA6">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BB6">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BC6">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BD6">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="BE6">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BF6">
         <v>3.55</v>
@@ -2123,58 +2123,58 @@
         <v>99</v>
       </c>
       <c r="F7">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G7">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H7">
         <v>4.2</v>
       </c>
       <c r="I7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="O7">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P7">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="Q7">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="R7">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="S7">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U7">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X7">
         <v>32</v>
@@ -2186,16 +2186,16 @@
         <v>48</v>
       </c>
       <c r="AA7">
-        <v>470</v>
+        <v>300</v>
       </c>
       <c r="AB7">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="AC7">
         <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE7">
         <v>60</v>
@@ -2204,13 +2204,13 @@
         <v>16.5</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
         <v>17.5</v>
       </c>
       <c r="AI7">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AJ7">
         <v>26</v>
@@ -2219,31 +2219,31 @@
         <v>17</v>
       </c>
       <c r="AL7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM7">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AN7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO7">
         <v>40</v>
       </c>
       <c r="AP7">
+        <v>18.5</v>
+      </c>
+      <c r="AQ7">
         <v>20</v>
       </c>
-      <c r="AQ7">
-        <v>17</v>
-      </c>
       <c r="AR7">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="AS7">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="AT7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU7">
         <v>9.199999999999999</v>
@@ -2252,19 +2252,19 @@
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AX7">
         <v>12.5</v>
       </c>
       <c r="AY7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7">
         <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>5.9</v>
+        <v>29</v>
       </c>
       <c r="BB7">
         <v>20</v>
@@ -2273,16 +2273,16 @@
         <v>14.5</v>
       </c>
       <c r="BD7">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BE7">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="BF7">
         <v>7.2</v>
       </c>
       <c r="BG7">
-        <v>5.9</v>
+        <v>21</v>
       </c>
       <c r="BH7">
         <v>5.2</v>
@@ -2312,10 +2312,10 @@
         <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS7">
         <v>15</v>
@@ -2330,7 +2330,7 @@
         <v>34</v>
       </c>
       <c r="BW7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BX7">
         <v>38</v>
@@ -2339,10 +2339,10 @@
         <v>24</v>
       </c>
       <c r="BZ7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="s">
         <v>101</v>
@@ -2365,25 +2365,25 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H8">
+        <v>2.26</v>
+      </c>
+      <c r="I8">
         <v>2.38</v>
       </c>
-      <c r="I8">
-        <v>2.44</v>
-      </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M8">
         <v>1.06</v>
@@ -2398,25 +2398,25 @@
         <v>2.1</v>
       </c>
       <c r="Q8">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R8">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S8">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
         <v>1.7</v>
       </c>
       <c r="U8">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V8">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W8">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X8">
         <v>17.5</v>
@@ -2428,22 +2428,22 @@
         <v>17.5</v>
       </c>
       <c r="AA8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB8">
         <v>15</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8">
         <v>12</v>
       </c>
       <c r="AE8">
+        <v>24</v>
+      </c>
+      <c r="AF8">
         <v>25</v>
-      </c>
-      <c r="AF8">
-        <v>28</v>
       </c>
       <c r="AG8">
         <v>14.5</v>
@@ -2455,10 +2455,10 @@
         <v>36</v>
       </c>
       <c r="AJ8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL8">
         <v>42</v>
@@ -2467,10 +2467,10 @@
         <v>80</v>
       </c>
       <c r="AN8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP8">
         <v>14.5</v>
@@ -2506,85 +2506,85 @@
         <v>14</v>
       </c>
       <c r="BA8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC8">
+        <v>29</v>
+      </c>
+      <c r="BD8">
+        <v>34</v>
+      </c>
+      <c r="BE8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF8">
+        <v>22</v>
+      </c>
+      <c r="BG8">
+        <v>13</v>
+      </c>
+      <c r="BH8">
+        <v>4.4</v>
+      </c>
+      <c r="BI8">
+        <v>2.98</v>
+      </c>
+      <c r="BJ8">
+        <v>11</v>
+      </c>
+      <c r="BK8">
+        <v>3.65</v>
+      </c>
+      <c r="BL8">
+        <v>120</v>
+      </c>
+      <c r="BM8">
+        <v>5.3</v>
+      </c>
+      <c r="BN8">
         <v>8</v>
       </c>
-      <c r="BD8">
-        <v>32</v>
-      </c>
-      <c r="BE8">
-        <v>55</v>
-      </c>
-      <c r="BF8">
-        <v>7.6</v>
-      </c>
-      <c r="BG8">
-        <v>14</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.01</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.21</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.01</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
       <c r="BO8">
-        <v>1.21</v>
+        <v>5</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ8">
-        <v>1.21</v>
+        <v>4.6</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>1.21</v>
+        <v>4.1</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>1.21</v>
+        <v>4.3</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA8">
-        <v>1.21</v>
+        <v>4.4</v>
       </c>
       <c r="CB8" t="s">
         <v>101</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -319,7 +319,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-23 02:13:27</t>
+    <t>2026-09-23 03:30:34</t>
   </si>
 </sst>
 </file>
@@ -913,175 +913,175 @@
         <v>94</v>
       </c>
       <c r="F2">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="G2">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="K2">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>1.14</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.12</v>
+        <v>1.76</v>
       </c>
       <c r="Q2">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
+        <v>1.28</v>
+      </c>
+      <c r="S2">
+        <v>3.75</v>
+      </c>
+      <c r="T2">
+        <v>2.36</v>
+      </c>
+      <c r="U2">
+        <v>1.57</v>
+      </c>
+      <c r="V2">
         <v>1.08</v>
       </c>
-      <c r="S2">
-        <v>2.1</v>
-      </c>
-      <c r="T2">
-        <v>1.01</v>
-      </c>
-      <c r="U2">
-        <v>1.01</v>
-      </c>
-      <c r="V2">
-        <v>1.01</v>
-      </c>
       <c r="W2">
-        <v>1.85</v>
+        <v>3.15</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
@@ -1093,25 +1093,25 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU2">
         <v>1.01</v>
@@ -1129,7 +1129,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -1155,175 +1155,175 @@
         <v>95</v>
       </c>
       <c r="F3">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="G3">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="I3">
-        <v>34</v>
+        <v>5.7</v>
       </c>
       <c r="J3">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>1.12</v>
+        <v>2.74</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.12</v>
+        <v>1.55</v>
       </c>
       <c r="Q3">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V3">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="W3">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y3">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="Z3">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AA3">
         <v>500</v>
       </c>
       <c r="AB3">
-        <v>500</v>
+        <v>7.8</v>
       </c>
       <c r="AC3">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AE3">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AF3">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AG3">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AH3">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AI3">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AJ3">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AK3">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AL3">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
+        <v>26</v>
+      </c>
+      <c r="AO3">
         <v>600</v>
       </c>
-      <c r="AO3">
-        <v>500</v>
-      </c>
       <c r="AP3">
-        <v>1.18</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3">
-        <v>1.26</v>
+        <v>10</v>
       </c>
       <c r="AR3">
-        <v>1.25</v>
+        <v>4.8</v>
       </c>
       <c r="AS3">
-        <v>1.26</v>
+        <v>5.3</v>
       </c>
       <c r="AT3">
-        <v>1.23</v>
+        <v>5.3</v>
       </c>
       <c r="AU3">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>1.25</v>
+        <v>16</v>
       </c>
       <c r="AW3">
-        <v>1.26</v>
+        <v>5.2</v>
       </c>
       <c r="AX3">
-        <v>1.24</v>
+        <v>8.4</v>
       </c>
       <c r="AY3">
-        <v>1.23</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3">
-        <v>1.24</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>1.26</v>
+        <v>5.2</v>
       </c>
       <c r="BB3">
-        <v>1.25</v>
+        <v>18.5</v>
       </c>
       <c r="BC3">
-        <v>1.25</v>
+        <v>20</v>
       </c>
       <c r="BD3">
-        <v>1.26</v>
+        <v>5</v>
       </c>
       <c r="BE3">
-        <v>1.27</v>
+        <v>5.3</v>
       </c>
       <c r="BF3">
-        <v>3.85</v>
+        <v>18.5</v>
       </c>
       <c r="BG3">
-        <v>1.26</v>
+        <v>5.3</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
@@ -1335,43 +1335,43 @@
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU3">
         <v>1.01</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW3">
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1397,175 +1397,175 @@
         <v>96</v>
       </c>
       <c r="F4">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="G4">
         <v>1.5</v>
       </c>
       <c r="H4">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>1.17</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.16</v>
+        <v>1.74</v>
       </c>
       <c r="Q4">
-        <v>1.37</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>1.53</v>
+        <v>3.65</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V4">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W4">
         <v>3</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AB4">
-        <v>500</v>
+        <v>7.6</v>
       </c>
       <c r="AC4">
-        <v>95</v>
+        <v>11.5</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF4">
-        <v>500</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ4">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AK4">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AL4">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AP4">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>2.5</v>
+        <v>19</v>
       </c>
       <c r="AR4">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS4">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="AT4">
-        <v>1.06</v>
+        <v>5.2</v>
       </c>
       <c r="AU4">
-        <v>1.07</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="AW4">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX4">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="AY4">
-        <v>1.09</v>
+        <v>8</v>
       </c>
       <c r="AZ4">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA4">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB4">
-        <v>1.09</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4">
-        <v>1.09</v>
+        <v>14</v>
       </c>
       <c r="BD4">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="BE4">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF4">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK4">
         <v>1.01</v>
@@ -1577,25 +1577,25 @@
         <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ4">
         <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS4">
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BU4">
         <v>1.01</v>
@@ -1613,7 +1613,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA4">
         <v>1.01</v>
@@ -1639,175 +1639,175 @@
         <v>97</v>
       </c>
       <c r="F5">
+        <v>1.66</v>
+      </c>
+      <c r="G5">
+        <v>1.84</v>
+      </c>
+      <c r="H5">
+        <v>5.6</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>3.45</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
         <v>1.46</v>
       </c>
-      <c r="G5">
-        <v>2.3</v>
-      </c>
-      <c r="H5">
-        <v>3.25</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>2.84</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P5">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="Q5">
-        <v>1.42</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="S5">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V5">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="W5">
-        <v>1.78</v>
+        <v>2.18</v>
       </c>
       <c r="X5">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="Y5">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="Z5">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA5">
         <v>700</v>
       </c>
       <c r="AB5">
-        <v>500</v>
+        <v>7.2</v>
       </c>
       <c r="AC5">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AE5">
         <v>700</v>
       </c>
       <c r="AF5">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="AG5">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AI5">
         <v>700</v>
       </c>
       <c r="AJ5">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AK5">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AL5">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM5">
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>600</v>
+        <v>15.5</v>
       </c>
       <c r="AO5">
         <v>700</v>
       </c>
       <c r="AP5">
-        <v>1.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5">
-        <v>1.19</v>
+        <v>12.5</v>
       </c>
       <c r="AR5">
-        <v>1.19</v>
+        <v>7.2</v>
       </c>
       <c r="AS5">
-        <v>1.19</v>
+        <v>8</v>
       </c>
       <c r="AT5">
-        <v>1.16</v>
+        <v>5.8</v>
       </c>
       <c r="AU5">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>1.19</v>
+        <v>6.4</v>
       </c>
       <c r="AW5">
-        <v>1.19</v>
+        <v>7.8</v>
       </c>
       <c r="AX5">
-        <v>1.17</v>
+        <v>7.8</v>
       </c>
       <c r="AY5">
-        <v>1.16</v>
+        <v>4.7</v>
       </c>
       <c r="AZ5">
-        <v>1.17</v>
+        <v>6.2</v>
       </c>
       <c r="BA5">
-        <v>1.19</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
-        <v>1.18</v>
+        <v>5.8</v>
       </c>
       <c r="BC5">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="BD5">
-        <v>1.18</v>
+        <v>7.2</v>
       </c>
       <c r="BE5">
-        <v>1.19</v>
+        <v>8</v>
       </c>
       <c r="BF5">
+        <v>12.5</v>
+      </c>
+      <c r="BG5">
+        <v>8</v>
+      </c>
+      <c r="BH5">
         <v>3.2</v>
       </c>
-      <c r="BG5">
-        <v>1.55</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
         <v>1.01</v>
@@ -1819,31 +1819,31 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ5">
         <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS5">
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU5">
         <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW5">
         <v>1.01</v>
@@ -1855,7 +1855,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA5">
         <v>1.01</v>
@@ -1881,175 +1881,175 @@
         <v>98</v>
       </c>
       <c r="F6">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="G6">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="H6">
-        <v>3.75</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
-        <v>110</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q6">
+        <v>2.2</v>
+      </c>
+      <c r="R6">
+        <v>1.25</v>
+      </c>
+      <c r="S6">
+        <v>4.1</v>
+      </c>
+      <c r="T6">
+        <v>2.18</v>
+      </c>
+      <c r="U6">
         <v>1.65</v>
       </c>
-      <c r="R6">
-        <v>1.09</v>
-      </c>
-      <c r="S6">
-        <v>1.66</v>
-      </c>
-      <c r="T6">
-        <v>1.01</v>
-      </c>
-      <c r="U6">
-        <v>1.01</v>
-      </c>
       <c r="V6">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W6">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AB6">
-        <v>500</v>
+        <v>6.8</v>
       </c>
       <c r="AC6">
-        <v>95</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF6">
-        <v>500</v>
+        <v>8.6</v>
       </c>
       <c r="AG6">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ6">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AK6">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AL6">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN6">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AP6">
-        <v>1.17</v>
+        <v>8.6</v>
       </c>
       <c r="AQ6">
-        <v>1.17</v>
+        <v>6</v>
       </c>
       <c r="AR6">
-        <v>1.17</v>
+        <v>7.6</v>
       </c>
       <c r="AS6">
-        <v>1.17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6">
-        <v>1.14</v>
+        <v>4.8</v>
       </c>
       <c r="AU6">
         <v>4.9</v>
       </c>
       <c r="AV6">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="AW6">
-        <v>1.17</v>
+        <v>8</v>
       </c>
       <c r="AX6">
-        <v>1.15</v>
+        <v>4.2</v>
       </c>
       <c r="AY6">
-        <v>1.14</v>
+        <v>7.6</v>
       </c>
       <c r="AZ6">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="BA6">
-        <v>1.17</v>
+        <v>8</v>
       </c>
       <c r="BB6">
-        <v>1.16</v>
+        <v>10.5</v>
       </c>
       <c r="BC6">
-        <v>1.16</v>
+        <v>6</v>
       </c>
       <c r="BD6">
-        <v>1.17</v>
+        <v>7.2</v>
       </c>
       <c r="BE6">
-        <v>1.17</v>
+        <v>8</v>
       </c>
       <c r="BF6">
-        <v>3.55</v>
+        <v>10</v>
       </c>
       <c r="BG6">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
@@ -2061,25 +2061,25 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ6">
         <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU6">
         <v>1.01</v>
@@ -2097,7 +2097,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2123,22 +2123,22 @@
         <v>99</v>
       </c>
       <c r="F7">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G7">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J7">
         <v>4.2</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L7">
         <v>1.27</v>
@@ -2147,7 +2147,7 @@
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>1.17</v>
@@ -2156,7 +2156,7 @@
         <v>2.74</v>
       </c>
       <c r="Q7">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R7">
         <v>1.69</v>
@@ -2168,13 +2168,13 @@
         <v>1.47</v>
       </c>
       <c r="U7">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X7">
         <v>32</v>
@@ -2186,19 +2186,19 @@
         <v>48</v>
       </c>
       <c r="AA7">
-        <v>300</v>
+        <v>470</v>
       </c>
       <c r="AB7">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="AC7">
         <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AE7">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF7">
         <v>16.5</v>
@@ -2207,10 +2207,10 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI7">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AJ7">
         <v>26</v>
@@ -2222,37 +2222,37 @@
         <v>28</v>
       </c>
       <c r="AM7">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO7">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="AP7">
         <v>18.5</v>
       </c>
       <c r="AQ7">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AR7">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="AS7">
-        <v>55</v>
+        <v>7.6</v>
       </c>
       <c r="AT7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU7">
         <v>9.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="AX7">
         <v>12.5</v>
@@ -2264,7 +2264,7 @@
         <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="BB7">
         <v>20</v>
@@ -2273,16 +2273,16 @@
         <v>14.5</v>
       </c>
       <c r="BD7">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="BE7">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="BF7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG7">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BH7">
         <v>5.2</v>
@@ -2291,7 +2291,7 @@
         <v>3.7</v>
       </c>
       <c r="BJ7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
         <v>6.8</v>
@@ -2300,7 +2300,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BN7">
         <v>5.7</v>
@@ -2309,10 +2309,10 @@
         <v>4</v>
       </c>
       <c r="BP7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR7">
         <v>23</v>
@@ -2321,13 +2321,13 @@
         <v>15</v>
       </c>
       <c r="BT7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW7">
         <v>22</v>
@@ -2365,25 +2365,25 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G8">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H8">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M8">
         <v>1.06</v>
@@ -2404,19 +2404,19 @@
         <v>1.45</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T8">
         <v>1.7</v>
       </c>
       <c r="U8">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X8">
         <v>17.5</v>
@@ -2440,10 +2440,10 @@
         <v>12</v>
       </c>
       <c r="AE8">
+        <v>25</v>
+      </c>
+      <c r="AF8">
         <v>24</v>
-      </c>
-      <c r="AF8">
-        <v>25</v>
       </c>
       <c r="AG8">
         <v>14.5</v>
@@ -2455,7 +2455,7 @@
         <v>36</v>
       </c>
       <c r="AJ8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK8">
         <v>36</v>
@@ -2467,10 +2467,10 @@
         <v>80</v>
       </c>
       <c r="AN8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP8">
         <v>14.5</v>
@@ -2482,7 +2482,7 @@
         <v>13.5</v>
       </c>
       <c r="AS8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AT8">
         <v>13</v>
@@ -2506,22 +2506,22 @@
         <v>14</v>
       </c>
       <c r="BA8">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="BB8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BC8">
         <v>29</v>
       </c>
       <c r="BD8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE8">
-        <v>9.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BF8">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BG8">
         <v>13</v>
@@ -2530,61 +2530,61 @@
         <v>4.4</v>
       </c>
       <c r="BI8">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ8">
         <v>11</v>
       </c>
       <c r="BK8">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BL8">
         <v>120</v>
       </c>
       <c r="BM8">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BN8">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BO8">
         <v>5</v>
       </c>
       <c r="BP8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BQ8">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS8">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BT8">
         <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV8">
         <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BX8">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BY8">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BZ8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA8">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB8" t="s">
         <v>101</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -319,7 +319,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-23 03:30:34</t>
+    <t>2026-09-23 05:41:42</t>
   </si>
 </sst>
 </file>
@@ -919,7 +919,7 @@
         <v>1.46</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I2">
         <v>15</v>
@@ -958,13 +958,13 @@
         <v>2.36</v>
       </c>
       <c r="U2">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
         <v>1.08</v>
       </c>
       <c r="W2">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="X2">
         <v>15.5</v>
@@ -973,13 +973,13 @@
         <v>34</v>
       </c>
       <c r="Z2">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC2">
         <v>13</v>
@@ -988,10 +988,10 @@
         <v>55</v>
       </c>
       <c r="AE2">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1000,7 +1000,7 @@
         <v>42</v>
       </c>
       <c r="AI2">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
         <v>13</v>
@@ -1012,67 +1012,67 @@
         <v>65</v>
       </c>
       <c r="AM2">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AR2">
+        <v>5.6</v>
+      </c>
+      <c r="AS2">
+        <v>5.6</v>
+      </c>
+      <c r="AT2">
+        <v>3.05</v>
+      </c>
+      <c r="AU2">
+        <v>3.95</v>
+      </c>
+      <c r="AV2">
+        <v>5.1</v>
+      </c>
+      <c r="AW2">
+        <v>5.6</v>
+      </c>
+      <c r="AX2">
+        <v>3.25</v>
+      </c>
+      <c r="AY2">
+        <v>3.9</v>
+      </c>
+      <c r="AZ2">
         <v>5</v>
       </c>
-      <c r="AS2">
+      <c r="BA2">
+        <v>5.6</v>
+      </c>
+      <c r="BB2">
+        <v>3.95</v>
+      </c>
+      <c r="BC2">
+        <v>4.4</v>
+      </c>
+      <c r="BD2">
         <v>5.2</v>
       </c>
-      <c r="AT2">
-        <v>5</v>
-      </c>
-      <c r="AU2">
-        <v>8.6</v>
-      </c>
-      <c r="AV2">
-        <v>4.8</v>
-      </c>
-      <c r="AW2">
-        <v>5.2</v>
-      </c>
-      <c r="AX2">
-        <v>3.2</v>
-      </c>
-      <c r="AY2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ2">
-        <v>4.7</v>
-      </c>
-      <c r="BA2">
-        <v>5.1</v>
-      </c>
-      <c r="BB2">
-        <v>3.75</v>
-      </c>
-      <c r="BC2">
-        <v>4.2</v>
-      </c>
-      <c r="BD2">
-        <v>4.8</v>
-      </c>
       <c r="BE2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF2">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BG2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
@@ -1084,13 +1084,13 @@
         <v>14.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2">
         <v>3.7</v>
@@ -1102,37 +1102,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT2">
         <v>15</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
         <v>20</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB2" t="s">
         <v>101</v>
@@ -1155,22 +1155,22 @@
         <v>95</v>
       </c>
       <c r="F3">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="G3">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="H3">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L3">
         <v>1.53</v>
@@ -1179,76 +1179,76 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
         <v>4.8</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA3">
         <v>500</v>
       </c>
       <c r="AB3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE3">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AF3">
+        <v>11</v>
+      </c>
+      <c r="AG3">
         <v>12.5</v>
-      </c>
-      <c r="AG3">
-        <v>13</v>
       </c>
       <c r="AH3">
         <v>28</v>
       </c>
       <c r="AI3">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AJ3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AK3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL3">
         <v>65</v>
@@ -1257,64 +1257,64 @@
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO3">
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR3">
-        <v>4.8</v>
+        <v>21</v>
       </c>
       <c r="AS3">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AT3">
         <v>5.3</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AW3">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA3">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC3">
         <v>20</v>
       </c>
       <c r="BD3">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="BE3">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BF3">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG3">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BH3">
         <v>3.1</v>
@@ -1323,58 +1323,58 @@
         <v>2.36</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BO3">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BP3">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BT3">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BX3">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BZ3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="CB3" t="s">
         <v>101</v>
@@ -1397,226 +1397,226 @@
         <v>96</v>
       </c>
       <c r="F4">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G4">
         <v>1.5</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q4">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S4">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="U4">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="V4">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W4">
         <v>3</v>
       </c>
       <c r="X4">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y4">
         <v>28</v>
       </c>
       <c r="Z4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AC4">
         <v>11.5</v>
       </c>
       <c r="AD4">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AE4">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI4">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AJ4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL4">
         <v>130</v>
       </c>
       <c r="AM4">
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="AN4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AO4">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="AQ4">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="AR4">
         <v>5.3</v>
       </c>
       <c r="AS4">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT4">
+        <v>2.96</v>
+      </c>
+      <c r="AU4">
+        <v>3.65</v>
+      </c>
+      <c r="AV4">
+        <v>4.8</v>
+      </c>
+      <c r="AW4">
+        <v>5.3</v>
+      </c>
+      <c r="AX4">
+        <v>3.4</v>
+      </c>
+      <c r="AY4">
+        <v>4.8</v>
+      </c>
+      <c r="AZ4">
+        <v>4.7</v>
+      </c>
+      <c r="BA4">
         <v>5.2</v>
       </c>
-      <c r="AU4">
-        <v>7.8</v>
-      </c>
-      <c r="AV4">
+      <c r="BB4">
+        <v>4.3</v>
+      </c>
+      <c r="BC4">
         <v>4.9</v>
       </c>
-      <c r="AW4">
-        <v>5.4</v>
-      </c>
-      <c r="AX4">
-        <v>6</v>
-      </c>
-      <c r="AY4">
-        <v>8</v>
-      </c>
-      <c r="AZ4">
-        <v>4.8</v>
-      </c>
-      <c r="BA4">
-        <v>5.4</v>
-      </c>
-      <c r="BB4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC4">
-        <v>14</v>
-      </c>
       <c r="BD4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE4">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="BG4">
         <v>10.5</v>
       </c>
       <c r="BH4">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BI4">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN4">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BO4">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BP4">
         <v>11</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BR4">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT4">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BZ4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="CB4" t="s">
         <v>101</v>
@@ -1639,226 +1639,226 @@
         <v>97</v>
       </c>
       <c r="F5">
-        <v>1.66</v>
+        <v>2.38</v>
       </c>
       <c r="G5">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="H5">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="J5">
+        <v>2.98</v>
+      </c>
+      <c r="K5">
         <v>3.45</v>
       </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="O5">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="P5">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="R5">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="T5">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="Y5">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z5">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="AA5">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="AB5">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD5">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="AE5">
-        <v>700</v>
+        <v>60</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH5">
         <v>27</v>
       </c>
       <c r="AI5">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="AJ5">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AK5">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AL5">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM5">
-        <v>580</v>
+        <v>210</v>
       </c>
       <c r="AN5">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="AO5">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="AP5">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5">
+        <v>9</v>
+      </c>
+      <c r="AR5">
+        <v>17</v>
+      </c>
+      <c r="AS5">
+        <v>7.8</v>
+      </c>
+      <c r="AT5">
+        <v>6.8</v>
+      </c>
+      <c r="AU5">
+        <v>4.9</v>
+      </c>
+      <c r="AV5">
         <v>12.5</v>
       </c>
-      <c r="AR5">
-        <v>7.2</v>
-      </c>
-      <c r="AS5">
-        <v>8</v>
-      </c>
-      <c r="AT5">
-        <v>5.8</v>
-      </c>
-      <c r="AU5">
-        <v>7.2</v>
-      </c>
-      <c r="AV5">
-        <v>6.4</v>
-      </c>
       <c r="AW5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BA5">
         <v>7.8</v>
       </c>
       <c r="BB5">
-        <v>5.8</v>
+        <v>25</v>
       </c>
       <c r="BC5">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BD5">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="BG5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH5">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="BI5">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BN5">
+        <v>5.4</v>
+      </c>
+      <c r="BO5">
         <v>4.3</v>
       </c>
-      <c r="BO5">
-        <v>3.3</v>
-      </c>
       <c r="BP5">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR5">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BT5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX5">
+        <v>65</v>
+      </c>
+      <c r="BY5">
+        <v>6.2</v>
+      </c>
+      <c r="BZ5">
         <v>1000</v>
       </c>
-      <c r="BY5">
-        <v>1.01</v>
-      </c>
-      <c r="BZ5">
-        <v>32</v>
-      </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="s">
         <v>101</v>
@@ -1881,61 +1881,61 @@
         <v>98</v>
       </c>
       <c r="F6">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G6">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="P6">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S6">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="T6">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W6">
         <v>2.52</v>
       </c>
       <c r="X6">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y6">
         <v>22</v>
@@ -1944,163 +1944,163 @@
         <v>85</v>
       </c>
       <c r="AA6">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="AB6">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE6">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AF6">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI6">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AJ6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AM6">
         <v>580</v>
       </c>
       <c r="AN6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO6">
-        <v>360</v>
+        <v>460</v>
       </c>
       <c r="AP6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ6">
+        <v>6.2</v>
+      </c>
+      <c r="AR6">
+        <v>7.8</v>
+      </c>
+      <c r="AS6">
+        <v>8.4</v>
+      </c>
+      <c r="AT6">
+        <v>5</v>
+      </c>
+      <c r="AU6">
+        <v>8</v>
+      </c>
+      <c r="AV6">
+        <v>7</v>
+      </c>
+      <c r="AW6">
+        <v>8.4</v>
+      </c>
+      <c r="AX6">
+        <v>6.4</v>
+      </c>
+      <c r="AY6">
+        <v>9</v>
+      </c>
+      <c r="AZ6">
+        <v>7</v>
+      </c>
+      <c r="BA6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB6">
+        <v>11.5</v>
+      </c>
+      <c r="BC6">
+        <v>17.5</v>
+      </c>
+      <c r="BD6">
+        <v>7.6</v>
+      </c>
+      <c r="BE6">
         <v>8.6</v>
       </c>
-      <c r="AQ6">
-        <v>6</v>
-      </c>
-      <c r="AR6">
-        <v>7.6</v>
-      </c>
-      <c r="AS6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT6">
-        <v>4.8</v>
-      </c>
-      <c r="AU6">
-        <v>4.9</v>
-      </c>
-      <c r="AV6">
-        <v>6.6</v>
-      </c>
-      <c r="AW6">
-        <v>8</v>
-      </c>
-      <c r="AX6">
-        <v>4.2</v>
-      </c>
-      <c r="AY6">
-        <v>7.6</v>
-      </c>
-      <c r="AZ6">
-        <v>6.6</v>
-      </c>
-      <c r="BA6">
-        <v>8</v>
-      </c>
-      <c r="BB6">
+      <c r="BF6">
         <v>10.5</v>
       </c>
-      <c r="BC6">
-        <v>6</v>
-      </c>
-      <c r="BD6">
-        <v>7.2</v>
-      </c>
-      <c r="BE6">
-        <v>8</v>
-      </c>
-      <c r="BF6">
-        <v>10</v>
-      </c>
       <c r="BG6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH6">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="BI6">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BJ6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN6">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BO6">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BP6">
         <v>11.5</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BT6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="s">
         <v>101</v>
@@ -2123,19 +2123,19 @@
         <v>99</v>
       </c>
       <c r="F7">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="G7">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H7">
+        <v>4.4</v>
+      </c>
+      <c r="I7">
+        <v>4.8</v>
+      </c>
+      <c r="J7">
         <v>4.3</v>
-      </c>
-      <c r="I7">
-        <v>4.6</v>
-      </c>
-      <c r="J7">
-        <v>4.2</v>
       </c>
       <c r="K7">
         <v>4.6</v>
@@ -2147,73 +2147,73 @@
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O7">
         <v>1.17</v>
       </c>
       <c r="P7">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q7">
         <v>1.53</v>
       </c>
       <c r="R7">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T7">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="U7">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V7">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y7">
         <v>26</v>
       </c>
       <c r="Z7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA7">
-        <v>470</v>
+        <v>300</v>
       </c>
       <c r="AB7">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD7">
         <v>21</v>
       </c>
       <c r="AE7">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AF7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI7">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AJ7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK7">
         <v>17</v>
@@ -2222,73 +2222,73 @@
         <v>28</v>
       </c>
       <c r="AM7">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AN7">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO7">
-        <v>250</v>
+        <v>65</v>
       </c>
       <c r="AP7">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AQ7">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AR7">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="AS7">
-        <v>7.6</v>
+        <v>60</v>
       </c>
       <c r="AT7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV7">
         <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AX7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ7">
         <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="BB7">
+        <v>18.5</v>
+      </c>
+      <c r="BC7">
+        <v>14</v>
+      </c>
+      <c r="BD7">
         <v>20</v>
       </c>
-      <c r="BC7">
-        <v>14.5</v>
-      </c>
-      <c r="BD7">
-        <v>13.5</v>
-      </c>
       <c r="BE7">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="BF7">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG7">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BH7">
         <v>5.2</v>
       </c>
       <c r="BI7">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
@@ -2303,16 +2303,16 @@
         <v>55</v>
       </c>
       <c r="BN7">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO7">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP7">
         <v>13</v>
       </c>
       <c r="BQ7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR7">
         <v>23</v>
@@ -2321,25 +2321,25 @@
         <v>15</v>
       </c>
       <c r="BT7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV7">
         <v>36</v>
       </c>
       <c r="BW7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BX7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BZ7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA7">
         <v>10</v>
@@ -2365,19 +2365,19 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="G8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H8">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="I8">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K8">
         <v>3.8</v>
@@ -2392,40 +2392,40 @@
         <v>4.2</v>
       </c>
       <c r="O8">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P8">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q8">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R8">
         <v>1.45</v>
       </c>
       <c r="S8">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T8">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V8">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W8">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA8">
         <v>32</v>
@@ -2443,22 +2443,22 @@
         <v>25</v>
       </c>
       <c r="AF8">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AG8">
         <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL8">
         <v>42</v>
@@ -2467,10 +2467,10 @@
         <v>80</v>
       </c>
       <c r="AN8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP8">
         <v>14.5</v>
@@ -2485,7 +2485,7 @@
         <v>26</v>
       </c>
       <c r="AT8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU8">
         <v>7.6</v>
@@ -2506,22 +2506,22 @@
         <v>14</v>
       </c>
       <c r="BA8">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="BB8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE8">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BF8">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="BG8">
         <v>13</v>
@@ -2533,34 +2533,34 @@
         <v>3</v>
       </c>
       <c r="BJ8">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BK8">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BL8">
         <v>120</v>
       </c>
       <c r="BM8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN8">
         <v>6.6</v>
-      </c>
-      <c r="BN8">
-        <v>6.8</v>
       </c>
       <c r="BO8">
         <v>5</v>
       </c>
       <c r="BP8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ8">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BR8">
         <v>34</v>
       </c>
       <c r="BS8">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BT8">
         <v>5.5</v>
@@ -2569,22 +2569,22 @@
         <v>4.2</v>
       </c>
       <c r="BV8">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BW8">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BX8">
         <v>28</v>
       </c>
       <c r="BY8">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ8">
         <v>22</v>
       </c>
       <c r="CA8">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="s">
         <v>101</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -319,7 +319,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-23 05:41:42</t>
+    <t>2026-09-23 07:53:17</t>
   </si>
 </sst>
 </file>
@@ -913,22 +913,22 @@
         <v>94</v>
       </c>
       <c r="F2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H2">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J2">
         <v>4.4</v>
       </c>
       <c r="K2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L2">
         <v>1.37</v>
@@ -937,34 +937,34 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
         <v>3.75</v>
       </c>
       <c r="T2">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="V2">
         <v>1.08</v>
       </c>
       <c r="W2">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="X2">
         <v>15.5</v>
@@ -973,7 +973,7 @@
         <v>34</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -982,16 +982,16 @@
         <v>6.6</v>
       </c>
       <c r="AC2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD2">
         <v>55</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AF2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1000,7 +1000,7 @@
         <v>42</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ2">
         <v>13</v>
@@ -1012,76 +1012,76 @@
         <v>65</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AN2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AR2">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AS2">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT2">
-        <v>3.05</v>
+        <v>5.3</v>
       </c>
       <c r="AU2">
-        <v>3.95</v>
+        <v>9.6</v>
       </c>
       <c r="AV2">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AW2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX2">
-        <v>3.25</v>
+        <v>5.9</v>
       </c>
       <c r="AY2">
-        <v>3.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BA2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB2">
-        <v>3.95</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC2">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="BD2">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF2">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="BG2">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH2">
         <v>3.45</v>
       </c>
       <c r="BI2">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK2">
         <v>6</v>
@@ -1093,13 +1093,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BN2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BO2">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BP2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ2">
         <v>4.8</v>
@@ -1111,7 +1111,7 @@
         <v>7.8</v>
       </c>
       <c r="BT2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BU2">
         <v>6</v>
@@ -1120,7 +1120,7 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1155,85 +1155,85 @@
         <v>95</v>
       </c>
       <c r="F3">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="G3">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J3">
         <v>3.15</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W3">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA3">
         <v>500</v>
       </c>
       <c r="AB3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3">
         <v>26</v>
       </c>
       <c r="AE3">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
@@ -1245,10 +1245,10 @@
         <v>500</v>
       </c>
       <c r="AJ3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL3">
         <v>65</v>
@@ -1257,19 +1257,19 @@
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO3">
-        <v>600</v>
+        <v>240</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR3">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AS3">
         <v>6.6</v>
@@ -1278,49 +1278,49 @@
         <v>5.3</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB3">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD3">
         <v>23</v>
       </c>
       <c r="BE3">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BF3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3">
         <v>14</v>
@@ -1332,49 +1332,49 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BN3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BQ3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR3">
         <v>44</v>
       </c>
       <c r="BS3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BT3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BW3">
+        <v>5.5</v>
+      </c>
+      <c r="BX3">
+        <v>95</v>
+      </c>
+      <c r="BY3">
         <v>5.6</v>
       </c>
-      <c r="BX3">
-        <v>90</v>
-      </c>
-      <c r="BY3">
-        <v>5.7</v>
-      </c>
       <c r="BZ3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="CA3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB3" t="s">
         <v>101</v>
@@ -1397,25 +1397,25 @@
         <v>96</v>
       </c>
       <c r="F4">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="G4">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
         <v>13</v>
       </c>
       <c r="J4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.08</v>
@@ -1424,13 +1424,13 @@
         <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
         <v>1.69</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
         <v>1.24</v>
@@ -1439,13 +1439,13 @@
         <v>4.2</v>
       </c>
       <c r="T4">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="U4">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="V4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W4">
         <v>3</v>
@@ -1457,7 +1457,7 @@
         <v>28</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1472,7 +1472,7 @@
         <v>48</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AF4">
         <v>8.199999999999999</v>
@@ -1505,55 +1505,55 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS4">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT4">
-        <v>2.96</v>
+        <v>4.8</v>
       </c>
       <c r="AU4">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="AV4">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AW4">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX4">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY4">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BA4">
+        <v>5.5</v>
+      </c>
+      <c r="BB4">
+        <v>10</v>
+      </c>
+      <c r="BC4">
+        <v>16</v>
+      </c>
+      <c r="BD4">
         <v>5.2</v>
       </c>
-      <c r="BB4">
-        <v>4.3</v>
-      </c>
-      <c r="BC4">
-        <v>4.9</v>
-      </c>
-      <c r="BD4">
-        <v>4.9</v>
-      </c>
       <c r="BE4">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF4">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4">
         <v>10.5</v>
@@ -1639,226 +1639,226 @@
         <v>97</v>
       </c>
       <c r="F5">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="G5">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I5">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="J5">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="L5">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="O5">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="P5">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q5">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S5">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="X5">
-        <v>17.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y5">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Z5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA5">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AB5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH5">
         <v>27</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AK5">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AM5">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AN5">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AO5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP5">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AQ5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>46</v>
       </c>
       <c r="AT5">
         <v>6.8</v>
       </c>
       <c r="AU5">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="AX5">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AY5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA5">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BB5">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BC5">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BD5">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BE5">
-        <v>8.199999999999999</v>
+        <v>110</v>
       </c>
       <c r="BF5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BG5">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BH5">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
         <v>101</v>
@@ -1881,22 +1881,22 @@
         <v>98</v>
       </c>
       <c r="F6">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G6">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>10.5</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L6">
         <v>1.5</v>
@@ -1908,7 +1908,7 @@
         <v>2.78</v>
       </c>
       <c r="O6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P6">
         <v>1.66</v>
@@ -1923,16 +1923,16 @@
         <v>4.6</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="V6">
         <v>1.11</v>
       </c>
       <c r="W6">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X6">
         <v>11</v>
@@ -1989,7 +1989,7 @@
         <v>460</v>
       </c>
       <c r="AP6">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AQ6">
         <v>6.2</v>
@@ -2004,7 +2004,7 @@
         <v>5</v>
       </c>
       <c r="AU6">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="AV6">
         <v>7</v>
@@ -2013,10 +2013,10 @@
         <v>8.4</v>
       </c>
       <c r="AX6">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AY6">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="AZ6">
         <v>7</v>
@@ -2025,10 +2025,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB6">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC6">
-        <v>17.5</v>
+        <v>7.6</v>
       </c>
       <c r="BD6">
         <v>7.6</v>
@@ -2037,7 +2037,7 @@
         <v>8.6</v>
       </c>
       <c r="BF6">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG6">
         <v>8.4</v>
@@ -2123,61 +2123,61 @@
         <v>99</v>
       </c>
       <c r="F7">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="G7">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="H7">
+        <v>4.6</v>
+      </c>
+      <c r="I7">
+        <v>4.9</v>
+      </c>
+      <c r="J7">
         <v>4.4</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>4.8</v>
-      </c>
-      <c r="J7">
-        <v>4.3</v>
-      </c>
-      <c r="K7">
-        <v>4.6</v>
       </c>
       <c r="L7">
         <v>1.27</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
         <v>6.2</v>
       </c>
       <c r="O7">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P7">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q7">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R7">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S7">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="T7">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U7">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
         <v>1.26</v>
       </c>
       <c r="W7">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y7">
         <v>26</v>
@@ -2192,10 +2192,10 @@
         <v>14.5</v>
       </c>
       <c r="AC7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE7">
         <v>55</v>
@@ -2207,28 +2207,28 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AK7">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AL7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN7">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP7">
         <v>23</v>
@@ -2237,22 +2237,22 @@
         <v>21</v>
       </c>
       <c r="AR7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX7">
         <v>12</v>
@@ -2261,16 +2261,16 @@
         <v>9</v>
       </c>
       <c r="AZ7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA7">
         <v>32</v>
       </c>
       <c r="BB7">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD7">
         <v>20</v>
@@ -2279,16 +2279,16 @@
         <v>46</v>
       </c>
       <c r="BF7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG7">
         <v>23</v>
       </c>
       <c r="BH7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
@@ -2303,13 +2303,13 @@
         <v>55</v>
       </c>
       <c r="BN7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO7">
         <v>4.4</v>
       </c>
       <c r="BP7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ7">
         <v>8.4</v>
@@ -2333,7 +2333,7 @@
         <v>23</v>
       </c>
       <c r="BX7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY7">
         <v>25</v>
@@ -2365,40 +2365,40 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G8">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H8">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I8">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O8">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P8">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q8">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R8">
         <v>1.45</v>
@@ -2407,97 +2407,97 @@
         <v>3</v>
       </c>
       <c r="T8">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="U8">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="V8">
         <v>1.74</v>
       </c>
       <c r="W8">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X8">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z8">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AA8">
         <v>32</v>
       </c>
       <c r="AB8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD8">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF8">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI8">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AJ8">
         <v>60</v>
       </c>
       <c r="AK8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM8">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ8">
         <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS8">
         <v>26</v>
       </c>
       <c r="AT8">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV8">
         <v>10</v>
       </c>
       <c r="AW8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY8">
         <v>12</v>
@@ -2509,82 +2509,82 @@
         <v>28</v>
       </c>
       <c r="BB8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC8">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="BD8">
         <v>34</v>
       </c>
       <c r="BE8">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="BF8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BG8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH8">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BI8">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ8">
         <v>9.4</v>
       </c>
       <c r="BK8">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BL8">
         <v>120</v>
       </c>
       <c r="BM8">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BO8">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BP8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BQ8">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BR8">
         <v>34</v>
       </c>
       <c r="BS8">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT8">
         <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW8">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BX8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY8">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
         <v>22</v>
       </c>
       <c r="CA8">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
         <v>101</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -319,7 +319,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-23 07:53:17</t>
+    <t>2026-09-23 10:07:11</t>
   </si>
 </sst>
 </file>
@@ -913,13 +913,13 @@
         <v>94</v>
       </c>
       <c r="F2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G2">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I2">
         <v>14.5</v>
@@ -928,46 +928,46 @@
         <v>4.4</v>
       </c>
       <c r="K2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L2">
         <v>1.37</v>
       </c>
       <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
+        <v>3.35</v>
+      </c>
+      <c r="O2">
+        <v>1.33</v>
+      </c>
+      <c r="P2">
+        <v>1.81</v>
+      </c>
+      <c r="Q2">
+        <v>1.98</v>
+      </c>
+      <c r="R2">
+        <v>1.3</v>
+      </c>
+      <c r="S2">
+        <v>3.7</v>
+      </c>
+      <c r="T2">
+        <v>2.32</v>
+      </c>
+      <c r="U2">
+        <v>1.6</v>
+      </c>
+      <c r="V2">
         <v>1.07</v>
       </c>
-      <c r="N2">
-        <v>3.25</v>
-      </c>
-      <c r="O2">
-        <v>1.36</v>
-      </c>
-      <c r="P2">
-        <v>1.75</v>
-      </c>
-      <c r="Q2">
-        <v>2.04</v>
-      </c>
-      <c r="R2">
-        <v>1.29</v>
-      </c>
-      <c r="S2">
-        <v>3.75</v>
-      </c>
-      <c r="T2">
-        <v>2.42</v>
-      </c>
-      <c r="U2">
-        <v>1.55</v>
-      </c>
-      <c r="V2">
-        <v>1.08</v>
-      </c>
       <c r="W2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="X2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y2">
         <v>34</v>
@@ -979,7 +979,7 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC2">
         <v>13.5</v>
@@ -988,19 +988,19 @@
         <v>55</v>
       </c>
       <c r="AE2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AF2">
         <v>7.4</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AJ2">
         <v>13</v>
@@ -1012,73 +1012,73 @@
         <v>65</v>
       </c>
       <c r="AM2">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AN2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AR2">
+        <v>6.4</v>
+      </c>
+      <c r="AS2">
+        <v>6.6</v>
+      </c>
+      <c r="AT2">
+        <v>5.5</v>
+      </c>
+      <c r="AU2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV2">
         <v>6</v>
       </c>
-      <c r="AS2">
-        <v>6.4</v>
-      </c>
-      <c r="AT2">
-        <v>5.3</v>
-      </c>
-      <c r="AU2">
-        <v>9.6</v>
-      </c>
-      <c r="AV2">
-        <v>5.7</v>
-      </c>
       <c r="AW2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC2">
         <v>15</v>
       </c>
       <c r="BD2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI2">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
         <v>15</v>
@@ -1096,7 +1096,7 @@
         <v>3.65</v>
       </c>
       <c r="BO2">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BP2">
         <v>9</v>
@@ -1111,7 +1111,7 @@
         <v>7.8</v>
       </c>
       <c r="BT2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BU2">
         <v>6</v>
@@ -1129,7 +1129,7 @@
         <v>9.4</v>
       </c>
       <c r="BZ2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA2">
         <v>6.6</v>
@@ -1155,67 +1155,67 @@
         <v>95</v>
       </c>
       <c r="F3">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="G3">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="H3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W3">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA3">
         <v>500</v>
@@ -1224,31 +1224,31 @@
         <v>7.2</v>
       </c>
       <c r="AC3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AE3">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AF3">
         <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI3">
         <v>500</v>
       </c>
       <c r="AJ3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL3">
         <v>65</v>
@@ -1257,37 +1257,37 @@
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO3">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AP3">
         <v>8</v>
       </c>
       <c r="AQ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AS3">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AT3">
         <v>5.3</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY3">
         <v>8.800000000000001</v>
@@ -1296,37 +1296,37 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BB3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD3">
         <v>23</v>
       </c>
       <c r="BE3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF3">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BH3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3">
         <v>14</v>
       </c>
       <c r="BK3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1335,28 +1335,28 @@
         <v>5.8</v>
       </c>
       <c r="BN3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3">
         <v>4.3</v>
       </c>
       <c r="BR3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS3">
         <v>5.2</v>
       </c>
       <c r="BT3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV3">
         <v>75</v>
@@ -1371,7 +1371,7 @@
         <v>5.6</v>
       </c>
       <c r="BZ3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA3">
         <v>5.2</v>
@@ -1397,43 +1397,43 @@
         <v>96</v>
       </c>
       <c r="F4">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="G4">
         <v>1.49</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4">
         <v>13</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
         <v>4.2</v>
@@ -1490,13 +1490,13 @@
         <v>14.5</v>
       </c>
       <c r="AK4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4">
         <v>130</v>
       </c>
       <c r="AM4">
-        <v>360</v>
+        <v>790</v>
       </c>
       <c r="AN4">
         <v>12</v>
@@ -1511,7 +1511,7 @@
         <v>19.5</v>
       </c>
       <c r="AR4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS4">
         <v>5.7</v>
@@ -1535,10 +1535,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BA4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB4">
         <v>10</v>
@@ -1547,7 +1547,7 @@
         <v>16</v>
       </c>
       <c r="BD4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE4">
         <v>5.6</v>
@@ -1639,22 +1639,22 @@
         <v>97</v>
       </c>
       <c r="F5">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="G5">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="H5">
+        <v>2.38</v>
+      </c>
+      <c r="I5">
+        <v>2.54</v>
+      </c>
+      <c r="J5">
         <v>3.05</v>
       </c>
-      <c r="I5">
-        <v>3.35</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
       <c r="K5">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
         <v>1.6</v>
@@ -1663,19 +1663,19 @@
         <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="O5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P5">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Q5">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S5">
         <v>5.7</v>
@@ -1684,181 +1684,181 @@
         <v>2.12</v>
       </c>
       <c r="U5">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="W5">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="X5">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y5">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z5">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AA5">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AB5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AE5">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AF5">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AG5">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AH5">
         <v>27</v>
       </c>
       <c r="AI5">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AK5">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AL5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AM5">
-        <v>240</v>
+        <v>790</v>
       </c>
       <c r="AN5">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AO5">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AP5">
         <v>7</v>
       </c>
       <c r="AQ5">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AR5">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AS5">
-        <v>46</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU5">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV5">
+        <v>11</v>
+      </c>
+      <c r="AW5">
+        <v>29</v>
+      </c>
+      <c r="AX5">
+        <v>17.5</v>
+      </c>
+      <c r="AY5">
+        <v>14</v>
+      </c>
+      <c r="AZ5">
+        <v>22</v>
+      </c>
+      <c r="BA5">
+        <v>11</v>
+      </c>
+      <c r="BB5">
+        <v>55</v>
+      </c>
+      <c r="BC5">
+        <v>11</v>
+      </c>
+      <c r="BD5">
         <v>11.5</v>
       </c>
-      <c r="AW5">
-        <v>38</v>
-      </c>
-      <c r="AX5">
-        <v>14</v>
-      </c>
-      <c r="AY5">
+      <c r="BE5">
+        <v>11.5</v>
+      </c>
+      <c r="BF5">
+        <v>11</v>
+      </c>
+      <c r="BG5">
+        <v>26</v>
+      </c>
+      <c r="BH5">
+        <v>2.7</v>
+      </c>
+      <c r="BI5">
+        <v>2.36</v>
+      </c>
+      <c r="BJ5">
         <v>12</v>
       </c>
-      <c r="AZ5">
-        <v>21</v>
-      </c>
-      <c r="BA5">
-        <v>44</v>
-      </c>
-      <c r="BB5">
-        <v>34</v>
-      </c>
-      <c r="BC5">
-        <v>32</v>
-      </c>
-      <c r="BD5">
-        <v>36</v>
-      </c>
-      <c r="BE5">
-        <v>110</v>
-      </c>
-      <c r="BF5">
-        <v>27</v>
-      </c>
-      <c r="BG5">
-        <v>42</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.01</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="CB5" t="s">
         <v>101</v>
@@ -1884,16 +1884,16 @@
         <v>1.52</v>
       </c>
       <c r="G6">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>10.5</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K6">
         <v>4.3</v>
@@ -1902,58 +1902,58 @@
         <v>1.5</v>
       </c>
       <c r="M6">
+        <v>1.09</v>
+      </c>
+      <c r="N6">
+        <v>2.98</v>
+      </c>
+      <c r="O6">
+        <v>1.44</v>
+      </c>
+      <c r="P6">
+        <v>1.68</v>
+      </c>
+      <c r="Q6">
+        <v>2.32</v>
+      </c>
+      <c r="R6">
+        <v>1.23</v>
+      </c>
+      <c r="S6">
+        <v>4.7</v>
+      </c>
+      <c r="T6">
+        <v>2.26</v>
+      </c>
+      <c r="U6">
+        <v>1.64</v>
+      </c>
+      <c r="V6">
         <v>1.1</v>
       </c>
-      <c r="N6">
-        <v>2.78</v>
-      </c>
-      <c r="O6">
-        <v>1.45</v>
-      </c>
-      <c r="P6">
-        <v>1.66</v>
-      </c>
-      <c r="Q6">
-        <v>2.34</v>
-      </c>
-      <c r="R6">
-        <v>1.22</v>
-      </c>
-      <c r="S6">
-        <v>4.6</v>
-      </c>
-      <c r="T6">
-        <v>2.36</v>
-      </c>
-      <c r="U6">
-        <v>1.57</v>
-      </c>
-      <c r="V6">
-        <v>1.11</v>
-      </c>
       <c r="W6">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="X6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z6">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AA6">
         <v>500</v>
       </c>
       <c r="AB6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE6">
         <v>250</v>
@@ -1962,7 +1962,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AG6">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AH6">
         <v>36</v>
@@ -1971,10 +1971,10 @@
         <v>230</v>
       </c>
       <c r="AJ6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL6">
         <v>130</v>
@@ -1983,124 +1983,124 @@
         <v>580</v>
       </c>
       <c r="AN6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6">
         <v>460</v>
       </c>
       <c r="AP6">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6">
+        <v>6</v>
+      </c>
+      <c r="AR6">
+        <v>7.6</v>
+      </c>
+      <c r="AS6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT6">
+        <v>5.3</v>
+      </c>
+      <c r="AU6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV6">
+        <v>6.8</v>
+      </c>
+      <c r="AW6">
+        <v>8</v>
+      </c>
+      <c r="AX6">
+        <v>6.6</v>
+      </c>
+      <c r="AY6">
+        <v>7.2</v>
+      </c>
+      <c r="AZ6">
+        <v>6.8</v>
+      </c>
+      <c r="BA6">
+        <v>8</v>
+      </c>
+      <c r="BB6">
+        <v>12</v>
+      </c>
+      <c r="BC6">
+        <v>17</v>
+      </c>
+      <c r="BD6">
+        <v>7.4</v>
+      </c>
+      <c r="BE6">
+        <v>8</v>
+      </c>
+      <c r="BF6">
+        <v>10</v>
+      </c>
+      <c r="BG6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH6">
+        <v>3.15</v>
+      </c>
+      <c r="BI6">
+        <v>2.46</v>
+      </c>
+      <c r="BJ6">
+        <v>14</v>
+      </c>
+      <c r="BK6">
         <v>6.2</v>
-      </c>
-      <c r="AR6">
-        <v>7.8</v>
-      </c>
-      <c r="AS6">
-        <v>8.4</v>
-      </c>
-      <c r="AT6">
-        <v>5</v>
-      </c>
-      <c r="AU6">
-        <v>4.9</v>
-      </c>
-      <c r="AV6">
-        <v>7</v>
-      </c>
-      <c r="AW6">
-        <v>8.4</v>
-      </c>
-      <c r="AX6">
-        <v>4.2</v>
-      </c>
-      <c r="AY6">
-        <v>4.9</v>
-      </c>
-      <c r="AZ6">
-        <v>7</v>
-      </c>
-      <c r="BA6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB6">
-        <v>6.2</v>
-      </c>
-      <c r="BC6">
-        <v>7.6</v>
-      </c>
-      <c r="BD6">
-        <v>7.6</v>
-      </c>
-      <c r="BE6">
-        <v>8.6</v>
-      </c>
-      <c r="BF6">
-        <v>5.3</v>
-      </c>
-      <c r="BG6">
-        <v>8.4</v>
-      </c>
-      <c r="BH6">
-        <v>3.1</v>
-      </c>
-      <c r="BI6">
-        <v>2.4</v>
-      </c>
-      <c r="BJ6">
-        <v>14.5</v>
-      </c>
-      <c r="BK6">
-        <v>5.9</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BO6">
         <v>2.92</v>
       </c>
       <c r="BP6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BR6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS6">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT6">
         <v>12.5</v>
       </c>
       <c r="BU6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="CA6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="s">
         <v>101</v>
@@ -2123,178 +2123,178 @@
         <v>99</v>
       </c>
       <c r="F7">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="G7">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="H7">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7">
         <v>4.9</v>
       </c>
-      <c r="J7">
-        <v>4.4</v>
-      </c>
       <c r="K7">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="L7">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M7">
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P7">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="Q7">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="R7">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="S7">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="T7">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U7">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="V7">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="X7">
+        <v>38</v>
+      </c>
+      <c r="Y7">
         <v>36</v>
       </c>
-      <c r="Y7">
-        <v>26</v>
-      </c>
       <c r="Z7">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AA7">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="AB7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI7">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AK7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL7">
+        <v>24</v>
+      </c>
+      <c r="AM7">
+        <v>80</v>
+      </c>
+      <c r="AN7">
+        <v>5.8</v>
+      </c>
+      <c r="AO7">
+        <v>44</v>
+      </c>
+      <c r="AP7">
         <v>27</v>
       </c>
-      <c r="AM7">
-        <v>70</v>
-      </c>
-      <c r="AN7">
-        <v>7</v>
-      </c>
-      <c r="AO7">
-        <v>55</v>
-      </c>
-      <c r="AP7">
-        <v>23</v>
-      </c>
       <c r="AQ7">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AR7">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AS7">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AT7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AW7">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AX7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA7">
+        <v>40</v>
+      </c>
+      <c r="BB7">
+        <v>15</v>
+      </c>
+      <c r="BC7">
+        <v>13</v>
+      </c>
+      <c r="BD7">
+        <v>19</v>
+      </c>
+      <c r="BE7">
+        <v>50</v>
+      </c>
+      <c r="BF7">
+        <v>5.1</v>
+      </c>
+      <c r="BG7">
         <v>32</v>
       </c>
-      <c r="BB7">
-        <v>17.5</v>
-      </c>
-      <c r="BC7">
-        <v>13.5</v>
-      </c>
-      <c r="BD7">
-        <v>20</v>
-      </c>
-      <c r="BE7">
-        <v>46</v>
-      </c>
-      <c r="BF7">
-        <v>6.4</v>
-      </c>
-      <c r="BG7">
-        <v>23</v>
-      </c>
       <c r="BH7">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BI7">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2303,46 +2303,46 @@
         <v>55</v>
       </c>
       <c r="BN7">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP7">
+        <v>11</v>
+      </c>
+      <c r="BQ7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR7">
+        <v>21</v>
+      </c>
+      <c r="BS7">
+        <v>14.5</v>
+      </c>
+      <c r="BT7">
+        <v>10.5</v>
+      </c>
+      <c r="BU7">
+        <v>8.6</v>
+      </c>
+      <c r="BV7">
+        <v>40</v>
+      </c>
+      <c r="BW7">
+        <v>26</v>
+      </c>
+      <c r="BX7">
+        <v>40</v>
+      </c>
+      <c r="BY7">
+        <v>26</v>
+      </c>
+      <c r="BZ7">
         <v>12.5</v>
       </c>
-      <c r="BQ7">
-        <v>8.4</v>
-      </c>
-      <c r="BR7">
-        <v>23</v>
-      </c>
-      <c r="BS7">
-        <v>15</v>
-      </c>
-      <c r="BT7">
-        <v>9.6</v>
-      </c>
-      <c r="BU7">
-        <v>6.6</v>
-      </c>
-      <c r="BV7">
-        <v>36</v>
-      </c>
-      <c r="BW7">
-        <v>23</v>
-      </c>
-      <c r="BX7">
-        <v>38</v>
-      </c>
-      <c r="BY7">
-        <v>25</v>
-      </c>
-      <c r="BZ7">
-        <v>15</v>
-      </c>
       <c r="CA7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CB7" t="s">
         <v>101</v>
@@ -2365,22 +2365,22 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="H8">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="I8">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
         <v>1.3</v>
@@ -2389,49 +2389,49 @@
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q8">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R8">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="U8">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V8">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="W8">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="X8">
         <v>23</v>
       </c>
       <c r="Y8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA8">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC8">
         <v>9</v>
@@ -2440,13 +2440,13 @@
         <v>13.5</v>
       </c>
       <c r="AE8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG8">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
         <v>16</v>
@@ -2455,49 +2455,49 @@
         <v>40</v>
       </c>
       <c r="AJ8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK8">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM8">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AN8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO8">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AP8">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR8">
         <v>14</v>
       </c>
       <c r="AS8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT8">
         <v>13.5</v>
       </c>
       <c r="AU8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV8">
         <v>10</v>
       </c>
       <c r="AW8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY8">
         <v>12</v>
@@ -2509,82 +2509,82 @@
         <v>28</v>
       </c>
       <c r="BB8">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BC8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BD8">
         <v>34</v>
       </c>
       <c r="BE8">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BF8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BG8">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH8">
         <v>3.8</v>
       </c>
       <c r="BI8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL8">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM8">
         <v>10.5</v>
       </c>
       <c r="BN8">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP8">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BQ8">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS8">
         <v>8.6</v>
       </c>
       <c r="BT8">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BU8">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV8">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BW8">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX8">
         <v>27</v>
       </c>
       <c r="BY8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8">
         <v>22</v>
       </c>
       <c r="CA8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB8" t="s">
         <v>101</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -319,7 +319,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-23 10:07:11</t>
+    <t>2026-09-23 12:21:57</t>
   </si>
 </sst>
 </file>
@@ -913,226 +913,226 @@
         <v>94</v>
       </c>
       <c r="F2">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="G2">
-        <v>1.42</v>
+        <v>970</v>
       </c>
       <c r="H2">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
-        <v>5.5</v>
+        <v>950</v>
       </c>
       <c r="L2">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P2">
-        <v>1.81</v>
+        <v>1.07</v>
       </c>
       <c r="Q2">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>2.12</v>
       </c>
       <c r="T2">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
+        <v>7.4</v>
+      </c>
+      <c r="AC2">
+        <v>970</v>
+      </c>
+      <c r="AD2">
+        <v>48</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>970</v>
+      </c>
+      <c r="AG2">
+        <v>970</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>240</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>70</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>970</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>10</v>
+      </c>
+      <c r="AQ2">
+        <v>2.66</v>
+      </c>
+      <c r="AR2">
+        <v>2.66</v>
+      </c>
+      <c r="AS2">
+        <v>2.66</v>
+      </c>
+      <c r="AT2">
+        <v>1.92</v>
+      </c>
+      <c r="AU2">
+        <v>2.5</v>
+      </c>
+      <c r="AV2">
+        <v>2.52</v>
+      </c>
+      <c r="AW2">
+        <v>2.66</v>
+      </c>
+      <c r="AX2">
         <v>6.8</v>
       </c>
-      <c r="AC2">
-        <v>13.5</v>
-      </c>
-      <c r="AD2">
-        <v>55</v>
-      </c>
-      <c r="AE2">
-        <v>340</v>
-      </c>
-      <c r="AF2">
-        <v>7.4</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>44</v>
-      </c>
-      <c r="AI2">
-        <v>280</v>
-      </c>
-      <c r="AJ2">
-        <v>13</v>
-      </c>
-      <c r="AK2">
-        <v>21</v>
-      </c>
-      <c r="AL2">
-        <v>65</v>
-      </c>
-      <c r="AM2">
-        <v>350</v>
-      </c>
-      <c r="AN2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>11.5</v>
-      </c>
-      <c r="AQ2">
-        <v>5.6</v>
-      </c>
-      <c r="AR2">
-        <v>6.4</v>
-      </c>
-      <c r="AS2">
-        <v>6.6</v>
-      </c>
-      <c r="AT2">
-        <v>5.5</v>
-      </c>
-      <c r="AU2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV2">
-        <v>6</v>
-      </c>
-      <c r="AW2">
-        <v>6.6</v>
-      </c>
-      <c r="AX2">
-        <v>6</v>
-      </c>
       <c r="AY2">
-        <v>8</v>
+        <v>2.22</v>
       </c>
       <c r="AZ2">
-        <v>5.8</v>
+        <v>2.66</v>
       </c>
       <c r="BA2">
-        <v>6.6</v>
+        <v>2.62</v>
       </c>
       <c r="BB2">
-        <v>9.4</v>
+        <v>2.64</v>
       </c>
       <c r="BC2">
-        <v>15</v>
+        <v>2.66</v>
       </c>
       <c r="BD2">
-        <v>6</v>
+        <v>2.56</v>
       </c>
       <c r="BE2">
-        <v>6.6</v>
+        <v>2.66</v>
       </c>
       <c r="BF2">
-        <v>7</v>
+        <v>2.16</v>
       </c>
       <c r="BG2">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH2">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>101</v>
@@ -1155,226 +1155,226 @@
         <v>95</v>
       </c>
       <c r="F3">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="G3">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="I3">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="J3">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="P3">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="U3">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="V3">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="X3">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Z3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA3">
-        <v>500</v>
+        <v>280</v>
       </c>
       <c r="AB3">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD3">
         <v>30</v>
       </c>
       <c r="AE3">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
+        <v>14.5</v>
+      </c>
+      <c r="AH3">
+        <v>38</v>
+      </c>
+      <c r="AI3">
+        <v>190</v>
+      </c>
+      <c r="AJ3">
+        <v>30</v>
+      </c>
+      <c r="AK3">
+        <v>38</v>
+      </c>
+      <c r="AL3">
+        <v>100</v>
+      </c>
+      <c r="AM3">
+        <v>410</v>
+      </c>
+      <c r="AN3">
+        <v>38</v>
+      </c>
+      <c r="AO3">
+        <v>280</v>
+      </c>
+      <c r="AP3">
+        <v>6.2</v>
+      </c>
+      <c r="AQ3">
+        <v>9.6</v>
+      </c>
+      <c r="AR3">
+        <v>6</v>
+      </c>
+      <c r="AS3">
+        <v>6.8</v>
+      </c>
+      <c r="AT3">
+        <v>4.8</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
+        <v>15.5</v>
+      </c>
+      <c r="AW3">
+        <v>60</v>
+      </c>
+      <c r="AX3">
+        <v>7.2</v>
+      </c>
+      <c r="AY3">
         <v>10.5</v>
       </c>
-      <c r="AG3">
-        <v>12</v>
-      </c>
-      <c r="AH3">
-        <v>29</v>
-      </c>
-      <c r="AI3">
-        <v>500</v>
-      </c>
-      <c r="AJ3">
+      <c r="AZ3">
         <v>23</v>
       </c>
-      <c r="AK3">
-        <v>27</v>
-      </c>
-      <c r="AL3">
-        <v>65</v>
-      </c>
-      <c r="AM3">
-        <v>500</v>
-      </c>
-      <c r="AN3">
-        <v>19.5</v>
-      </c>
-      <c r="AO3">
-        <v>220</v>
-      </c>
-      <c r="AP3">
-        <v>8</v>
-      </c>
-      <c r="AQ3">
-        <v>12.5</v>
-      </c>
-      <c r="AR3">
+      <c r="BA3">
+        <v>24</v>
+      </c>
+      <c r="BB3">
         <v>21</v>
       </c>
-      <c r="AS3">
-        <v>6</v>
-      </c>
-      <c r="AT3">
-        <v>5.3</v>
-      </c>
-      <c r="AU3">
-        <v>7</v>
-      </c>
-      <c r="AV3">
-        <v>20</v>
-      </c>
-      <c r="AW3">
-        <v>5.9</v>
-      </c>
-      <c r="AX3">
-        <v>7.6</v>
-      </c>
-      <c r="AY3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ3">
-        <v>21</v>
-      </c>
-      <c r="BA3">
-        <v>5.9</v>
-      </c>
-      <c r="BB3">
-        <v>15.5</v>
-      </c>
       <c r="BC3">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BD3">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="BE3">
         <v>7</v>
       </c>
       <c r="BF3">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="BG3">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="BH3">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="BI3">
-        <v>2.42</v>
+        <v>1.79</v>
       </c>
       <c r="BJ3">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="BK3">
-        <v>4.1</v>
+        <v>17.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BN3">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BO3">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP3">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="BQ3">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>910</v>
       </c>
       <c r="BS3">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU3">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="BV3">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="BW3">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BX3">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="BY3">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3">
-        <v>40</v>
+        <v>960</v>
       </c>
       <c r="CA3">
-        <v>5.2</v>
+        <v>48</v>
       </c>
       <c r="CB3" t="s">
         <v>101</v>
@@ -1397,226 +1397,226 @@
         <v>96</v>
       </c>
       <c r="F4">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="G4">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="H4">
         <v>9.800000000000001</v>
       </c>
       <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
+        <v>3.95</v>
+      </c>
+      <c r="K4">
+        <v>4.4</v>
+      </c>
+      <c r="L4">
+        <v>1.82</v>
+      </c>
+      <c r="M4">
+        <v>1.13</v>
+      </c>
+      <c r="N4">
+        <v>2.54</v>
+      </c>
+      <c r="O4">
+        <v>1.61</v>
+      </c>
+      <c r="P4">
+        <v>1.49</v>
+      </c>
+      <c r="Q4">
+        <v>2.88</v>
+      </c>
+      <c r="R4">
+        <v>1.16</v>
+      </c>
+      <c r="S4">
+        <v>6.4</v>
+      </c>
+      <c r="T4">
+        <v>2.96</v>
+      </c>
+      <c r="U4">
+        <v>1.4</v>
+      </c>
+      <c r="V4">
+        <v>1.08</v>
+      </c>
+      <c r="W4">
+        <v>2.88</v>
+      </c>
+      <c r="X4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y4">
+        <v>30</v>
+      </c>
+      <c r="Z4">
+        <v>150</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>5.9</v>
+      </c>
+      <c r="AC4">
         <v>13</v>
       </c>
-      <c r="J4">
-        <v>4.1</v>
-      </c>
-      <c r="K4">
-        <v>4.9</v>
-      </c>
-      <c r="L4">
-        <v>1.48</v>
-      </c>
-      <c r="M4">
-        <v>1.08</v>
-      </c>
-      <c r="N4">
-        <v>3.15</v>
-      </c>
-      <c r="O4">
-        <v>1.4</v>
-      </c>
-      <c r="P4">
-        <v>1.71</v>
-      </c>
-      <c r="Q4">
-        <v>2.2</v>
-      </c>
-      <c r="R4">
-        <v>1.26</v>
-      </c>
-      <c r="S4">
-        <v>4.2</v>
-      </c>
-      <c r="T4">
-        <v>2.42</v>
-      </c>
-      <c r="U4">
-        <v>1.52</v>
-      </c>
-      <c r="V4">
-        <v>1.09</v>
-      </c>
-      <c r="W4">
-        <v>3</v>
-      </c>
-      <c r="X4">
-        <v>13</v>
-      </c>
-      <c r="Y4">
-        <v>28</v>
-      </c>
-      <c r="Z4">
-        <v>120</v>
-      </c>
-      <c r="AA4">
-        <v>1000</v>
-      </c>
-      <c r="AB4">
-        <v>6.6</v>
-      </c>
-      <c r="AC4">
-        <v>11.5</v>
-      </c>
       <c r="AD4">
-        <v>48</v>
+        <v>990</v>
       </c>
       <c r="AE4">
-        <v>330</v>
+        <v>510</v>
       </c>
       <c r="AF4">
         <v>8.199999999999999</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AI4">
-        <v>260</v>
+        <v>490</v>
       </c>
       <c r="AJ4">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AL4">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AM4">
-        <v>790</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AR4">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS4">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT4">
+        <v>4.1</v>
+      </c>
+      <c r="AU4">
+        <v>8</v>
+      </c>
+      <c r="AV4">
+        <v>5</v>
+      </c>
+      <c r="AW4">
         <v>4.8</v>
       </c>
-      <c r="AU4">
-        <v>8.4</v>
-      </c>
-      <c r="AV4">
+      <c r="AX4">
+        <v>5.3</v>
+      </c>
+      <c r="AY4">
+        <v>9</v>
+      </c>
+      <c r="AZ4">
+        <v>4.5</v>
+      </c>
+      <c r="BA4">
+        <v>4.8</v>
+      </c>
+      <c r="BB4">
+        <v>9.4</v>
+      </c>
+      <c r="BC4">
+        <v>17.5</v>
+      </c>
+      <c r="BD4">
         <v>5.1</v>
       </c>
-      <c r="AW4">
-        <v>5.6</v>
-      </c>
-      <c r="AX4">
-        <v>5.8</v>
-      </c>
-      <c r="AY4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ4">
-        <v>5.3</v>
-      </c>
-      <c r="BA4">
-        <v>5.6</v>
-      </c>
-      <c r="BB4">
-        <v>10</v>
-      </c>
-      <c r="BC4">
-        <v>16</v>
-      </c>
-      <c r="BD4">
-        <v>5.3</v>
-      </c>
       <c r="BE4">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG4">
+        <v>4.8</v>
+      </c>
+      <c r="BH4">
+        <v>2.16</v>
+      </c>
+      <c r="BI4">
+        <v>1.96</v>
+      </c>
+      <c r="BJ4">
+        <v>26</v>
+      </c>
+      <c r="BK4">
+        <v>19</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>5</v>
+      </c>
+      <c r="BN4">
+        <v>4.1</v>
+      </c>
+      <c r="BO4">
+        <v>3.25</v>
+      </c>
+      <c r="BP4">
+        <v>18</v>
+      </c>
+      <c r="BQ4">
         <v>10.5</v>
       </c>
-      <c r="BH4">
-        <v>3.4</v>
-      </c>
-      <c r="BI4">
-        <v>2.54</v>
-      </c>
-      <c r="BJ4">
-        <v>16.5</v>
-      </c>
-      <c r="BK4">
-        <v>4.5</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>6</v>
-      </c>
-      <c r="BN4">
-        <v>3.95</v>
-      </c>
-      <c r="BO4">
-        <v>2.92</v>
-      </c>
-      <c r="BP4">
-        <v>11</v>
-      </c>
-      <c r="BQ4">
-        <v>3.95</v>
-      </c>
       <c r="BR4">
-        <v>42</v>
+        <v>910</v>
       </c>
       <c r="BS4">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT4">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BU4">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="BW4">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY4">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BZ4">
-        <v>27</v>
+        <v>960</v>
       </c>
       <c r="CA4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="CB4" t="s">
         <v>101</v>
@@ -1639,226 +1639,226 @@
         <v>97</v>
       </c>
       <c r="F5">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="G5">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="H5">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="I5">
-        <v>2.54</v>
+        <v>3.35</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="M5">
+        <v>1.18</v>
+      </c>
+      <c r="N5">
+        <v>2.18</v>
+      </c>
+      <c r="O5">
+        <v>1.77</v>
+      </c>
+      <c r="P5">
+        <v>1.38</v>
+      </c>
+      <c r="Q5">
+        <v>3.45</v>
+      </c>
+      <c r="R5">
         <v>1.12</v>
       </c>
-      <c r="N5">
-        <v>2.56</v>
-      </c>
-      <c r="O5">
-        <v>1.56</v>
-      </c>
-      <c r="P5">
+      <c r="S5">
+        <v>8.4</v>
+      </c>
+      <c r="T5">
+        <v>2.48</v>
+      </c>
+      <c r="U5">
+        <v>1.54</v>
+      </c>
+      <c r="V5">
+        <v>1.44</v>
+      </c>
+      <c r="W5">
         <v>1.52</v>
       </c>
-      <c r="Q5">
-        <v>2.66</v>
-      </c>
-      <c r="R5">
-        <v>1.17</v>
-      </c>
-      <c r="S5">
-        <v>5.7</v>
-      </c>
-      <c r="T5">
-        <v>2.12</v>
-      </c>
-      <c r="U5">
-        <v>1.7</v>
-      </c>
-      <c r="V5">
-        <v>1.65</v>
-      </c>
-      <c r="W5">
-        <v>1.36</v>
-      </c>
       <c r="X5">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="Y5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z5">
+        <v>21</v>
+      </c>
+      <c r="AA5">
+        <v>75</v>
+      </c>
+      <c r="AB5">
         <v>7.2</v>
       </c>
-      <c r="Z5">
-        <v>14</v>
-      </c>
-      <c r="AA5">
+      <c r="AC5">
+        <v>7.6</v>
+      </c>
+      <c r="AD5">
+        <v>17</v>
+      </c>
+      <c r="AE5">
+        <v>70</v>
+      </c>
+      <c r="AF5">
+        <v>17</v>
+      </c>
+      <c r="AG5">
+        <v>16</v>
+      </c>
+      <c r="AH5">
         <v>38</v>
       </c>
-      <c r="AB5">
-        <v>10</v>
-      </c>
-      <c r="AC5">
-        <v>7.4</v>
-      </c>
-      <c r="AD5">
-        <v>12</v>
-      </c>
-      <c r="AE5">
-        <v>36</v>
-      </c>
-      <c r="AF5">
-        <v>25</v>
-      </c>
-      <c r="AG5">
-        <v>17.5</v>
-      </c>
-      <c r="AH5">
+      <c r="AI5">
+        <v>130</v>
+      </c>
+      <c r="AJ5">
+        <v>60</v>
+      </c>
+      <c r="AK5">
+        <v>65</v>
+      </c>
+      <c r="AL5">
+        <v>120</v>
+      </c>
+      <c r="AM5">
+        <v>380</v>
+      </c>
+      <c r="AN5">
+        <v>90</v>
+      </c>
+      <c r="AO5">
+        <v>110</v>
+      </c>
+      <c r="AP5">
+        <v>5.9</v>
+      </c>
+      <c r="AQ5">
+        <v>6.6</v>
+      </c>
+      <c r="AR5">
+        <v>15.5</v>
+      </c>
+      <c r="AS5">
+        <v>48</v>
+      </c>
+      <c r="AT5">
+        <v>6</v>
+      </c>
+      <c r="AU5">
+        <v>6.8</v>
+      </c>
+      <c r="AV5">
+        <v>13.5</v>
+      </c>
+      <c r="AW5">
+        <v>50</v>
+      </c>
+      <c r="AX5">
+        <v>13.5</v>
+      </c>
+      <c r="AY5">
+        <v>12.5</v>
+      </c>
+      <c r="AZ5">
         <v>27</v>
       </c>
-      <c r="AI5">
-        <v>65</v>
-      </c>
-      <c r="AJ5">
-        <v>95</v>
-      </c>
-      <c r="AK5">
-        <v>70</v>
-      </c>
-      <c r="AL5">
-        <v>100</v>
-      </c>
-      <c r="AM5">
-        <v>790</v>
-      </c>
-      <c r="AN5">
-        <v>95</v>
-      </c>
-      <c r="AO5">
+      <c r="BA5">
+        <v>90</v>
+      </c>
+      <c r="BB5">
         <v>42</v>
       </c>
-      <c r="AP5">
-        <v>7</v>
-      </c>
-      <c r="AQ5">
-        <v>5.8</v>
-      </c>
-      <c r="AR5">
-        <v>12</v>
-      </c>
-      <c r="AS5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT5">
-        <v>7.4</v>
-      </c>
-      <c r="AU5">
-        <v>5.6</v>
-      </c>
-      <c r="AV5">
+      <c r="BC5">
+        <v>44</v>
+      </c>
+      <c r="BD5">
+        <v>85</v>
+      </c>
+      <c r="BE5">
+        <v>210</v>
+      </c>
+      <c r="BF5">
+        <v>60</v>
+      </c>
+      <c r="BG5">
+        <v>40</v>
+      </c>
+      <c r="BH5">
+        <v>2.06</v>
+      </c>
+      <c r="BI5">
+        <v>1.91</v>
+      </c>
+      <c r="BJ5">
+        <v>18</v>
+      </c>
+      <c r="BK5">
+        <v>15</v>
+      </c>
+      <c r="BL5">
+        <v>960</v>
+      </c>
+      <c r="BM5">
         <v>11</v>
       </c>
-      <c r="AW5">
-        <v>29</v>
-      </c>
-      <c r="AX5">
-        <v>17.5</v>
-      </c>
-      <c r="AY5">
-        <v>14</v>
-      </c>
-      <c r="AZ5">
-        <v>22</v>
-      </c>
-      <c r="BA5">
-        <v>11</v>
-      </c>
-      <c r="BB5">
-        <v>55</v>
-      </c>
-      <c r="BC5">
-        <v>11</v>
-      </c>
-      <c r="BD5">
-        <v>11.5</v>
-      </c>
-      <c r="BE5">
-        <v>11.5</v>
-      </c>
-      <c r="BF5">
-        <v>11</v>
-      </c>
-      <c r="BG5">
-        <v>26</v>
-      </c>
-      <c r="BH5">
-        <v>2.7</v>
-      </c>
-      <c r="BI5">
-        <v>2.36</v>
-      </c>
-      <c r="BJ5">
-        <v>12</v>
-      </c>
-      <c r="BK5">
-        <v>5.7</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>2.14</v>
-      </c>
       <c r="BN5">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BP5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BQ5">
-        <v>2.04</v>
+        <v>30</v>
       </c>
       <c r="BR5">
-        <v>65</v>
+        <v>860</v>
       </c>
       <c r="BS5">
-        <v>2.1</v>
+        <v>80</v>
       </c>
       <c r="BT5">
+        <v>6.6</v>
+      </c>
+      <c r="BU5">
         <v>5.4</v>
       </c>
-      <c r="BU5">
-        <v>3.6</v>
-      </c>
       <c r="BV5">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="BW5">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BY5">
-        <v>2.08</v>
+        <v>75</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA5">
-        <v>2.08</v>
+        <v>10.5</v>
       </c>
       <c r="CB5" t="s">
         <v>101</v>
@@ -1881,226 +1881,226 @@
         <v>98</v>
       </c>
       <c r="F6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G6">
         <v>1.58</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J6">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="N6">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="O6">
+        <v>1.68</v>
+      </c>
+      <c r="P6">
+        <v>1.45</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6">
+        <v>1.14</v>
+      </c>
+      <c r="S6">
+        <v>7.2</v>
+      </c>
+      <c r="T6">
+        <v>2.66</v>
+      </c>
+      <c r="U6">
         <v>1.44</v>
-      </c>
-      <c r="P6">
-        <v>1.68</v>
-      </c>
-      <c r="Q6">
-        <v>2.32</v>
-      </c>
-      <c r="R6">
-        <v>1.23</v>
-      </c>
-      <c r="S6">
-        <v>4.7</v>
-      </c>
-      <c r="T6">
-        <v>2.26</v>
-      </c>
-      <c r="U6">
-        <v>1.64</v>
       </c>
       <c r="V6">
         <v>1.1</v>
       </c>
       <c r="W6">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Z6">
         <v>100</v>
       </c>
       <c r="AA6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD6">
+        <v>60</v>
+      </c>
+      <c r="AE6">
+        <v>440</v>
+      </c>
+      <c r="AF6">
+        <v>7.8</v>
+      </c>
+      <c r="AG6">
+        <v>12</v>
+      </c>
+      <c r="AH6">
+        <v>55</v>
+      </c>
+      <c r="AI6">
+        <v>450</v>
+      </c>
+      <c r="AJ6">
+        <v>17</v>
+      </c>
+      <c r="AK6">
         <v>40</v>
       </c>
-      <c r="AE6">
-        <v>250</v>
-      </c>
-      <c r="AF6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG6">
-        <v>10</v>
-      </c>
-      <c r="AH6">
-        <v>36</v>
-      </c>
-      <c r="AI6">
-        <v>230</v>
-      </c>
-      <c r="AJ6">
-        <v>14.5</v>
-      </c>
-      <c r="AK6">
-        <v>22</v>
-      </c>
       <c r="AL6">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AM6">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AO6">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AR6">
         <v>7.6</v>
       </c>
       <c r="AS6">
+        <v>8.6</v>
+      </c>
+      <c r="AT6">
+        <v>4.5</v>
+      </c>
+      <c r="AU6">
+        <v>8</v>
+      </c>
+      <c r="AV6">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT6">
-        <v>5.3</v>
-      </c>
-      <c r="AU6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV6">
-        <v>6.8</v>
-      </c>
       <c r="AW6">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AX6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY6">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="BA6">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BB6">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC6">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="BD6">
         <v>7.4</v>
       </c>
       <c r="BE6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="BG6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH6">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="BI6">
-        <v>2.46</v>
+        <v>1.82</v>
       </c>
       <c r="BJ6">
+        <v>26</v>
+      </c>
+      <c r="BK6">
+        <v>20</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>14.5</v>
+      </c>
+      <c r="BN6">
+        <v>3.85</v>
+      </c>
+      <c r="BO6">
+        <v>3.45</v>
+      </c>
+      <c r="BP6">
+        <v>17.5</v>
+      </c>
+      <c r="BQ6">
+        <v>14.5</v>
+      </c>
+      <c r="BR6">
+        <v>110</v>
+      </c>
+      <c r="BS6">
+        <v>12.5</v>
+      </c>
+      <c r="BT6">
         <v>14</v>
       </c>
-      <c r="BK6">
-        <v>6.2</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>10.5</v>
-      </c>
-      <c r="BN6">
-        <v>3.8</v>
-      </c>
-      <c r="BO6">
-        <v>2.92</v>
-      </c>
-      <c r="BP6">
+      <c r="BU6">
         <v>11</v>
       </c>
-      <c r="BQ6">
-        <v>5.5</v>
-      </c>
-      <c r="BR6">
-        <v>36</v>
-      </c>
-      <c r="BS6">
-        <v>8.4</v>
-      </c>
-      <c r="BT6">
-        <v>12.5</v>
-      </c>
-      <c r="BU6">
-        <v>5.8</v>
-      </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BW6">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BZ6">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="CA6">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="CB6" t="s">
         <v>101</v>
@@ -2123,73 +2123,73 @@
         <v>99</v>
       </c>
       <c r="F7">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="G7">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="H7">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K7">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>1.25</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P7">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="Q7">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R7">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="S7">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T7">
         <v>1.58</v>
       </c>
       <c r="U7">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W7">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z7">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AA7">
         <v>140</v>
       </c>
       <c r="AB7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC7">
         <v>12</v>
@@ -2207,49 +2207,49 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AK7">
         <v>14.5</v>
       </c>
       <c r="AL7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ7">
         <v>28</v>
       </c>
       <c r="AR7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AT7">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU7">
         <v>10.5</v>
       </c>
       <c r="AV7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW7">
         <v>50</v>
@@ -2261,28 +2261,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC7">
         <v>13</v>
       </c>
       <c r="BD7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE7">
         <v>50</v>
       </c>
       <c r="BF7">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG7">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BH7">
         <v>5.7</v>
@@ -2294,16 +2294,16 @@
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>55</v>
+        <v>5.4</v>
       </c>
       <c r="BN7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO7">
         <v>4.3</v>
@@ -2312,37 +2312,37 @@
         <v>11</v>
       </c>
       <c r="BQ7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR7">
         <v>21</v>
       </c>
       <c r="BS7">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="BT7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU7">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="BV7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW7">
-        <v>26</v>
+        <v>5.1</v>
       </c>
       <c r="BX7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY7">
-        <v>26</v>
+        <v>5.1</v>
       </c>
       <c r="BZ7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA7">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="CB7" t="s">
         <v>101</v>
@@ -2365,25 +2365,25 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G8">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H8">
+        <v>2.34</v>
+      </c>
+      <c r="I8">
         <v>2.4</v>
       </c>
-      <c r="I8">
-        <v>2.46</v>
-      </c>
       <c r="J8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M8">
         <v>1.05</v>
@@ -2392,52 +2392,52 @@
         <v>4.4</v>
       </c>
       <c r="O8">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P8">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q8">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R8">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="T8">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U8">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V8">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W8">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y8">
         <v>13</v>
       </c>
       <c r="Z8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC8">
         <v>9</v>
       </c>
       <c r="AD8">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
         <v>24</v>
@@ -2452,25 +2452,25 @@
         <v>16</v>
       </c>
       <c r="AI8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ8">
         <v>55</v>
       </c>
       <c r="AK8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL8">
         <v>40</v>
       </c>
       <c r="AM8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO8">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AP8">
         <v>16.5</v>
@@ -2482,13 +2482,13 @@
         <v>14</v>
       </c>
       <c r="AS8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT8">
         <v>13.5</v>
       </c>
       <c r="AU8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV8">
         <v>10</v>
@@ -2497,7 +2497,7 @@
         <v>20</v>
       </c>
       <c r="AX8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY8">
         <v>12</v>
@@ -2506,40 +2506,40 @@
         <v>14</v>
       </c>
       <c r="BA8">
+        <v>27</v>
+      </c>
+      <c r="BB8">
+        <v>40</v>
+      </c>
+      <c r="BC8">
         <v>28</v>
       </c>
-      <c r="BB8">
-        <v>42</v>
-      </c>
-      <c r="BC8">
-        <v>27</v>
-      </c>
       <c r="BD8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE8">
         <v>55</v>
       </c>
       <c r="BF8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BH8">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BI8">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BJ8">
         <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BL8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM8">
         <v>10.5</v>
@@ -2548,7 +2548,7 @@
         <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP8">
         <v>22</v>
@@ -2557,34 +2557,34 @@
         <v>7.6</v>
       </c>
       <c r="BR8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BU8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV8">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BW8">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="CA8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
         <v>101</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>League</t>
   </si>
@@ -256,34 +256,22 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>US United Soccer League</t>
-  </si>
-  <si>
     <t>Peruvian Primera Division</t>
   </si>
   <si>
     <t>2026-09-23</t>
   </si>
   <si>
-    <t>16:00:00</t>
-  </si>
-  <si>
     <t>20:00:00</t>
   </si>
   <si>
-    <t>Birmingham Legion FC</t>
-  </si>
-  <si>
     <t>Asociacion Deportiva Tarma</t>
   </si>
   <si>
-    <t>Brooklyn FC</t>
-  </si>
-  <si>
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-23 14:33:38</t>
+    <t>2026-09-23 16:46:10</t>
   </si>
 </sst>
 </file>
@@ -615,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -865,483 +853,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
         <v>82</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>83</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2">
+        <v>3.35</v>
+      </c>
+      <c r="G2">
+        <v>3.5</v>
+      </c>
+      <c r="H2">
+        <v>2.14</v>
+      </c>
+      <c r="I2">
+        <v>2.2</v>
+      </c>
+      <c r="J2">
+        <v>3.9</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>1.33</v>
+      </c>
+      <c r="M2">
+        <v>1.05</v>
+      </c>
+      <c r="N2">
+        <v>4.5</v>
+      </c>
+      <c r="O2">
+        <v>1.26</v>
+      </c>
+      <c r="P2">
+        <v>2.24</v>
+      </c>
+      <c r="Q2">
+        <v>1.76</v>
+      </c>
+      <c r="R2">
+        <v>1.47</v>
+      </c>
+      <c r="S2">
+        <v>3</v>
+      </c>
+      <c r="T2">
+        <v>1.67</v>
+      </c>
+      <c r="U2">
+        <v>2.38</v>
+      </c>
+      <c r="V2">
+        <v>1.83</v>
+      </c>
+      <c r="W2">
+        <v>1.4</v>
+      </c>
+      <c r="X2">
+        <v>19</v>
+      </c>
+      <c r="Y2">
+        <v>11</v>
+      </c>
+      <c r="Z2">
+        <v>15.5</v>
+      </c>
+      <c r="AA2">
+        <v>27</v>
+      </c>
+      <c r="AB2">
+        <v>15</v>
+      </c>
+      <c r="AC2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD2">
+        <v>10.5</v>
+      </c>
+      <c r="AE2">
+        <v>22</v>
+      </c>
+      <c r="AF2">
+        <v>27</v>
+      </c>
+      <c r="AG2">
+        <v>13.5</v>
+      </c>
+      <c r="AH2">
+        <v>16.5</v>
+      </c>
+      <c r="AI2">
+        <v>40</v>
+      </c>
+      <c r="AJ2">
+        <v>65</v>
+      </c>
+      <c r="AK2">
+        <v>38</v>
+      </c>
+      <c r="AL2">
+        <v>42</v>
+      </c>
+      <c r="AM2">
+        <v>75</v>
+      </c>
+      <c r="AN2">
+        <v>32</v>
+      </c>
+      <c r="AO2">
+        <v>14</v>
+      </c>
+      <c r="AP2">
+        <v>16.5</v>
+      </c>
+      <c r="AQ2">
+        <v>10.5</v>
+      </c>
+      <c r="AR2">
+        <v>13.5</v>
+      </c>
+      <c r="AS2">
+        <v>25</v>
+      </c>
+      <c r="AT2">
+        <v>13.5</v>
+      </c>
+      <c r="AU2">
+        <v>8.4</v>
+      </c>
+      <c r="AV2">
+        <v>10</v>
+      </c>
+      <c r="AW2">
+        <v>19</v>
+      </c>
+      <c r="AX2">
+        <v>23</v>
+      </c>
+      <c r="AY2">
+        <v>12.5</v>
+      </c>
+      <c r="AZ2">
+        <v>15</v>
+      </c>
+      <c r="BA2">
+        <v>28</v>
+      </c>
+      <c r="BB2">
+        <v>55</v>
+      </c>
+      <c r="BC2">
+        <v>32</v>
+      </c>
+      <c r="BD2">
+        <v>36</v>
+      </c>
+      <c r="BE2">
+        <v>55</v>
+      </c>
+      <c r="BF2">
+        <v>27</v>
+      </c>
+      <c r="BG2">
+        <v>12</v>
+      </c>
+      <c r="BH2">
+        <v>4.6</v>
+      </c>
+      <c r="BI2">
+        <v>3.65</v>
+      </c>
+      <c r="BJ2">
+        <v>11</v>
+      </c>
+      <c r="BK2">
+        <v>8</v>
+      </c>
+      <c r="BL2">
+        <v>110</v>
+      </c>
+      <c r="BM2">
+        <v>7</v>
+      </c>
+      <c r="BN2">
+        <v>7.2</v>
+      </c>
+      <c r="BO2">
+        <v>4.6</v>
+      </c>
+      <c r="BP2">
+        <v>23</v>
+      </c>
+      <c r="BQ2">
+        <v>5</v>
+      </c>
+      <c r="BR2">
+        <v>34</v>
+      </c>
+      <c r="BS2">
+        <v>5.4</v>
+      </c>
+      <c r="BT2">
+        <v>6.2</v>
+      </c>
+      <c r="BU2">
+        <v>4.7</v>
+      </c>
+      <c r="BV2">
+        <v>15</v>
+      </c>
+      <c r="BW2">
+        <v>4.7</v>
+      </c>
+      <c r="BX2">
+        <v>29</v>
+      </c>
+      <c r="BY2">
+        <v>5.2</v>
+      </c>
+      <c r="BZ2">
+        <v>19</v>
+      </c>
+      <c r="CA2">
+        <v>4.7</v>
+      </c>
+      <c r="CB2" t="s">
         <v>85</v>
-      </c>
-      <c r="E2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2">
-        <v>1.05</v>
-      </c>
-      <c r="G2">
-        <v>1.06</v>
-      </c>
-      <c r="H2">
-        <v>100</v>
-      </c>
-      <c r="I2">
-        <v>190</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
-      <c r="K2">
-        <v>29</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>3.4</v>
-      </c>
-      <c r="Q2">
-        <v>1.38</v>
-      </c>
-      <c r="R2">
-        <v>1.43</v>
-      </c>
-      <c r="S2">
-        <v>3.1</v>
-      </c>
-      <c r="T2">
-        <v>2.52</v>
-      </c>
-      <c r="U2">
-        <v>1.59</v>
-      </c>
-      <c r="V2">
-        <v>1.01</v>
-      </c>
-      <c r="W2">
-        <v>19</v>
-      </c>
-      <c r="X2">
-        <v>1000</v>
-      </c>
-      <c r="Y2">
-        <v>1000</v>
-      </c>
-      <c r="Z2">
-        <v>1000</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>1000</v>
-      </c>
-      <c r="AC2">
-        <v>1000</v>
-      </c>
-      <c r="AD2">
-        <v>1000</v>
-      </c>
-      <c r="AE2">
-        <v>1000</v>
-      </c>
-      <c r="AF2">
-        <v>3.4</v>
-      </c>
-      <c r="AG2">
-        <v>7.4</v>
-      </c>
-      <c r="AH2">
-        <v>30</v>
-      </c>
-      <c r="AI2">
-        <v>220</v>
-      </c>
-      <c r="AJ2">
-        <v>4.6</v>
-      </c>
-      <c r="AK2">
-        <v>10.5</v>
-      </c>
-      <c r="AL2">
-        <v>46</v>
-      </c>
-      <c r="AM2">
-        <v>380</v>
-      </c>
-      <c r="AN2">
-        <v>7.4</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>110</v>
-      </c>
-      <c r="AQ2">
-        <v>110</v>
-      </c>
-      <c r="AR2">
-        <v>110</v>
-      </c>
-      <c r="AS2">
-        <v>110</v>
-      </c>
-      <c r="AT2">
-        <v>15</v>
-      </c>
-      <c r="AU2">
-        <v>16.5</v>
-      </c>
-      <c r="AV2">
-        <v>16.5</v>
-      </c>
-      <c r="AW2">
-        <v>16.5</v>
-      </c>
-      <c r="AX2">
-        <v>3.15</v>
-      </c>
-      <c r="AY2">
-        <v>6.2</v>
-      </c>
-      <c r="AZ2">
-        <v>25</v>
-      </c>
-      <c r="BA2">
-        <v>100</v>
-      </c>
-      <c r="BB2">
-        <v>4.2</v>
-      </c>
-      <c r="BC2">
-        <v>9.4</v>
-      </c>
-      <c r="BD2">
-        <v>30</v>
-      </c>
-      <c r="BE2">
-        <v>16</v>
-      </c>
-      <c r="BF2">
-        <v>5.5</v>
-      </c>
-      <c r="BG2">
-        <v>16.5</v>
-      </c>
-      <c r="BH2">
-        <v>0</v>
-      </c>
-      <c r="BI2">
-        <v>0</v>
-      </c>
-      <c r="BJ2">
-        <v>0</v>
-      </c>
-      <c r="BK2">
-        <v>0</v>
-      </c>
-      <c r="BL2">
-        <v>0</v>
-      </c>
-      <c r="BM2">
-        <v>0</v>
-      </c>
-      <c r="BN2">
-        <v>0</v>
-      </c>
-      <c r="BO2">
-        <v>0</v>
-      </c>
-      <c r="BP2">
-        <v>0</v>
-      </c>
-      <c r="BQ2">
-        <v>0</v>
-      </c>
-      <c r="BR2">
-        <v>0</v>
-      </c>
-      <c r="BS2">
-        <v>0</v>
-      </c>
-      <c r="BT2">
-        <v>0</v>
-      </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
-      <c r="BV2">
-        <v>0</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
-      <c r="BY2">
-        <v>0</v>
-      </c>
-      <c r="BZ2">
-        <v>0</v>
-      </c>
-      <c r="CA2">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:80">
-      <c r="A3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3">
-        <v>3.7</v>
-      </c>
-      <c r="G3">
-        <v>3.9</v>
-      </c>
-      <c r="H3">
-        <v>2.02</v>
-      </c>
-      <c r="I3">
-        <v>2.08</v>
-      </c>
-      <c r="J3">
-        <v>3.9</v>
-      </c>
-      <c r="K3">
-        <v>4.1</v>
-      </c>
-      <c r="L3">
-        <v>1.33</v>
-      </c>
-      <c r="M3">
-        <v>1.05</v>
-      </c>
-      <c r="N3">
-        <v>4.5</v>
-      </c>
-      <c r="O3">
-        <v>1.25</v>
-      </c>
-      <c r="P3">
-        <v>2.26</v>
-      </c>
-      <c r="Q3">
-        <v>1.73</v>
-      </c>
-      <c r="R3">
-        <v>1.51</v>
-      </c>
-      <c r="S3">
-        <v>2.88</v>
-      </c>
-      <c r="T3">
-        <v>1.65</v>
-      </c>
-      <c r="U3">
-        <v>2.44</v>
-      </c>
-      <c r="V3">
-        <v>1.92</v>
-      </c>
-      <c r="W3">
-        <v>1.34</v>
-      </c>
-      <c r="X3">
-        <v>19.5</v>
-      </c>
-      <c r="Y3">
-        <v>12</v>
-      </c>
-      <c r="Z3">
-        <v>14.5</v>
-      </c>
-      <c r="AA3">
-        <v>27</v>
-      </c>
-      <c r="AB3">
-        <v>17.5</v>
-      </c>
-      <c r="AC3">
-        <v>9</v>
-      </c>
-      <c r="AD3">
-        <v>11</v>
-      </c>
-      <c r="AE3">
-        <v>23</v>
-      </c>
-      <c r="AF3">
-        <v>32</v>
-      </c>
-      <c r="AG3">
-        <v>15.5</v>
-      </c>
-      <c r="AH3">
-        <v>17</v>
-      </c>
-      <c r="AI3">
-        <v>38</v>
-      </c>
-      <c r="AJ3">
-        <v>75</v>
-      </c>
-      <c r="AK3">
-        <v>42</v>
-      </c>
-      <c r="AL3">
-        <v>46</v>
-      </c>
-      <c r="AM3">
-        <v>90</v>
-      </c>
-      <c r="AN3">
-        <v>48</v>
-      </c>
-      <c r="AO3">
-        <v>12.5</v>
-      </c>
-      <c r="AP3">
-        <v>16.5</v>
-      </c>
-      <c r="AQ3">
-        <v>10.5</v>
-      </c>
-      <c r="AR3">
-        <v>12.5</v>
-      </c>
-      <c r="AS3">
-        <v>22</v>
-      </c>
-      <c r="AT3">
-        <v>15.5</v>
-      </c>
-      <c r="AU3">
-        <v>8</v>
-      </c>
-      <c r="AV3">
-        <v>9.6</v>
-      </c>
-      <c r="AW3">
-        <v>17.5</v>
-      </c>
-      <c r="AX3">
-        <v>25</v>
-      </c>
-      <c r="AY3">
-        <v>13.5</v>
-      </c>
-      <c r="AZ3">
-        <v>14.5</v>
-      </c>
-      <c r="BA3">
-        <v>27</v>
-      </c>
-      <c r="BB3">
-        <v>30</v>
-      </c>
-      <c r="BC3">
-        <v>30</v>
-      </c>
-      <c r="BD3">
-        <v>36</v>
-      </c>
-      <c r="BE3">
-        <v>40</v>
-      </c>
-      <c r="BF3">
-        <v>19</v>
-      </c>
-      <c r="BG3">
-        <v>10.5</v>
-      </c>
-      <c r="BH3">
-        <v>4.7</v>
-      </c>
-      <c r="BI3">
-        <v>3.65</v>
-      </c>
-      <c r="BJ3">
-        <v>11</v>
-      </c>
-      <c r="BK3">
-        <v>3.7</v>
-      </c>
-      <c r="BL3">
-        <v>110</v>
-      </c>
-      <c r="BM3">
-        <v>5.4</v>
-      </c>
-      <c r="BN3">
-        <v>7.8</v>
-      </c>
-      <c r="BO3">
-        <v>3.3</v>
-      </c>
-      <c r="BP3">
-        <v>30</v>
-      </c>
-      <c r="BQ3">
-        <v>4.5</v>
-      </c>
-      <c r="BR3">
-        <v>42</v>
-      </c>
-      <c r="BS3">
-        <v>5</v>
-      </c>
-      <c r="BT3">
-        <v>5.9</v>
-      </c>
-      <c r="BU3">
-        <v>4.4</v>
-      </c>
-      <c r="BV3">
-        <v>16</v>
-      </c>
-      <c r="BW3">
-        <v>4.2</v>
-      </c>
-      <c r="BX3">
-        <v>28</v>
-      </c>
-      <c r="BY3">
-        <v>4.7</v>
-      </c>
-      <c r="BZ3">
-        <v>22</v>
-      </c>
-      <c r="CA3">
-        <v>4.4</v>
-      </c>
-      <c r="CB3" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-23.xlsx
@@ -271,7 +271,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-09-23 16:46:10</t>
+    <t>2026-09-23 18:58:20</t>
   </si>
 </sst>
 </file>
@@ -865,226 +865,226 @@
         <v>84</v>
       </c>
       <c r="F2">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="G2">
-        <v>3.5</v>
+        <v>1.05</v>
       </c>
       <c r="H2">
-        <v>2.14</v>
+        <v>75</v>
       </c>
       <c r="I2">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>21</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="L2">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T2">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.4</v>
+        <v>26</v>
       </c>
       <c r="X2">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1.03</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1000</v>
+      </c>
+      <c r="AQ2">
+        <v>34</v>
+      </c>
+      <c r="AR2">
+        <v>34</v>
+      </c>
+      <c r="AS2">
+        <v>34</v>
+      </c>
+      <c r="AT2">
+        <v>1000</v>
+      </c>
+      <c r="AU2">
+        <v>12.5</v>
+      </c>
+      <c r="AV2">
+        <v>50</v>
+      </c>
+      <c r="AW2">
+        <v>50</v>
+      </c>
+      <c r="AX2">
+        <v>1000</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>26</v>
+      </c>
+      <c r="BA2">
+        <v>50</v>
+      </c>
+      <c r="BB2">
+        <v>1000</v>
+      </c>
+      <c r="BC2">
         <v>22</v>
       </c>
-      <c r="AF2">
-        <v>27</v>
-      </c>
-      <c r="AG2">
-        <v>13.5</v>
-      </c>
-      <c r="AH2">
-        <v>16.5</v>
-      </c>
-      <c r="AI2">
-        <v>40</v>
-      </c>
-      <c r="AJ2">
-        <v>65</v>
-      </c>
-      <c r="AK2">
-        <v>38</v>
-      </c>
-      <c r="AL2">
-        <v>42</v>
-      </c>
-      <c r="AM2">
-        <v>75</v>
-      </c>
-      <c r="AN2">
-        <v>32</v>
-      </c>
-      <c r="AO2">
-        <v>14</v>
-      </c>
-      <c r="AP2">
-        <v>16.5</v>
-      </c>
-      <c r="AQ2">
-        <v>10.5</v>
-      </c>
-      <c r="AR2">
-        <v>13.5</v>
-      </c>
-      <c r="AS2">
-        <v>25</v>
-      </c>
-      <c r="AT2">
-        <v>13.5</v>
-      </c>
-      <c r="AU2">
-        <v>8.4</v>
-      </c>
-      <c r="AV2">
-        <v>10</v>
-      </c>
-      <c r="AW2">
-        <v>19</v>
-      </c>
-      <c r="AX2">
-        <v>23</v>
-      </c>
-      <c r="AY2">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>28</v>
-      </c>
-      <c r="BB2">
-        <v>55</v>
-      </c>
-      <c r="BC2">
-        <v>32</v>
-      </c>
       <c r="BD2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BE2">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="BF2">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="BG2">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="BH2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>85</v>
